--- a/database/event/5339/event_5339_evp_summary.xlsx
+++ b/database/event/5339/event_5339_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.4588</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3448</v>
+        <v>2.2841</v>
       </c>
       <c r="E2" t="n">
         <v>6.8474</v>
@@ -548,7 +548,7 @@
         <v>1.4587</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3446</v>
+        <v>2.2839</v>
       </c>
       <c r="E3" t="n">
         <v>6.8468</v>
@@ -594,7 +594,7 @@
         <v>1.3452</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1294</v>
+        <v>2.0717</v>
       </c>
       <c r="E4" t="n">
         <v>6.3142</v>
@@ -640,7 +640,7 @@
         <v>1.1186</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6997</v>
+        <v>1.6479</v>
       </c>
       <c r="E5" t="n">
         <v>5.2505</v>
@@ -686,7 +686,7 @@
         <v>1.044</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5583</v>
+        <v>1.5084</v>
       </c>
       <c r="E6" t="n">
         <v>4.9005</v>
@@ -732,7 +732,7 @@
         <v>0.9359</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3532</v>
+        <v>1.3062</v>
       </c>
       <c r="E7" t="n">
         <v>4.3928</v>
@@ -778,7 +778,7 @@
         <v>0.8052</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1055</v>
+        <v>1.0618</v>
       </c>
       <c r="E8" t="n">
         <v>3.7795</v>
@@ -824,7 +824,7 @@
         <v>0.7554999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0112</v>
+        <v>0.9689</v>
       </c>
       <c r="E9" t="n">
         <v>3.5462</v>
@@ -870,7 +870,7 @@
         <v>0.663</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8358</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>3.112</v>
@@ -916,7 +916,7 @@
         <v>0.6594</v>
       </c>
       <c r="D11" t="n">
-        <v>0.829</v>
+        <v>0.7892</v>
       </c>
       <c r="E11" t="n">
         <v>3.0952</v>
@@ -962,7 +962,7 @@
         <v>0.625</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7637</v>
+        <v>0.7248</v>
       </c>
       <c r="E12" t="n">
         <v>2.9335</v>
@@ -1008,7 +1008,7 @@
         <v>0.5621</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6445</v>
+        <v>0.6072</v>
       </c>
       <c r="E13" t="n">
         <v>2.6383</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5819</v>
+        <v>2.5722</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5501</v>
+        <v>0.548</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6217</v>
+        <v>0.5809</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5819</v>
+        <v>2.5722</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5819</v>
+        <v>2.5722</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5819</v>
+        <v>2.5722</v>
       </c>
       <c r="I14" t="n">
         <v>2.5939</v>
@@ -1100,7 +1100,7 @@
         <v>0.5048</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5001</v>
       </c>
       <c r="E15" t="n">
         <v>2.3694</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3563</v>
+        <v>2.3475</v>
       </c>
       <c r="C16" t="n">
-        <v>0.502</v>
+        <v>0.5001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5305</v>
+        <v>0.4913</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3563</v>
+        <v>2.3475</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3563</v>
+        <v>2.3475</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3563</v>
+        <v>2.3475</v>
       </c>
       <c r="I16" t="n">
         <v>2.3672</v>
@@ -1192,7 +1192,7 @@
         <v>0.463</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4566</v>
+        <v>0.422</v>
       </c>
       <c r="E17" t="n">
         <v>2.1734</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0899</v>
+        <v>2.0821</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4452</v>
+        <v>0.4436</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4229</v>
+        <v>0.3856</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0899</v>
+        <v>2.0821</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0899</v>
+        <v>2.0821</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0899</v>
+        <v>2.0821</v>
       </c>
       <c r="I18" t="n">
         <v>2.0996</v>
@@ -1284,7 +1284,7 @@
         <v>0.4377</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4085</v>
+        <v>0.3745</v>
       </c>
       <c r="E19" t="n">
         <v>2.0543</v>
@@ -1330,7 +1330,7 @@
         <v>0.32</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1855</v>
+        <v>0.1546</v>
       </c>
       <c r="E20" t="n">
         <v>1.5022</v>
@@ -1376,7 +1376,7 @@
         <v>0.3146</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1752</v>
+        <v>0.1444</v>
       </c>
       <c r="E21" t="n">
         <v>1.4768</v>
@@ -1422,7 +1422,7 @@
         <v>0.2839</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1169</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>1.3324</v>
@@ -1468,7 +1468,7 @@
         <v>0.2413</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0361</v>
+        <v>0.0073</v>
       </c>
       <c r="E23" t="n">
         <v>1.1325</v>
@@ -1514,7 +1514,7 @@
         <v>0.24</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0338</v>
+        <v>0.005</v>
       </c>
       <c r="E24" t="n">
         <v>1.1267</v>
@@ -1560,7 +1560,7 @@
         <v>0.0834</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2632</v>
+        <v>-0.288</v>
       </c>
       <c r="E25" t="n">
         <v>0.3914</v>
@@ -1606,7 +1606,7 @@
         <v>0.0694</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2898</v>
+        <v>-0.3142</v>
       </c>
       <c r="E26" t="n">
         <v>0.3256</v>
@@ -1652,7 +1652,7 @@
         <v>0.0571</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3131</v>
+        <v>-0.3371</v>
       </c>
       <c r="E27" t="n">
         <v>0.2681</v>
@@ -1698,7 +1698,7 @@
         <v>0.0434</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3391</v>
+        <v>-0.3628</v>
       </c>
       <c r="E28" t="n">
         <v>0.2037</v>
@@ -1744,7 +1744,7 @@
         <v>0.008</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4061</v>
+        <v>-0.4289</v>
       </c>
       <c r="E29" t="n">
         <v>0.0377</v>
@@ -1790,7 +1790,7 @@
         <v>-0.054</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.2534</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1749</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.753</v>
+        <v>-0.771</v>
       </c>
       <c r="E31" t="n">
         <v>-0.821</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1814</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7653</v>
+        <v>-0.7831</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8512999999999999</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2302</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8579</v>
+        <v>-0.8745000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>-1.0807</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2349</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8667</v>
+        <v>-0.8831</v>
       </c>
       <c r="E34" t="n">
         <v>-1.1025</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2473</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8903</v>
+        <v>-0.9063</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1607</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2822</v>
+        <v>-1.2774</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2732</v>
+        <v>-0.2721</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9393</v>
+        <v>-0.9528</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2822</v>
+        <v>-1.2774</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2822</v>
+        <v>-1.2774</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2822</v>
+        <v>-1.2774</v>
       </c>
       <c r="I36" t="n">
         <v>-1.2882</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2756</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.944</v>
+        <v>-0.9594</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2938</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2976</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9857</v>
+        <v>-1.0004</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3969</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6896</v>
+        <v>-1.6833</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.36</v>
+        <v>-0.3586</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1039</v>
+        <v>-1.1145</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6896</v>
+        <v>-1.6833</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6896</v>
+        <v>-1.6833</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6896</v>
+        <v>-1.6833</v>
       </c>
       <c r="I39" t="n">
         <v>-1.6975</v>
@@ -2250,7 +2250,7 @@
         <v>-0.3707</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1243</v>
+        <v>-1.1371</v>
       </c>
       <c r="E40" t="n">
         <v>-1.74</v>
@@ -2296,7 +2296,7 @@
         <v>-0.4531</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2806</v>
+        <v>-1.2913</v>
       </c>
       <c r="E41" t="n">
         <v>-2.127</v>

--- a/database/event/5339/event_5339_evp_summary.xlsx
+++ b/database/event/5339/event_5339_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8474</v>
+        <v>6.169</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4588</v>
+        <v>1.3143</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2841</v>
+        <v>2.147</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8474</v>
+        <v>6.169</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3095</v>
+        <v>3.8418</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5379</v>
+        <v>2.3272</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7778</v>
+        <v>8.049899999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8725</v>
+        <v>4.1856</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5379</v>
+        <v>2.3272</v>
       </c>
       <c r="K2" t="n">
         <v>192</v>
@@ -529,7 +529,7 @@
         <v>77</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4104</v>
+        <v>6.5128</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8468</v>
+        <v>6.0163</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4587</v>
+        <v>1.2817</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2839</v>
+        <v>2.078</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8468</v>
+        <v>6.0163</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8473</v>
+        <v>3.5527</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9995</v>
+        <v>2.4636</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8473</v>
+        <v>7.0312</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1183</v>
+        <v>3.6559</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9995</v>
+        <v>2.4636</v>
       </c>
       <c r="K3" t="n">
         <v>192</v>
@@ -575,7 +575,7 @@
         <v>77</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1178</v>
+        <v>6.1195</v>
       </c>
       <c r="N3" t="n">
         <v>269</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3142</v>
+        <v>5.4634</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3452</v>
+        <v>1.1639</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0717</v>
+        <v>1.8284</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3142</v>
+        <v>5.4634</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9269</v>
+        <v>3.5147</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3873</v>
+        <v>1.9487</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9269</v>
+        <v>6.8971</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1829</v>
+        <v>3.5862</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3873</v>
+        <v>1.9487</v>
       </c>
       <c r="K4" t="n">
         <v>192</v>
@@ -621,7 +621,7 @@
         <v>77</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5702</v>
+        <v>5.5349</v>
       </c>
       <c r="N4" t="n">
         <v>269</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.2505</v>
+        <v>5.0943</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1186</v>
+        <v>1.0853</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6479</v>
+        <v>1.6618</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2505</v>
+        <v>5.0943</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5788</v>
+        <v>4.4366</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6717</v>
+        <v>0.6577</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8611</v>
+        <v>10.1455</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7506</v>
+        <v>5.2752</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6717</v>
+        <v>0.6577</v>
       </c>
       <c r="K5" t="n">
         <v>167</v>
@@ -667,7 +667,7 @@
         <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4223</v>
+        <v>5.9329</v>
       </c>
       <c r="N5" t="n">
         <v>252</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9005</v>
+        <v>4.868</v>
       </c>
       <c r="C6" t="n">
-        <v>1.044</v>
+        <v>1.0371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5084</v>
+        <v>1.5596</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9005</v>
+        <v>4.868</v>
       </c>
       <c r="F6" t="n">
-        <v>4.8663</v>
+        <v>4.4518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0342</v>
+        <v>0.4162</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9091</v>
+        <v>12.7657</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4106</v>
+        <v>6.6376</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0342</v>
+        <v>0.4162</v>
       </c>
       <c r="K6" t="n">
         <v>338</v>
@@ -713,7 +713,7 @@
         <v>77</v>
       </c>
       <c r="M6" t="n">
-        <v>6.4448</v>
+        <v>7.0538</v>
       </c>
       <c r="N6" t="n">
         <v>415</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.3928</v>
+        <v>4.2179</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9359</v>
+        <v>0.8986</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3062</v>
+        <v>1.2662</v>
       </c>
       <c r="E7" t="n">
-        <v>4.3928</v>
+        <v>4.2179</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5193</v>
+        <v>4.2732</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1265</v>
+        <v>-0.0553</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6216</v>
+        <v>9.569900000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5565</v>
+        <v>4.9759</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1265</v>
+        <v>-0.0553</v>
       </c>
       <c r="K7" t="n">
         <v>338</v>
@@ -759,7 +759,7 @@
         <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>4.43</v>
+        <v>4.9206</v>
       </c>
       <c r="N7" t="n">
         <v>415</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7795</v>
+        <v>4.0976</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8052</v>
+        <v>0.873</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0618</v>
+        <v>1.2118</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7795</v>
+        <v>4.0976</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6894</v>
+        <v>3.4035</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0901</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6894</v>
+        <v>6.5054</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9904</v>
+        <v>3.3825</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0901</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="L8" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0805</v>
+        <v>4.0766</v>
       </c>
       <c r="N8" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5462</v>
+        <v>3.6948</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7871</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9689</v>
+        <v>1.03</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5462</v>
+        <v>3.6948</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1622</v>
+        <v>3.4342</v>
       </c>
       <c r="G9" t="n">
-        <v>0.384</v>
+        <v>0.2606</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1622</v>
+        <v>6.6137</v>
       </c>
       <c r="I9" t="n">
-        <v>2.563</v>
+        <v>3.4388</v>
       </c>
       <c r="J9" t="n">
-        <v>0.384</v>
+        <v>0.2606</v>
       </c>
       <c r="K9" t="n">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="L9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M9" t="n">
-        <v>2.947</v>
+        <v>3.6994</v>
       </c>
       <c r="N9" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.112</v>
+        <v>3.671</v>
       </c>
       <c r="C10" t="n">
-        <v>0.663</v>
+        <v>0.7821</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7959000000000001</v>
+        <v>1.0193</v>
       </c>
       <c r="E10" t="n">
-        <v>3.112</v>
+        <v>3.671</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4514</v>
+        <v>2.8262</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6606</v>
+        <v>0.8448</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4514</v>
+        <v>4.4715</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9869</v>
+        <v>2.325</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6606</v>
+        <v>0.8448</v>
       </c>
       <c r="K10" t="n">
         <v>192</v>
@@ -897,7 +897,7 @@
         <v>77</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6475</v>
+        <v>3.1698</v>
       </c>
       <c r="N10" t="n">
         <v>269</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0952</v>
+        <v>3.3014</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6594</v>
+        <v>0.7033</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7892</v>
+        <v>0.8524</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0952</v>
+        <v>3.3014</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0421</v>
+        <v>3.0723</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0531</v>
+        <v>0.2291</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0421</v>
+        <v>5.3385</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4657</v>
+        <v>2.7758</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0531</v>
+        <v>0.2291</v>
       </c>
       <c r="K11" t="n">
         <v>167</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>2.5188</v>
+        <v>3.0049</v>
       </c>
       <c r="N11" t="n">
         <v>252</v>
@@ -952,216 +952,216 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9335</v>
+        <v>3.2579</v>
       </c>
       <c r="C12" t="n">
-        <v>0.625</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7248</v>
+        <v>0.8328</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9335</v>
+        <v>3.2579</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5844</v>
+        <v>3.2579</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5844</v>
+        <v>3.7941</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0947</v>
+        <v>3.7941</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="L12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.4438</v>
+        <v>3.7941</v>
       </c>
       <c r="N12" t="n">
-        <v>375</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6383</v>
+        <v>3.1488</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5621</v>
+        <v>0.6708</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6072</v>
+        <v>0.7835</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6383</v>
+        <v>3.1488</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6383</v>
+        <v>1.7284</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.4204</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6383</v>
+        <v>1.7284</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6383</v>
+        <v>0.8987000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.4204</v>
       </c>
       <c r="K13" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6383</v>
+        <v>2.3191</v>
       </c>
       <c r="N13" t="n">
-        <v>253</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5722</v>
+        <v>3.0259</v>
       </c>
       <c r="C14" t="n">
-        <v>0.548</v>
+        <v>0.6446</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5809</v>
+        <v>0.728</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5722</v>
+        <v>3.0259</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5722</v>
+        <v>2.7114</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.3145</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5722</v>
+        <v>4.0669</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5939</v>
+        <v>2.1146</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.3145</v>
       </c>
       <c r="K14" t="n">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5939</v>
+        <v>2.4291</v>
       </c>
       <c r="N14" t="n">
-        <v>249</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3694</v>
+        <v>2.8365</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5048</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5001</v>
+        <v>0.6425</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3694</v>
+        <v>2.8365</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3694</v>
+        <v>2.8365</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3694</v>
+        <v>2.8687</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3694</v>
+        <v>2.9867</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3694</v>
+        <v>2.9867</v>
       </c>
       <c r="N15" t="n">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3475</v>
+        <v>2.7571</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5001</v>
+        <v>0.5874</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4913</v>
+        <v>0.6067</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3475</v>
+        <v>2.7571</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3475</v>
+        <v>2.7571</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3475</v>
+        <v>2.7571</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3672</v>
+        <v>2.8705</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3672</v>
+        <v>2.8705</v>
       </c>
       <c r="N16" t="n">
         <v>249</v>
@@ -1182,783 +1182,783 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.1734</v>
+        <v>2.7535</v>
       </c>
       <c r="C17" t="n">
-        <v>0.463</v>
+        <v>0.5866</v>
       </c>
       <c r="D17" t="n">
-        <v>0.422</v>
+        <v>0.6051</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1734</v>
+        <v>2.7535</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1734</v>
+        <v>2.2983</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4552</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1734</v>
+        <v>2.6114</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1734</v>
+        <v>1.3578</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.4552</v>
       </c>
       <c r="K17" t="n">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M17" t="n">
-        <v>2.1734</v>
+        <v>1.813</v>
       </c>
       <c r="N17" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0821</v>
+        <v>2.7466</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4436</v>
+        <v>0.5851</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3856</v>
+        <v>0.6019</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0821</v>
+        <v>2.7466</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0821</v>
+        <v>2.7466</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0821</v>
+        <v>2.7466</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0996</v>
+        <v>2.7466</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0996</v>
+        <v>2.7466</v>
       </c>
       <c r="N18" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0543</v>
+        <v>2.6992</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4377</v>
+        <v>0.575</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3745</v>
+        <v>0.5805</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0543</v>
+        <v>2.6992</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1518</v>
+        <v>2.6992</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9025</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1518</v>
+        <v>2.6992</v>
       </c>
       <c r="I19" t="n">
-        <v>0.123</v>
+        <v>2.6992</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9025</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="L19" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0255</v>
+        <v>2.6992</v>
       </c>
       <c r="N19" t="n">
-        <v>375</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.5022</v>
+        <v>2.3208</v>
       </c>
       <c r="C20" t="n">
-        <v>0.32</v>
+        <v>0.4944</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1546</v>
+        <v>0.4097</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5022</v>
+        <v>2.3208</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1457</v>
+        <v>2.5453</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3565</v>
+        <v>-0.2245</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1457</v>
+        <v>3.4817</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9286</v>
+        <v>1.8103</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3565</v>
+        <v>-0.2245</v>
       </c>
       <c r="K20" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="L20" t="n">
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2851</v>
+        <v>1.5858</v>
       </c>
       <c r="N20" t="n">
-        <v>252</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4768</v>
+        <v>2.0988</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3146</v>
+        <v>0.4471</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1444</v>
+        <v>0.3095</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4768</v>
+        <v>2.0988</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9141</v>
+        <v>2.0988</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4373</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9141</v>
+        <v>2.0988</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5514</v>
+        <v>2.1851</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4373</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1141</v>
+        <v>2.1851</v>
       </c>
       <c r="N21" t="n">
-        <v>375</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Xeppaa</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3324</v>
+        <v>2.0171</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2839</v>
+        <v>0.4297</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.2726</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3324</v>
+        <v>2.0171</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3324</v>
+        <v>3.1034</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1.0863</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3324</v>
+        <v>5.4482</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3324</v>
+        <v>2.8328</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1.0863</v>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3324</v>
+        <v>1.7465</v>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1325</v>
+        <v>1.8648</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2413</v>
+        <v>0.3973</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0073</v>
+        <v>0.2039</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1325</v>
+        <v>1.8648</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8102</v>
+        <v>0.6151</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6777</v>
+        <v>1.2497</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8102</v>
+        <v>0.6151</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2778</v>
+        <v>0.3198</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6777</v>
+        <v>1.2497</v>
       </c>
       <c r="K23" t="n">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="L23" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6001000000000001</v>
+        <v>1.5695</v>
       </c>
       <c r="N23" t="n">
-        <v>415</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1267</v>
+        <v>1.7004</v>
       </c>
       <c r="C24" t="n">
-        <v>0.24</v>
+        <v>0.3623</v>
       </c>
       <c r="D24" t="n">
-        <v>0.005</v>
+        <v>0.1296</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1267</v>
+        <v>1.7004</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3682</v>
+        <v>2.2668</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4949</v>
+        <v>-0.5664</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3682</v>
+        <v>2.5004</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2984</v>
+        <v>1.3001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4949</v>
+        <v>-0.5664</v>
       </c>
       <c r="K24" t="n">
-        <v>290</v>
+        <v>167</v>
       </c>
       <c r="L24" t="n">
         <v>85</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1965</v>
+        <v>0.7337</v>
       </c>
       <c r="N24" t="n">
-        <v>375</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vanity</t>
+          <t>s0m</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3914</v>
+        <v>1.631</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0834</v>
+        <v>0.3475</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.288</v>
+        <v>0.0983</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3914</v>
+        <v>1.631</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3914</v>
+        <v>2.5082</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.8772</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3914</v>
+        <v>3.3511</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3914</v>
+        <v>1.7424</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.8772</v>
       </c>
       <c r="K25" t="n">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3914</v>
+        <v>0.8652</v>
       </c>
       <c r="N25" t="n">
-        <v>100</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Xeppaa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0694</v>
+        <v>0.3132</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3142</v>
+        <v>0.0258</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3256</v>
+        <v>1.4703</v>
       </c>
       <c r="N26" t="n">
-        <v>253</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0571</v>
+        <v>0.176</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3371</v>
+        <v>-0.2652</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>99</v>
+        <v>253</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2681</v>
+        <v>0.8259</v>
       </c>
       <c r="N27" t="n">
-        <v>99</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>s0m</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2037</v>
+        <v>0.7378</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0434</v>
+        <v>0.1572</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3628</v>
+        <v>-0.3049</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2037</v>
+        <v>0.7378</v>
       </c>
       <c r="F28" t="n">
-        <v>1.5443</v>
+        <v>0.7378</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.3406</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.5443</v>
+        <v>0.7378</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2517</v>
+        <v>0.7378</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.3406</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="L28" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.08889999999999998</v>
+        <v>0.7378</v>
       </c>
       <c r="N28" t="n">
-        <v>415</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0377</v>
+        <v>0.6099</v>
       </c>
       <c r="C29" t="n">
-        <v>0.008</v>
+        <v>0.1299</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4289</v>
+        <v>-0.3627</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0377</v>
+        <v>0.6099</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9574</v>
+        <v>1.1113</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.9197</v>
+        <v>-0.5014</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9574</v>
+        <v>1.1113</v>
       </c>
       <c r="I29" t="n">
-        <v>0.776</v>
+        <v>0.5778</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.9197</v>
+        <v>-0.5014</v>
       </c>
       <c r="K29" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="L29" t="n">
         <v>85</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1436999999999999</v>
+        <v>0.07640000000000002</v>
       </c>
       <c r="N29" t="n">
-        <v>252</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>vanity</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.054</v>
+        <v>0.1291</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.3645</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2534</v>
+        <v>0.6059</v>
       </c>
       <c r="N30" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>leaf</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1749</v>
+        <v>-0.0155</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.771</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.821</v>
+        <v>-0.0728</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>leaf</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.4884</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1814</v>
+        <v>-0.1041</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7831</v>
+        <v>-0.8585</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.4884</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1941</v>
+        <v>-0.4884</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6572</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1941</v>
+        <v>-0.4884</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1573</v>
+        <v>-0.4884</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6572</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="L32" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8145</v>
+        <v>-0.4884</v>
       </c>
       <c r="N32" t="n">
-        <v>375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6273</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2302</v>
+        <v>-0.1336</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.9212</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6273</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6273</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6273</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6531</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>99</v>
+        <v>249</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0807</v>
+        <v>-0.6531</v>
       </c>
       <c r="N33" t="n">
-        <v>99</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2349</v>
+        <v>-0.137</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8831</v>
+        <v>-0.9284</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1025</v>
+        <v>-0.6432</v>
       </c>
       <c r="N34" t="n">
         <v>99</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>trk</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2473</v>
+        <v>-0.1394</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9063</v>
+        <v>-0.9334</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1607</v>
+        <v>-0.6542</v>
       </c>
       <c r="N35" t="n">
         <v>99</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2774</v>
+        <v>-0.7286</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2721</v>
+        <v>-0.1552</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9528</v>
+        <v>-0.9669</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2774</v>
+        <v>-0.7286</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2774</v>
+        <v>-0.7286</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2774</v>
+        <v>-0.7286</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2882</v>
+        <v>-0.7286</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2882</v>
+        <v>-0.7286</v>
       </c>
       <c r="N36" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>trk</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2756</v>
+        <v>-0.1799</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9594</v>
+        <v>-1.0192</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2938</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2976</v>
+        <v>-0.1838</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0004</v>
+        <v>-1.0275</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>253</v>
+        <v>100</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3969</v>
+        <v>-0.8628</v>
       </c>
       <c r="N38" t="n">
-        <v>253</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6833</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3586</v>
+        <v>-0.1968</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1145</v>
+        <v>-1.0551</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6833</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6833</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6833</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6975</v>
+        <v>-0.9619</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6975</v>
+        <v>-0.9619</v>
       </c>
       <c r="N39" t="n">
         <v>249</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mCe</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.74</v>
+        <v>-1.1417</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3707</v>
+        <v>-0.2432</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1371</v>
+        <v>-1.1534</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.74</v>
+        <v>-1.1417</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.74</v>
+        <v>-1.2086</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.0669</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.74</v>
+        <v>-1.2086</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.74</v>
+        <v>-0.6284</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.0669</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.74</v>
+        <v>-0.5615</v>
       </c>
       <c r="N40" t="n">
-        <v>100</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>mCe</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.127</v>
+        <v>-1.1604</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4531</v>
+        <v>-0.2472</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2913</v>
+        <v>-1.1619</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.127</v>
+        <v>-1.1604</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.9799</v>
+        <v>-1.1604</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1471</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9799</v>
+        <v>-1.1604</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.6048</v>
+        <v>-1.1604</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1471</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>338</v>
+        <v>100</v>
       </c>
       <c r="L41" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.7519</v>
+        <v>-1.1604</v>
       </c>
       <c r="N41" t="n">
-        <v>415</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9768</v>
+        <v>1.6723</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9768</v>
+        <v>1.6723</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2971</v>
+        <v>1.2148</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2971</v>
+        <v>1.2148</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8696</v>
+        <v>0.9766</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8696</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6258</v>
+        <v>0.7441</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6258</v>
+        <v>0.7441</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2521</v>
+        <v>-0.162</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2521</v>
+        <v>-0.162</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1465</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1594</v>
+        <v>-0.1465</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.75</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3214</v>
+        <v>-0.2512</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3214</v>
+        <v>-0.2512</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4709</v>
+        <v>-0.3246</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4709</v>
+        <v>-0.3246</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5333</v>
+        <v>-0.3616</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5333</v>
+        <v>-0.3616</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.61</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5626</v>
+        <v>-0.3802</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4281</v>
+        <v>1.2744</v>
       </c>
       <c r="J12" t="n">
-        <v>28.562</v>
+        <v>25.488</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4281</v>
+        <v>1.2744</v>
       </c>
       <c r="J13" t="n">
-        <v>28.562</v>
+        <v>25.488</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3526</v>
+        <v>-0.2771</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.052</v>
+        <v>-5.542</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4414</v>
+        <v>-0.3687</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.827999999999999</v>
+        <v>-7.374</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.627</v>
+        <v>-0.5646</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.54</v>
+        <v>-11.292</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5308</v>
+        <v>0.6282</v>
       </c>
       <c r="J17" t="n">
-        <v>10.616</v>
+        <v>12.564</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.96</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0578</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.37</v>
+        <v>-1.156</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2016</v>
+        <v>-0.127</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.032</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.77</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4098</v>
+        <v>-0.2606</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.196</v>
+        <v>-5.212</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4522</v>
+        <v>-0.2898</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.044</v>
+        <v>-5.796</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3783</v>
+        <v>0.3281</v>
       </c>
       <c r="J22" t="n">
-        <v>10.9707</v>
+        <v>9.514900000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3636</v>
+        <v>0.3138</v>
       </c>
       <c r="J23" t="n">
-        <v>10.5444</v>
+        <v>9.100199999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0551</v>
+        <v>0.0321</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5979</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3626</v>
+        <v>-0.2259</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.5154</v>
+        <v>-6.5511</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5415</v>
+        <v>-0.3522</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.7035</v>
+        <v>-10.2138</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.22</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3929</v>
+        <v>0.3263</v>
       </c>
       <c r="J27" t="n">
-        <v>11.3941</v>
+        <v>9.4627</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3195</v>
+        <v>0.2619</v>
       </c>
       <c r="J28" t="n">
-        <v>9.265499999999999</v>
+        <v>7.5951</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.03</v>
+        <v>0.0419</v>
       </c>
       <c r="J29" t="n">
-        <v>0.87</v>
+        <v>1.2151</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.0255</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.9169</v>
+        <v>-0.7395</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2763</v>
+        <v>-0.1624</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.012700000000001</v>
+        <v>-4.7096</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5377</v>
+        <v>0.4884</v>
       </c>
       <c r="J32" t="n">
-        <v>15.5933</v>
+        <v>14.1636</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3965</v>
+        <v>0.3489</v>
       </c>
       <c r="J33" t="n">
-        <v>11.4985</v>
+        <v>10.1181</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2702</v>
+        <v>0.229</v>
       </c>
       <c r="J34" t="n">
-        <v>7.8358</v>
+        <v>6.641</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2702</v>
+        <v>-0.229</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.8358</v>
+        <v>-6.641</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7893</v>
+        <v>-0.7492</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.8897</v>
+        <v>-21.7268</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4763</v>
+        <v>0.569</v>
       </c>
       <c r="J37" t="n">
-        <v>13.8127</v>
+        <v>16.501</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3054</v>
+        <v>0.3593</v>
       </c>
       <c r="J38" t="n">
-        <v>8.8566</v>
+        <v>10.4197</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1001</v>
+        <v>0.1478</v>
       </c>
       <c r="J39" t="n">
-        <v>2.9029</v>
+        <v>4.2862</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0801</v>
+        <v>0.1257</v>
       </c>
       <c r="J40" t="n">
-        <v>2.3229</v>
+        <v>3.6453</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2529</v>
+        <v>-0.1445</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.3341</v>
+        <v>-4.1905</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.1</v>
       </c>
       <c r="I42" t="n">
-        <v>2.0593</v>
+        <v>1.8168</v>
       </c>
       <c r="J42" t="n">
-        <v>51.4825</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7008</v>
+        <v>0.788</v>
       </c>
       <c r="J43" t="n">
-        <v>17.52</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.28</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6282</v>
+        <v>0.7207</v>
       </c>
       <c r="J44" t="n">
-        <v>15.705</v>
+        <v>18.0175</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.151</v>
+        <v>0.2394</v>
       </c>
       <c r="J45" t="n">
-        <v>3.775</v>
+        <v>5.985</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3378</v>
+        <v>-0.2519</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.445</v>
+        <v>-6.2975</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1783</v>
+        <v>0.1612</v>
       </c>
       <c r="J47" t="n">
-        <v>4.4575</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0838</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.1875</v>
+        <v>-2.095</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1249</v>
+        <v>-0.1073</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.1225</v>
+        <v>-2.6825</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3345</v>
+        <v>-0.2202</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.362500000000001</v>
+        <v>-5.505</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6816</v>
+        <v>-0.4574</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.04</v>
+        <v>-11.435</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.87</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1331</v>
+        <v>-0.1274</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.0613</v>
+        <v>-2.9302</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2803</v>
+        <v>-0.2239</v>
       </c>
       <c r="J53" t="n">
-        <v>-6.4469</v>
+        <v>-5.1497</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2803</v>
+        <v>-0.2239</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.4469</v>
+        <v>-5.1497</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.65</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3451</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.7208</v>
+        <v>-7.9373</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.4853</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.4726</v>
+        <v>-11.1619</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1618</v>
+        <v>1.1211</v>
       </c>
       <c r="J57" t="n">
-        <v>26.7214</v>
+        <v>25.7853</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.39</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9517</v>
       </c>
       <c r="J58" t="n">
-        <v>20.6931</v>
+        <v>21.8891</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.33</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7382</v>
+        <v>0.8288</v>
       </c>
       <c r="J59" t="n">
-        <v>16.9786</v>
+        <v>19.0624</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6901</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>15.8723</v>
+        <v>18.0504</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.29</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6428</v>
+        <v>0.74</v>
       </c>
       <c r="J61" t="n">
-        <v>14.7844</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.3864</v>
+        <v>0.4413</v>
       </c>
       <c r="J62" t="n">
-        <v>11.592</v>
+        <v>13.239</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2964</v>
+        <v>0.328</v>
       </c>
       <c r="J63" t="n">
-        <v>8.891999999999999</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0674</v>
       </c>
       <c r="J64" t="n">
-        <v>2.172</v>
+        <v>2.022</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1899</v>
+        <v>-0.1108</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.697</v>
+        <v>-3.324</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.68</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5447</v>
+        <v>-0.3542</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.341</v>
+        <v>-10.626</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.54</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3315</v>
+        <v>1.2093</v>
       </c>
       <c r="J67" t="n">
-        <v>39.945</v>
+        <v>36.279</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4691</v>
+        <v>0.4722</v>
       </c>
       <c r="J68" t="n">
-        <v>14.073</v>
+        <v>14.166</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.003</v>
+        <v>0.0625</v>
       </c>
       <c r="J69" t="n">
-        <v>0.09</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.003</v>
+        <v>0.0625</v>
       </c>
       <c r="J70" t="n">
-        <v>0.09</v>
+        <v>1.875</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.96</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2737</v>
+        <v>-0.2015</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.211</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6327</v>
+        <v>0.7711</v>
       </c>
       <c r="J72" t="n">
-        <v>26.5734</v>
+        <v>32.3862</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3252</v>
+        <v>0.3718</v>
       </c>
       <c r="J73" t="n">
-        <v>13.6584</v>
+        <v>15.6156</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.99</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0601</v>
+        <v>-0.024</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.5242</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.86</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3037</v>
+        <v>-0.182</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.7554</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4204</v>
+        <v>-0.2635</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.6568</v>
+        <v>-11.067</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0029</v>
+        <v>0.9786</v>
       </c>
       <c r="J77" t="n">
-        <v>42.1218</v>
+        <v>41.1012</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.498</v>
+        <v>0.4662</v>
       </c>
       <c r="J78" t="n">
-        <v>20.916</v>
+        <v>19.5804</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3199</v>
+        <v>0.3021</v>
       </c>
       <c r="J79" t="n">
-        <v>13.4358</v>
+        <v>12.6882</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2016</v>
+        <v>-0.1458</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.4672</v>
+        <v>-6.1236</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8328</v>
+        <v>-0.7921</v>
       </c>
       <c r="J81" t="n">
-        <v>-34.9776</v>
+        <v>-33.2682</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5196</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="J82" t="n">
-        <v>15.0684</v>
+        <v>17.8756</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4933</v>
+        <v>0.5815</v>
       </c>
       <c r="J83" t="n">
-        <v>14.3057</v>
+        <v>16.8635</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1934</v>
+        <v>-0.1119</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.6086</v>
+        <v>-3.2451</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3696</v>
+        <v>-0.2292</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.7184</v>
+        <v>-6.6468</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5206</v>
+        <v>-0.3365</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.0974</v>
+        <v>-9.7585</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9241</v>
+        <v>0.9105</v>
       </c>
       <c r="J87" t="n">
-        <v>26.7989</v>
+        <v>26.4045</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8567</v>
+        <v>0.8408</v>
       </c>
       <c r="J88" t="n">
-        <v>24.8443</v>
+        <v>24.3832</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.23</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6666</v>
+        <v>0.6493</v>
       </c>
       <c r="J89" t="n">
-        <v>19.3314</v>
+        <v>18.8297</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0926</v>
+        <v>-0.0296</v>
       </c>
       <c r="J90" t="n">
-        <v>-2.6854</v>
+        <v>-0.8584000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8275</v>
+        <v>-0.784</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.9975</v>
+        <v>-22.736</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3654</v>
+        <v>0.4076</v>
       </c>
       <c r="J92" t="n">
-        <v>9.500400000000001</v>
+        <v>10.5976</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.97</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.1414</v>
+        <v>-1.1466</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0439</v>
+        <v>-0.0441</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.1414</v>
+        <v>-1.1466</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2533</v>
+        <v>-0.1587</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.5858</v>
+        <v>-4.1262</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.66</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5585</v>
+        <v>-0.3655</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.521</v>
+        <v>-9.503</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2749</v>
+        <v>1.1738</v>
       </c>
       <c r="J97" t="n">
-        <v>33.1474</v>
+        <v>30.5188</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3961</v>
+        <v>0.4422</v>
       </c>
       <c r="J98" t="n">
-        <v>10.2986</v>
+        <v>11.4972</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2793</v>
+        <v>0.3363</v>
       </c>
       <c r="J99" t="n">
-        <v>7.2618</v>
+        <v>8.7438</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1274</v>
+        <v>0.1905</v>
       </c>
       <c r="J100" t="n">
-        <v>3.3124</v>
+        <v>4.953</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.0257</v>
+        <v>0.091</v>
       </c>
       <c r="J101" t="n">
-        <v>0.6682</v>
+        <v>2.366</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9492</v>
+        <v>0.8808</v>
       </c>
       <c r="J102" t="n">
-        <v>16.1364</v>
+        <v>14.9736</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.75</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8872</v>
+        <v>0.8232</v>
       </c>
       <c r="J103" t="n">
-        <v>15.0824</v>
+        <v>13.9944</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.63</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7564</v>
+        <v>0.7069</v>
       </c>
       <c r="J104" t="n">
-        <v>12.8588</v>
+        <v>12.0173</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.59</v>
       </c>
       <c r="I105" t="n">
-        <v>0.7095</v>
+        <v>0.668</v>
       </c>
       <c r="J105" t="n">
-        <v>12.0615</v>
+        <v>11.356</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.2522</v>
+        <v>-0.1368</v>
       </c>
       <c r="J106" t="n">
-        <v>-4.2874</v>
+        <v>-2.3256</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.82</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.198</v>
+        <v>-0.1745</v>
       </c>
       <c r="J107" t="n">
-        <v>-3.366</v>
+        <v>-2.9665</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.3259</v>
+        <v>-0.2574</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.5403</v>
+        <v>-4.3758</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3259</v>
+        <v>-0.2574</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.5403</v>
+        <v>-4.3758</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.65</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4918</v>
+        <v>-0.34</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.3606</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7589</v>
+        <v>-0.5173</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.9013</v>
+        <v>-8.7941</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.23</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4407</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>11.4582</v>
+        <v>13.2236</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.18</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3693</v>
+        <v>0.4156</v>
       </c>
       <c r="J113" t="n">
-        <v>9.601800000000001</v>
+        <v>10.8056</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2477</v>
+        <v>-0.1514</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.4402</v>
+        <v>-3.9364</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4305</v>
+        <v>-0.2736</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.193</v>
+        <v>-7.1136</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.74</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4583</v>
+        <v>-0.293</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.9158</v>
+        <v>-7.618</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3133</v>
+        <v>1.1989</v>
       </c>
       <c r="J117" t="n">
-        <v>34.1458</v>
+        <v>31.1714</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.31</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8289</v>
+        <v>0.8237</v>
       </c>
       <c r="J118" t="n">
-        <v>21.5514</v>
+        <v>21.4162</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.14</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3653</v>
+        <v>0.4161</v>
       </c>
       <c r="J119" t="n">
-        <v>9.4978</v>
+        <v>10.8186</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.158</v>
+        <v>0.2207</v>
       </c>
       <c r="J120" t="n">
-        <v>4.108</v>
+        <v>5.7382</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6758</v>
+        <v>-0.6172</v>
       </c>
       <c r="J121" t="n">
-        <v>-17.5708</v>
+        <v>-16.0472</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>1.068</v>
+        <v>0.7622</v>
       </c>
       <c r="J122" t="n">
-        <v>32.04</v>
+        <v>22.866</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4133</v>
+        <v>0.3747</v>
       </c>
       <c r="J123" t="n">
-        <v>12.399</v>
+        <v>11.241</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2037</v>
+        <v>0.2382</v>
       </c>
       <c r="J124" t="n">
-        <v>6.111</v>
+        <v>7.146</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2566</v>
+        <v>-0.1909</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.698</v>
+        <v>-5.727</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3228</v>
+        <v>-0.2564</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.683999999999999</v>
+        <v>-7.692</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.46</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7127</v>
+        <v>0.6563</v>
       </c>
       <c r="J127" t="n">
-        <v>21.381</v>
+        <v>19.689</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0985</v>
+        <v>-0.0513</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.955</v>
+        <v>-1.539</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1974</v>
+        <v>-0.1132</v>
       </c>
       <c r="J129" t="n">
-        <v>-5.922</v>
+        <v>-3.396</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2322</v>
+        <v>-0.1358</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.966</v>
+        <v>-4.074</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3578</v>
+        <v>-0.2205</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.734</v>
+        <v>-6.615</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.4679</v>
+        <v>1.0272</v>
       </c>
       <c r="J132" t="n">
-        <v>38.1654</v>
+        <v>26.7072</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4581</v>
+        <v>0.4271</v>
       </c>
       <c r="J133" t="n">
-        <v>11.9106</v>
+        <v>11.1046</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3961</v>
+        <v>0.3978</v>
       </c>
       <c r="J134" t="n">
-        <v>10.2986</v>
+        <v>10.3428</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1898</v>
+        <v>0.251</v>
       </c>
       <c r="J135" t="n">
-        <v>4.9348</v>
+        <v>6.526</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6006</v>
+        <v>-0.5367</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.6156</v>
+        <v>-13.9542</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2689</v>
+        <v>0.2854</v>
       </c>
       <c r="J137" t="n">
-        <v>6.9914</v>
+        <v>7.4204</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1999</v>
+        <v>0.2003</v>
       </c>
       <c r="J138" t="n">
-        <v>5.1974</v>
+        <v>5.2078</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.93</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1432</v>
+        <v>-0.094</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7232</v>
+        <v>-2.444</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3368</v>
+        <v>-0.2112</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.7568</v>
+        <v>-5.4912</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4392</v>
+        <v>-0.2806</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.4192</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4496</v>
+        <v>0.4444</v>
       </c>
       <c r="J142" t="n">
-        <v>12.5888</v>
+        <v>12.4432</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3643</v>
+        <v>0.3792</v>
       </c>
       <c r="J143" t="n">
-        <v>10.2004</v>
+        <v>10.6176</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3321</v>
+        <v>-0.2053</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.2988</v>
+        <v>-5.7484</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.82</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3472</v>
+        <v>-0.2155</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.7216</v>
+        <v>-6.034</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3913</v>
+        <v>-0.2457</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.9564</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4755</v>
+        <v>1.0313</v>
       </c>
       <c r="J147" t="n">
-        <v>41.314</v>
+        <v>28.8764</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.19</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5895</v>
+        <v>0.4685</v>
       </c>
       <c r="J148" t="n">
-        <v>16.506</v>
+        <v>13.118</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2141</v>
+        <v>-0.1522</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.9948</v>
+        <v>-4.2616</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.408</v>
+        <v>-0.3441</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.424</v>
+        <v>-9.6348</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7935</v>
+        <v>-0.7484</v>
       </c>
       <c r="J151" t="n">
-        <v>-22.218</v>
+        <v>-20.9552</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5616</v>
+        <v>0.4249</v>
       </c>
       <c r="J152" t="n">
-        <v>16.2864</v>
+        <v>12.3221</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.431</v>
+        <v>0.3559</v>
       </c>
       <c r="J153" t="n">
-        <v>12.499</v>
+        <v>10.3211</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2816</v>
+        <v>0.2491</v>
       </c>
       <c r="J154" t="n">
-        <v>8.166399999999999</v>
+        <v>7.2239</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.09</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1343</v>
+        <v>0.1436</v>
       </c>
       <c r="J155" t="n">
-        <v>3.8947</v>
+        <v>4.1644</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3412</v>
+        <v>-0.2042</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.8948</v>
+        <v>-5.9218</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3783</v>
+        <v>0.3258</v>
       </c>
       <c r="J157" t="n">
-        <v>10.9707</v>
+        <v>9.4482</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1235</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.5815</v>
+        <v>-2.1286</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.92</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.183</v>
+        <v>-0.1089</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.307</v>
+        <v>-3.1581</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.91</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2013</v>
+        <v>-0.1202</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.8377</v>
+        <v>-3.4858</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2191</v>
+        <v>-0.1314</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.3539</v>
+        <v>-3.8106</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.23</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4573</v>
+        <v>0.4483</v>
       </c>
       <c r="J162" t="n">
-        <v>12.8044</v>
+        <v>12.5524</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3101</v>
+        <v>0.3312</v>
       </c>
       <c r="J163" t="n">
-        <v>8.6828</v>
+        <v>9.2736</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2464</v>
+        <v>-0.1569</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.8992</v>
+        <v>-4.3932</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3747</v>
+        <v>-0.2383</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.4916</v>
+        <v>-6.6724</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7052</v>
+        <v>-0.4745</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.7456</v>
+        <v>-13.286</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.25</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6867</v>
+        <v>0.5401</v>
       </c>
       <c r="J167" t="n">
-        <v>19.2276</v>
+        <v>15.1228</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.61</v>
+        <v>0.498</v>
       </c>
       <c r="J168" t="n">
-        <v>17.08</v>
+        <v>13.944</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5271</v>
+        <v>0.4554</v>
       </c>
       <c r="J169" t="n">
-        <v>14.7588</v>
+        <v>12.7512</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.13</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3376</v>
+        <v>0.3672</v>
       </c>
       <c r="J170" t="n">
-        <v>9.4528</v>
+        <v>10.2816</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1898</v>
+        <v>0.251</v>
       </c>
       <c r="J171" t="n">
-        <v>5.3144</v>
+        <v>7.028</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0017</v>
+        <v>-0.0355</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.0357</v>
+        <v>-0.7455000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.82</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2276</v>
+        <v>-0.1873</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.7796</v>
+        <v>-3.9333</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2441</v>
+        <v>-0.1977</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.1261</v>
+        <v>-4.1517</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2606</v>
+        <v>-0.2079</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.4726</v>
+        <v>-4.3659</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.32</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9386</v>
+        <v>-0.6553</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.7106</v>
+        <v>-13.7613</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8112</v>
       </c>
       <c r="J177" t="n">
-        <v>18.5766</v>
+        <v>17.0352</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7992</v>
+        <v>0.7312</v>
       </c>
       <c r="J178" t="n">
-        <v>16.7832</v>
+        <v>15.3552</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.61</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7661</v>
+        <v>0.701</v>
       </c>
       <c r="J179" t="n">
-        <v>16.0881</v>
+        <v>14.721</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3546</v>
+        <v>0.3664</v>
       </c>
       <c r="J180" t="n">
-        <v>7.4466</v>
+        <v>7.6944</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.86</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.363</v>
+        <v>-0.2172</v>
       </c>
       <c r="J181" t="n">
-        <v>-7.623</v>
+        <v>-4.5612</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.2319</v>
+        <v>1.1526</v>
       </c>
       <c r="J182" t="n">
-        <v>35.7251</v>
+        <v>33.4254</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.36</v>
       </c>
       <c r="I183" t="n">
-        <v>0.8948</v>
+        <v>0.9117</v>
       </c>
       <c r="J183" t="n">
-        <v>25.9492</v>
+        <v>26.4393</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5541</v>
+        <v>0.6212</v>
       </c>
       <c r="J184" t="n">
-        <v>16.0689</v>
+        <v>18.0148</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3184</v>
+        <v>0.3973</v>
       </c>
       <c r="J185" t="n">
-        <v>9.233599999999999</v>
+        <v>11.5217</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0912</v>
+        <v>0.1691</v>
       </c>
       <c r="J186" t="n">
-        <v>2.6448</v>
+        <v>4.9039</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.02</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1293</v>
+        <v>0.1029</v>
       </c>
       <c r="J187" t="n">
-        <v>3.7497</v>
+        <v>2.9841</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.92</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.113</v>
+        <v>-0.0978</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.277</v>
+        <v>-2.8362</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.113</v>
+        <v>-0.0978</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.277</v>
+        <v>-2.8362</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1318</v>
+        <v>-0.1093</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.8222</v>
+        <v>-3.1697</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7088</v>
+        <v>-0.4775</v>
       </c>
       <c r="J191" t="n">
-        <v>-20.5552</v>
+        <v>-13.8475</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.59</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4001</v>
+        <v>1.2567</v>
       </c>
       <c r="J192" t="n">
-        <v>40.6029</v>
+        <v>36.4443</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7942</v>
+        <v>0.7946</v>
       </c>
       <c r="J193" t="n">
-        <v>23.0318</v>
+        <v>23.0434</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.12</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2957</v>
+        <v>0.3587</v>
       </c>
       <c r="J194" t="n">
-        <v>8.5753</v>
+        <v>10.4023</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.179</v>
+        <v>0.2458</v>
       </c>
       <c r="J195" t="n">
-        <v>5.191</v>
+        <v>7.1282</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.89</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5023</v>
+        <v>-0.4312</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.5667</v>
+        <v>-12.5048</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3095</v>
+        <v>0.3391</v>
       </c>
       <c r="J197" t="n">
-        <v>8.9755</v>
+        <v>9.8339</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1541</v>
+        <v>0.1494</v>
       </c>
       <c r="J198" t="n">
-        <v>4.4689</v>
+        <v>4.3326</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1338</v>
+        <v>0.1257</v>
       </c>
       <c r="J199" t="n">
-        <v>3.8802</v>
+        <v>3.6453</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1124</v>
+        <v>0.101</v>
       </c>
       <c r="J200" t="n">
-        <v>3.2596</v>
+        <v>2.929</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7352</v>
+        <v>-0.4973</v>
       </c>
       <c r="J201" t="n">
-        <v>-21.3208</v>
+        <v>-14.4217</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.4625</v>
+        <v>0.5344</v>
       </c>
       <c r="J202" t="n">
-        <v>11.1</v>
+        <v>12.8256</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0189</v>
+        <v>-0.0098</v>
       </c>
       <c r="J203" t="n">
-        <v>0.4536</v>
+        <v>-0.2352</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3239</v>
+        <v>-0.2066</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.7736</v>
+        <v>-4.9584</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4291</v>
+        <v>-0.2758</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.2984</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4988</v>
+        <v>-0.3239</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.9712</v>
+        <v>-7.7736</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.5172</v>
+        <v>1.3369</v>
       </c>
       <c r="J207" t="n">
-        <v>36.4128</v>
+        <v>32.0856</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.2499</v>
+        <v>1.1643</v>
       </c>
       <c r="J208" t="n">
-        <v>29.9976</v>
+        <v>27.9432</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5513</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>13.2312</v>
+        <v>14.892</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2037</v>
+        <v>-0.1198</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.8888</v>
+        <v>-2.8752</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4668</v>
+        <v>-0.3902</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.2032</v>
+        <v>-9.364800000000001</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4143</v>
+        <v>0.4707</v>
       </c>
       <c r="J212" t="n">
-        <v>10.7718</v>
+        <v>12.2382</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>0.0119</v>
+        <v>-0.0121</v>
       </c>
       <c r="J213" t="n">
-        <v>0.3094</v>
+        <v>-0.3146</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0371</v>
+        <v>-0.0424</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.9646</v>
+        <v>-1.1024</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4192</v>
+        <v>-0.2681</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.8992</v>
+        <v>-6.9706</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5686</v>
+        <v>-0.3732</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.7836</v>
+        <v>-9.703200000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9211</v>
+        <v>0.9248</v>
       </c>
       <c r="J217" t="n">
-        <v>23.9486</v>
+        <v>24.0448</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.34</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8763</v>
+        <v>0.8807</v>
       </c>
       <c r="J218" t="n">
-        <v>22.7838</v>
+        <v>22.8982</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.24</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6333</v>
+        <v>0.6513</v>
       </c>
       <c r="J219" t="n">
-        <v>16.4658</v>
+        <v>16.9338</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.09</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2005</v>
+        <v>0.2707</v>
       </c>
       <c r="J220" t="n">
-        <v>5.213</v>
+        <v>7.0382</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.04</v>
       </c>
       <c r="I221" t="n">
-        <v>0.0444</v>
+        <v>0.1158</v>
       </c>
       <c r="J221" t="n">
-        <v>1.1544</v>
+        <v>3.0108</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3289</v>
+        <v>1.2214</v>
       </c>
       <c r="J222" t="n">
-        <v>30.5647</v>
+        <v>28.0922</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.54</v>
       </c>
       <c r="I223" t="n">
-        <v>1.2309</v>
+        <v>1.1607</v>
       </c>
       <c r="J223" t="n">
-        <v>28.3107</v>
+        <v>26.6961</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.5324</v>
+        <v>0.6279</v>
       </c>
       <c r="J224" t="n">
-        <v>12.2452</v>
+        <v>14.4417</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5083</v>
+        <v>0.6041</v>
       </c>
       <c r="J225" t="n">
-        <v>11.6909</v>
+        <v>13.8943</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2851</v>
+        <v>0.3778</v>
       </c>
       <c r="J226" t="n">
-        <v>6.5573</v>
+        <v>8.689399999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11469,10 +11469,10 @@
         <v>0.91</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1043</v>
+        <v>-0.1</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.3989</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3621</v>
+        <v>-0.244</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.3283</v>
+        <v>-5.612</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.66</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5272</v>
+        <v>-0.3487</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.1256</v>
+        <v>-8.020099999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6082</v>
+        <v>-0.405</v>
       </c>
       <c r="J231" t="n">
-        <v>-13.9886</v>
+        <v>-9.315</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.7</v>
       </c>
       <c r="I232" t="n">
-        <v>1.555</v>
+        <v>1.3636</v>
       </c>
       <c r="J232" t="n">
-        <v>34.21</v>
+        <v>29.9992</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>1.444</v>
+        <v>1.2912</v>
       </c>
       <c r="J233" t="n">
-        <v>31.768</v>
+        <v>28.4064</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.4292</v>
+        <v>0.516</v>
       </c>
       <c r="J234" t="n">
-        <v>9.442399999999999</v>
+        <v>11.352</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0132</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>0.2904</v>
+        <v>2.0724</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3589</v>
+        <v>-0.2754</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.8958</v>
+        <v>-6.0588</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2799</v>
+        <v>0.2888</v>
       </c>
       <c r="J237" t="n">
-        <v>6.1578</v>
+        <v>6.3536</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.0576</v>
+        <v>-0.0673</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.2672</v>
+        <v>-1.4806</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2207</v>
+        <v>-0.1689</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.8554</v>
+        <v>-3.7158</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.372</v>
+        <v>-0.2465</v>
       </c>
       <c r="J240" t="n">
-        <v>-8.183999999999999</v>
+        <v>-5.423</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.46</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7867</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.3074</v>
+        <v>-11.8096</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.02</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1146</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>3.3234</v>
+        <v>2.6332</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.96</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0506</v>
+        <v>-0.0535</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.4674</v>
+        <v>-1.5515</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0919</v>
+        <v>-0.0788</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.6651</v>
+        <v>-2.2852</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.87</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2384</v>
+        <v>-0.1553</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.9136</v>
+        <v>-4.5037</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5118</v>
+        <v>-0.3332</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.8422</v>
+        <v>-9.662800000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3858</v>
+        <v>1.2511</v>
       </c>
       <c r="J247" t="n">
-        <v>40.1882</v>
+        <v>36.2819</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.57</v>
       </c>
       <c r="I248" t="n">
-        <v>1.3282</v>
+        <v>1.214</v>
       </c>
       <c r="J248" t="n">
-        <v>38.5178</v>
+        <v>35.206</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4476</v>
+        <v>0.5241</v>
       </c>
       <c r="J249" t="n">
-        <v>12.9804</v>
+        <v>15.1989</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2899</v>
+        <v>0.3697</v>
       </c>
       <c r="J250" t="n">
-        <v>8.4071</v>
+        <v>10.7213</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6491</v>
+        <v>-0.5855</v>
       </c>
       <c r="J251" t="n">
-        <v>-18.8239</v>
+        <v>-16.9795</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.91</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0501</v>
+        <v>-0.0712</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.1022</v>
+        <v>-1.5664</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.76</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.296</v>
+        <v>-0.2382</v>
       </c>
       <c r="J253" t="n">
-        <v>-6.512</v>
+        <v>-5.2404</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.68</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4413</v>
+        <v>-0.3136</v>
       </c>
       <c r="J254" t="n">
-        <v>-9.708600000000001</v>
+        <v>-6.8992</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.58</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.4056</v>
       </c>
       <c r="J255" t="n">
-        <v>-13.1846</v>
+        <v>-8.9232</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.5</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7081</v>
+        <v>-0.4805</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.5782</v>
+        <v>-10.571</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.04</v>
       </c>
       <c r="I257" t="n">
-        <v>2.0168</v>
+        <v>1.7264</v>
       </c>
       <c r="J257" t="n">
-        <v>44.3696</v>
+        <v>37.9808</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.42</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9194</v>
+        <v>0.9972</v>
       </c>
       <c r="J258" t="n">
-        <v>20.2268</v>
+        <v>21.9384</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.39</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8447</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>18.5834</v>
+        <v>20.7922</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.2615</v>
+        <v>0.3613</v>
       </c>
       <c r="J260" t="n">
-        <v>5.753</v>
+        <v>7.9486</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.13</v>
       </c>
       <c r="I261" t="n">
-        <v>0.2359</v>
+        <v>0.3345</v>
       </c>
       <c r="J261" t="n">
-        <v>5.1898</v>
+        <v>7.359</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.2942</v>
+        <v>0.3144</v>
       </c>
       <c r="J262" t="n">
-        <v>7.0608</v>
+        <v>7.5456</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.05</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1717</v>
+        <v>0.162</v>
       </c>
       <c r="J263" t="n">
-        <v>4.1208</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.3444</v>
+        <v>-0.2184</v>
       </c>
       <c r="J264" t="n">
-        <v>-8.265599999999999</v>
+        <v>-5.2416</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.8</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.3597</v>
+        <v>-0.2284</v>
       </c>
       <c r="J265" t="n">
-        <v>-8.6328</v>
+        <v>-5.4816</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3896</v>
+        <v>-0.2482</v>
       </c>
       <c r="J266" t="n">
-        <v>-9.3504</v>
+        <v>-5.9568</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.49</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1561</v>
+        <v>1.1087</v>
       </c>
       <c r="J267" t="n">
-        <v>27.7464</v>
+        <v>26.6088</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.48</v>
       </c>
       <c r="I268" t="n">
-        <v>1.1357</v>
+        <v>1.0961</v>
       </c>
       <c r="J268" t="n">
-        <v>27.2568</v>
+        <v>26.3064</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.35</v>
       </c>
       <c r="I269" t="n">
-        <v>0.8529</v>
+        <v>0.8827</v>
       </c>
       <c r="J269" t="n">
-        <v>20.4696</v>
+        <v>21.1848</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.3312</v>
+        <v>0.4163</v>
       </c>
       <c r="J270" t="n">
-        <v>7.9488</v>
+        <v>9.991199999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.1541</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J271" t="n">
-        <v>-3.6984</v>
+        <v>-1.7136</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.31</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5387</v>
+        <v>0.6409</v>
       </c>
       <c r="J272" t="n">
-        <v>13.4675</v>
+        <v>16.0225</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.3892</v>
+        <v>0.444</v>
       </c>
       <c r="J273" t="n">
-        <v>9.73</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.92</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1869</v>
+        <v>-0.11</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.6725</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.82</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3504</v>
+        <v>-0.217</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.76</v>
+        <v>-5.425</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5561</v>
+        <v>-0.3627</v>
       </c>
       <c r="J276" t="n">
-        <v>-13.9025</v>
+        <v>-9.067500000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0648</v>
+        <v>1.0322</v>
       </c>
       <c r="J277" t="n">
-        <v>26.62</v>
+        <v>25.805</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6062</v>
       </c>
       <c r="J278" t="n">
-        <v>15.7125</v>
+        <v>15.155</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3767</v>
+        <v>0.3754</v>
       </c>
       <c r="J279" t="n">
-        <v>9.4175</v>
+        <v>9.385</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1424</v>
+        <v>-0.0793</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.56</v>
+        <v>-1.9825</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6801</v>
+        <v>-0.6253</v>
       </c>
       <c r="J281" t="n">
-        <v>-17.0025</v>
+        <v>-15.6325</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2441</v>
+        <v>0.2427</v>
       </c>
       <c r="J282" t="n">
-        <v>5.8584</v>
+        <v>5.8248</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.95</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.039</v>
+        <v>-0.0549</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-1.3176</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.79</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3402</v>
+        <v>-0.2274</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.1648</v>
+        <v>-5.4576</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.74</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4194</v>
+        <v>-0.2757</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.0656</v>
+        <v>-6.6168</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6521</v>
+        <v>-0.436</v>
       </c>
       <c r="J286" t="n">
-        <v>-15.6504</v>
+        <v>-10.464</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0817</v>
+        <v>1.0562</v>
       </c>
       <c r="J287" t="n">
-        <v>25.9608</v>
+        <v>25.3488</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8177</v>
+        <v>0.8296</v>
       </c>
       <c r="J288" t="n">
-        <v>19.6248</v>
+        <v>19.9104</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.24</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6478</v>
       </c>
       <c r="J289" t="n">
-        <v>14.6976</v>
+        <v>15.5472</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3033</v>
+        <v>0.3766</v>
       </c>
       <c r="J290" t="n">
-        <v>7.2792</v>
+        <v>9.038399999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1435</v>
       </c>
       <c r="J291" t="n">
-        <v>1.6584</v>
+        <v>3.444</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5841</v>
+        <v>0.707</v>
       </c>
       <c r="J292" t="n">
-        <v>12.8502</v>
+        <v>15.554</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1782</v>
+        <v>0.1572</v>
       </c>
       <c r="J293" t="n">
-        <v>3.9204</v>
+        <v>3.4584</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4077</v>
+        <v>-0.2719</v>
       </c>
       <c r="J294" t="n">
-        <v>-8.9694</v>
+        <v>-5.9818</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.7824</v>
+        <v>-0.5336</v>
       </c>
       <c r="J295" t="n">
-        <v>-17.2128</v>
+        <v>-11.7392</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.46</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.7824</v>
+        <v>-0.5336</v>
       </c>
       <c r="J296" t="n">
-        <v>-17.2128</v>
+        <v>-11.7392</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.62</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3972</v>
+        <v>1.2625</v>
       </c>
       <c r="J297" t="n">
-        <v>30.7384</v>
+        <v>27.775</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.55</v>
       </c>
       <c r="I298" t="n">
-        <v>1.262</v>
+        <v>1.1773</v>
       </c>
       <c r="J298" t="n">
-        <v>27.764</v>
+        <v>25.9006</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.24</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5436</v>
+        <v>0.6328</v>
       </c>
       <c r="J299" t="n">
-        <v>11.9592</v>
+        <v>13.9216</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3451</v>
+        <v>0.4356</v>
       </c>
       <c r="J300" t="n">
-        <v>7.5922</v>
+        <v>9.5832</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.05</v>
       </c>
       <c r="I301" t="n">
-        <v>0.0396</v>
+        <v>0.1227</v>
       </c>
       <c r="J301" t="n">
-        <v>0.8712</v>
+        <v>2.6994</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3596</v>
+        <v>0.4016</v>
       </c>
       <c r="J302" t="n">
-        <v>10.0688</v>
+        <v>11.2448</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.14</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3139</v>
+        <v>0.3432</v>
       </c>
       <c r="J303" t="n">
-        <v>8.789199999999999</v>
+        <v>9.6096</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0018</v>
+        <v>-0.0159</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.0504</v>
+        <v>-0.4452</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3238</v>
+        <v>-0.202</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.0664</v>
+        <v>-5.656</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.59</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6495</v>
+        <v>-0.4324</v>
       </c>
       <c r="J306" t="n">
-        <v>-18.186</v>
+        <v>-12.1072</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.58</v>
       </c>
       <c r="I307" t="n">
-        <v>1.3928</v>
+        <v>1.251</v>
       </c>
       <c r="J307" t="n">
-        <v>38.9984</v>
+        <v>35.028</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0933</v>
+        <v>1.0572</v>
       </c>
       <c r="J308" t="n">
-        <v>30.6124</v>
+        <v>29.6016</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.16</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4281</v>
+        <v>0.4677</v>
       </c>
       <c r="J309" t="n">
-        <v>11.9868</v>
+        <v>13.0956</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.88</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.522</v>
+        <v>-0.4535</v>
       </c>
       <c r="J310" t="n">
-        <v>-14.616</v>
+        <v>-12.698</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6989</v>
+        <v>-0.6424</v>
       </c>
       <c r="J311" t="n">
-        <v>-19.5692</v>
+        <v>-17.9872</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4571</v>
+        <v>0.5367</v>
       </c>
       <c r="J312" t="n">
-        <v>12.7988</v>
+        <v>15.0276</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.23</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4158</v>
+        <v>0.4836</v>
       </c>
       <c r="J313" t="n">
-        <v>11.6424</v>
+        <v>13.5408</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.02</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0435</v>
+        <v>0.0626</v>
       </c>
       <c r="J314" t="n">
-        <v>1.218</v>
+        <v>1.7528</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3467</v>
+        <v>-0.2121</v>
       </c>
       <c r="J315" t="n">
-        <v>-9.707599999999999</v>
+        <v>-5.9388</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3759</v>
+        <v>-0.2324</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.5252</v>
+        <v>-6.5072</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.6</v>
       </c>
       <c r="I317" t="n">
-        <v>1.437</v>
+        <v>1.28</v>
       </c>
       <c r="J317" t="n">
-        <v>40.236</v>
+        <v>35.84</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.24</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6705</v>
+        <v>0.6637</v>
       </c>
       <c r="J318" t="n">
-        <v>18.774</v>
+        <v>18.5836</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.09</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2278</v>
+        <v>0.2834</v>
       </c>
       <c r="J319" t="n">
-        <v>6.3784</v>
+        <v>7.9352</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.97</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.2464</v>
+        <v>-0.1718</v>
       </c>
       <c r="J320" t="n">
-        <v>-6.8992</v>
+        <v>-4.8104</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.9</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.4637</v>
+        <v>-0.3933</v>
       </c>
       <c r="J321" t="n">
-        <v>-12.9836</v>
+        <v>-11.0124</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.13</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2871</v>
+        <v>0.24</v>
       </c>
       <c r="J322" t="n">
-        <v>8.613</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1262</v>
+        <v>0.0929</v>
       </c>
       <c r="J323" t="n">
-        <v>3.786</v>
+        <v>2.787</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0551</v>
+        <v>0.0321</v>
       </c>
       <c r="J324" t="n">
-        <v>1.653</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.2013</v>
+        <v>-0.1202</v>
       </c>
       <c r="J325" t="n">
-        <v>-6.039</v>
+        <v>-3.606</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.4061</v>
+        <v>-0.2558</v>
       </c>
       <c r="J326" t="n">
-        <v>-12.183</v>
+        <v>-7.674</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.6</v>
       </c>
       <c r="I327" t="n">
-        <v>0.8511</v>
+        <v>0.7665</v>
       </c>
       <c r="J327" t="n">
-        <v>25.533</v>
+        <v>22.995</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1302</v>
+        <v>0.122</v>
       </c>
       <c r="J328" t="n">
-        <v>3.906</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.03</v>
       </c>
       <c r="I329" t="n">
-        <v>0.045</v>
+        <v>0.0579</v>
       </c>
       <c r="J329" t="n">
-        <v>1.35</v>
+        <v>1.737</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.2966</v>
+        <v>-0.1753</v>
       </c>
       <c r="J330" t="n">
-        <v>-8.898</v>
+        <v>-5.259</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3853</v>
+        <v>-0.2375</v>
       </c>
       <c r="J331" t="n">
-        <v>-11.559</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.58</v>
       </c>
       <c r="I332" t="n">
-        <v>1.3839</v>
+        <v>1.2458</v>
       </c>
       <c r="J332" t="n">
-        <v>40.1331</v>
+        <v>36.1282</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.24</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6509</v>
+        <v>0.6562</v>
       </c>
       <c r="J333" t="n">
-        <v>18.8761</v>
+        <v>19.0298</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.12</v>
       </c>
       <c r="I334" t="n">
-        <v>0.2991</v>
+        <v>0.3601</v>
       </c>
       <c r="J334" t="n">
-        <v>8.6739</v>
+        <v>10.4429</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.02</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.0188</v>
+        <v>0.0499</v>
       </c>
       <c r="J335" t="n">
-        <v>-0.5452</v>
+        <v>1.4471</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.1781</v>
+        <v>-0.101</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.1649</v>
+        <v>-2.929</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.17</v>
       </c>
       <c r="I337" t="n">
-        <v>0.3841</v>
+        <v>0.4287</v>
       </c>
       <c r="J337" t="n">
-        <v>11.1389</v>
+        <v>12.4323</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.063</v>
+        <v>-0.0639</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.827</v>
+        <v>-1.8531</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.89</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1805</v>
+        <v>-0.1333</v>
       </c>
       <c r="J339" t="n">
-        <v>-5.2345</v>
+        <v>-3.8657</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3321</v>
+        <v>-0.2142</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.6309</v>
+        <v>-6.2118</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.57</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.443</v>
       </c>
       <c r="J341" t="n">
-        <v>-19.2212</v>
+        <v>-12.847</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.59</v>
       </c>
       <c r="I342" t="n">
-        <v>1.411</v>
+        <v>1.2631</v>
       </c>
       <c r="J342" t="n">
-        <v>40.919</v>
+        <v>36.6299</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8981</v>
+        <v>0.8933</v>
       </c>
       <c r="J343" t="n">
-        <v>26.0449</v>
+        <v>25.9057</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I344" t="n">
-        <v>0.4964</v>
+        <v>0.5159</v>
       </c>
       <c r="J344" t="n">
-        <v>14.3956</v>
+        <v>14.9611</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.9</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.4682</v>
+        <v>-0.3969</v>
       </c>
       <c r="J345" t="n">
-        <v>-13.5778</v>
+        <v>-11.5101</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.86</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5095</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.6779</v>
+        <v>-14.7755</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4048</v>
+        <v>0.46</v>
       </c>
       <c r="J347" t="n">
-        <v>11.7392</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.07</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1983</v>
+        <v>0.1991</v>
       </c>
       <c r="J348" t="n">
-        <v>5.7507</v>
+        <v>5.7739</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.02</v>
       </c>
       <c r="I349" t="n">
-        <v>0.0963</v>
+        <v>0.0785</v>
       </c>
       <c r="J349" t="n">
-        <v>2.7927</v>
+        <v>2.2765</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4815</v>
+        <v>-0.3101</v>
       </c>
       <c r="J350" t="n">
-        <v>-13.9635</v>
+        <v>-8.992900000000001</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.3387</v>
       </c>
       <c r="J351" t="n">
-        <v>-15.1293</v>
+        <v>-9.8223</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.53</v>
       </c>
       <c r="I352" t="n">
-        <v>1.21</v>
+        <v>1.1481</v>
       </c>
       <c r="J352" t="n">
-        <v>29.04</v>
+        <v>27.5544</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.52</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1899</v>
+        <v>1.1359</v>
       </c>
       <c r="J353" t="n">
-        <v>28.5576</v>
+        <v>27.2616</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0446</v>
+        <v>1.0491</v>
       </c>
       <c r="J354" t="n">
-        <v>25.0704</v>
+        <v>25.1784</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.2</v>
       </c>
       <c r="I355" t="n">
-        <v>0.4347</v>
+        <v>0.5308</v>
       </c>
       <c r="J355" t="n">
-        <v>10.4328</v>
+        <v>12.7392</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.05</v>
       </c>
       <c r="I356" t="n">
-        <v>0.032</v>
+        <v>0.1168</v>
       </c>
       <c r="J356" t="n">
-        <v>0.768</v>
+        <v>2.8032</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.07</v>
       </c>
       <c r="I357" t="n">
-        <v>0.2617</v>
+        <v>0.2638</v>
       </c>
       <c r="J357" t="n">
-        <v>6.2808</v>
+        <v>6.3312</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1819</v>
+        <v>-0.1525</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.3656</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.85</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.199</v>
+        <v>-0.1632</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.776</v>
+        <v>-3.9168</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.62</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.5760999999999999</v>
+        <v>-0.3834</v>
       </c>
       <c r="J360" t="n">
-        <v>-13.8264</v>
+        <v>-9.201599999999999</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.51</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.7186</v>
+        <v>-0.4858</v>
       </c>
       <c r="J361" t="n">
-        <v>-17.2464</v>
+        <v>-11.6592</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.9365</v>
+        <v>0.926</v>
       </c>
       <c r="J362" t="n">
-        <v>25.2855</v>
+        <v>25.002</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4336</v>
+        <v>0.4464</v>
       </c>
       <c r="J363" t="n">
-        <v>11.7072</v>
+        <v>12.0528</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.14</v>
       </c>
       <c r="I364" t="n">
-        <v>0.3941</v>
+        <v>0.4216</v>
       </c>
       <c r="J364" t="n">
-        <v>10.6407</v>
+        <v>11.3832</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2374</v>
+        <v>0.287</v>
       </c>
       <c r="J365" t="n">
-        <v>6.4098</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.1598</v>
+        <v>-0.0892</v>
       </c>
       <c r="J366" t="n">
-        <v>-4.3146</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5098</v>
+        <v>0.6005</v>
       </c>
       <c r="J367" t="n">
-        <v>13.7646</v>
+        <v>16.2135</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.26</v>
       </c>
       <c r="I368" t="n">
-        <v>0.4831</v>
+        <v>0.5647</v>
       </c>
       <c r="J368" t="n">
-        <v>13.0437</v>
+        <v>15.2469</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.2114</v>
+        <v>-0.1292</v>
       </c>
       <c r="J369" t="n">
-        <v>-5.7078</v>
+        <v>-3.4884</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.72</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4846</v>
+        <v>-0.3118</v>
       </c>
       <c r="J370" t="n">
-        <v>-13.0842</v>
+        <v>-8.4186</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.61</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.4151</v>
       </c>
       <c r="J371" t="n">
-        <v>-16.9155</v>
+        <v>-11.2077</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.76</v>
       </c>
       <c r="I372" t="n">
-        <v>1.6908</v>
+        <v>1.4523</v>
       </c>
       <c r="J372" t="n">
-        <v>42.27</v>
+        <v>36.3075</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.19</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4599</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J373" t="n">
-        <v>11.4975</v>
+        <v>13.2175</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.16</v>
       </c>
       <c r="I374" t="n">
-        <v>0.3803</v>
+        <v>0.4534</v>
       </c>
       <c r="J374" t="n">
-        <v>9.5075</v>
+        <v>11.335</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2722</v>
+        <v>0.3477</v>
       </c>
       <c r="J375" t="n">
-        <v>6.805</v>
+        <v>8.692500000000001</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.99</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1968</v>
+        <v>-0.1145</v>
       </c>
       <c r="J376" t="n">
-        <v>-4.92</v>
+        <v>-2.8625</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>0.9</v>
       </c>
       <c r="I377" t="n">
-        <v>-0.124</v>
+        <v>-0.1123</v>
       </c>
       <c r="J377" t="n">
-        <v>-3.1</v>
+        <v>-2.8075</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.87</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1767</v>
+        <v>-0.1457</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.4175</v>
+        <v>-3.6425</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.85</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2116</v>
+        <v>-0.1669</v>
       </c>
       <c r="J379" t="n">
-        <v>-5.29</v>
+        <v>-4.1725</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.73</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4274</v>
+        <v>-0.2828</v>
       </c>
       <c r="J380" t="n">
-        <v>-10.685</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.68</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.3304</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.5125</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.7194</v>
+        <v>0.6747</v>
       </c>
       <c r="J382" t="n">
-        <v>20.1432</v>
+        <v>18.8916</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.06</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2731</v>
+        <v>0.2302</v>
       </c>
       <c r="J383" t="n">
-        <v>7.6468</v>
+        <v>6.4456</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1961</v>
+        <v>-0.1634</v>
       </c>
       <c r="J384" t="n">
-        <v>-5.4908</v>
+        <v>-4.5752</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.9</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.3943</v>
+        <v>-0.3477</v>
       </c>
       <c r="J385" t="n">
-        <v>-11.0404</v>
+        <v>-9.7356</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.84</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5626</v>
+        <v>-0.5142</v>
       </c>
       <c r="J386" t="n">
-        <v>-15.7528</v>
+        <v>-14.3976</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.31</v>
       </c>
       <c r="I387" t="n">
-        <v>0.5128</v>
+        <v>0.6125</v>
       </c>
       <c r="J387" t="n">
-        <v>14.3584</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.17</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3173</v>
+        <v>0.3663</v>
       </c>
       <c r="J388" t="n">
-        <v>8.884399999999999</v>
+        <v>10.2564</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.03</v>
       </c>
       <c r="I389" t="n">
-        <v>0.0509</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="J389" t="n">
-        <v>1.4252</v>
+        <v>2.3408</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.96</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.1368</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J390" t="n">
-        <v>-3.8304</v>
+        <v>-1.946</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.339</v>
+        <v>-0.2053</v>
       </c>
       <c r="J391" t="n">
-        <v>-9.492000000000001</v>
+        <v>-5.7484</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5339/event_5339_evp_summary.xlsx
+++ b/database/event/5339/event_5339_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.169</v>
+        <v>6.2741</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3143</v>
+        <v>1.3367</v>
       </c>
       <c r="D2" t="n">
-        <v>2.147</v>
+        <v>2.2319</v>
       </c>
       <c r="E2" t="n">
-        <v>6.169</v>
+        <v>6.2741</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8418</v>
+        <v>3.7895</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3272</v>
+        <v>2.4846</v>
       </c>
       <c r="H2" t="n">
-        <v>8.049899999999999</v>
+        <v>7.6086</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1856</v>
+        <v>4.1086</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3272</v>
+        <v>2.4846</v>
       </c>
       <c r="K2" t="n">
         <v>192</v>
@@ -529,7 +529,7 @@
         <v>77</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5128</v>
+        <v>6.5932</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0163</v>
+        <v>6.2231</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2817</v>
+        <v>1.3258</v>
       </c>
       <c r="D3" t="n">
-        <v>2.078</v>
+        <v>2.2087</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0163</v>
+        <v>6.2231</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5527</v>
+        <v>3.4832</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4636</v>
+        <v>2.7399</v>
       </c>
       <c r="H3" t="n">
-        <v>7.0312</v>
+        <v>6.5981</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6559</v>
+        <v>3.5629</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4636</v>
+        <v>2.7399</v>
       </c>
       <c r="K3" t="n">
         <v>192</v>
@@ -575,7 +575,7 @@
         <v>77</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1195</v>
+        <v>6.3028</v>
       </c>
       <c r="N3" t="n">
         <v>269</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4634</v>
+        <v>5.584</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1639</v>
+        <v>1.1896</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8284</v>
+        <v>1.9177</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4634</v>
+        <v>5.584</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5147</v>
+        <v>3.4497</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9487</v>
+        <v>2.1343</v>
       </c>
       <c r="H4" t="n">
-        <v>6.8971</v>
+        <v>6.4875</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5862</v>
+        <v>3.5032</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9487</v>
+        <v>2.1343</v>
       </c>
       <c r="K4" t="n">
         <v>192</v>
@@ -621,7 +621,7 @@
         <v>77</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5349</v>
+        <v>5.6375</v>
       </c>
       <c r="N4" t="n">
         <v>269</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0943</v>
+        <v>5.1033</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0853</v>
+        <v>1.0872</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6618</v>
+        <v>1.6989</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0943</v>
+        <v>5.1033</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4366</v>
+        <v>4.3608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6577</v>
+        <v>0.7425</v>
       </c>
       <c r="H5" t="n">
-        <v>10.1455</v>
+        <v>9.4937</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2752</v>
+        <v>5.1265</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6577</v>
+        <v>0.7425</v>
       </c>
       <c r="K5" t="n">
         <v>167</v>
@@ -667,7 +667,7 @@
         <v>85</v>
       </c>
       <c r="M5" t="n">
-        <v>5.9329</v>
+        <v>5.869</v>
       </c>
       <c r="N5" t="n">
         <v>252</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.868</v>
+        <v>4.9414</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0371</v>
+        <v>1.0527</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5596</v>
+        <v>1.6252</v>
       </c>
       <c r="E6" t="n">
-        <v>4.868</v>
+        <v>4.9414</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4162</v>
+        <v>0.3607</v>
       </c>
       <c r="H6" t="n">
-        <v>12.7657</v>
+        <v>11.8283</v>
       </c>
       <c r="I6" t="n">
-        <v>6.6376</v>
+        <v>6.3872</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4162</v>
+        <v>0.3607</v>
       </c>
       <c r="K6" t="n">
         <v>338</v>
@@ -713,7 +713,7 @@
         <v>77</v>
       </c>
       <c r="M6" t="n">
-        <v>7.0538</v>
+        <v>6.7479</v>
       </c>
       <c r="N6" t="n">
         <v>415</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2179</v>
+        <v>4.0617</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8986</v>
+        <v>0.8653</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2662</v>
+        <v>1.2248</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2179</v>
+        <v>4.0617</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2732</v>
+        <v>4.1551</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0553</v>
+        <v>-0.0934</v>
       </c>
       <c r="H7" t="n">
-        <v>9.569900000000001</v>
+        <v>8.815099999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>4.9759</v>
+        <v>4.7601</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0553</v>
+        <v>-0.0934</v>
       </c>
       <c r="K7" t="n">
         <v>338</v>
@@ -759,7 +759,7 @@
         <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>4.9206</v>
+        <v>4.666700000000001</v>
       </c>
       <c r="N7" t="n">
         <v>415</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0976</v>
+        <v>4.0468</v>
       </c>
       <c r="C8" t="n">
-        <v>0.873</v>
+        <v>0.8621</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2118</v>
+        <v>1.218</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0976</v>
+        <v>4.0468</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4035</v>
+        <v>3.3698</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5054</v>
+        <v>6.224</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3825</v>
+        <v>3.3609</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.677</v>
       </c>
       <c r="K8" t="n">
         <v>192</v>
@@ -805,7 +805,7 @@
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0766</v>
+        <v>4.0379</v>
       </c>
       <c r="N8" t="n">
         <v>269</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6948</v>
+        <v>3.6581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7871</v>
+        <v>0.7793</v>
       </c>
       <c r="D9" t="n">
-        <v>1.03</v>
+        <v>1.041</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6948</v>
+        <v>3.6581</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4342</v>
+        <v>2.751</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2606</v>
+        <v>0.9071</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6137</v>
+        <v>4.1823</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4388</v>
+        <v>2.2584</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2606</v>
+        <v>0.9071</v>
       </c>
       <c r="K9" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="L9" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6994</v>
+        <v>3.1655</v>
       </c>
       <c r="N9" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.671</v>
+        <v>3.6448</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7821</v>
+        <v>0.7765</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0193</v>
+        <v>1.035</v>
       </c>
       <c r="E10" t="n">
-        <v>3.671</v>
+        <v>3.6448</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8262</v>
+        <v>3.3361</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8448</v>
+        <v>0.3087</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4715</v>
+        <v>6.1127</v>
       </c>
       <c r="I10" t="n">
-        <v>2.325</v>
+        <v>3.3008</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8448</v>
+        <v>0.3087</v>
       </c>
       <c r="K10" t="n">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1698</v>
+        <v>3.6095</v>
       </c>
       <c r="N10" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3014</v>
+        <v>3.2508</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7033</v>
+        <v>0.6926</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8524</v>
+        <v>0.8556</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3014</v>
+        <v>3.2508</v>
       </c>
       <c r="F11" t="n">
-        <v>3.0723</v>
+        <v>3.02</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2291</v>
+        <v>0.2308</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3385</v>
+        <v>5.0699</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7758</v>
+        <v>2.7377</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2291</v>
+        <v>0.2308</v>
       </c>
       <c r="K11" t="n">
         <v>167</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0049</v>
+        <v>2.9685</v>
       </c>
       <c r="N11" t="n">
         <v>252</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2579</v>
+        <v>3.0669</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6534</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8328</v>
+        <v>0.7719</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2579</v>
+        <v>3.0669</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2579</v>
+        <v>1.5121</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.5548</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7941</v>
+        <v>1.5121</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7941</v>
+        <v>0.8165</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.5548</v>
       </c>
       <c r="K12" t="n">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7941</v>
+        <v>2.3713</v>
       </c>
       <c r="N12" t="n">
-        <v>253</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1488</v>
+        <v>2.9972</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6708</v>
+        <v>0.6385</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7835</v>
+        <v>0.7402</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1488</v>
+        <v>2.9972</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7284</v>
+        <v>2.6337</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4204</v>
+        <v>0.3635</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7284</v>
+        <v>3.7954</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8987000000000001</v>
+        <v>2.0495</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4204</v>
+        <v>0.3635</v>
       </c>
       <c r="K13" t="n">
         <v>290</v>
@@ -1035,7 +1035,7 @@
         <v>85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3191</v>
+        <v>2.413</v>
       </c>
       <c r="N13" t="n">
         <v>375</v>
@@ -1044,124 +1044,124 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0259</v>
+        <v>2.8964</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6446</v>
+        <v>0.6171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.728</v>
+        <v>0.6943</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0259</v>
+        <v>2.8964</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7114</v>
+        <v>2.8964</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3145</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0669</v>
+        <v>3.6143</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1146</v>
+        <v>3.6143</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3145</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="L14" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4291</v>
+        <v>3.6143</v>
       </c>
       <c r="N14" t="n">
-        <v>375</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oSee</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8365</v>
+        <v>2.7468</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6425</v>
+        <v>0.6262</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8365</v>
+        <v>2.7468</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8365</v>
+        <v>2.2449</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8687</v>
+        <v>2.5126</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9867</v>
+        <v>1.3568</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="K15" t="n">
-        <v>249</v>
+        <v>167</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9867</v>
+        <v>1.8587</v>
       </c>
       <c r="N15" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>oSee</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7571</v>
+        <v>2.5314</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5874</v>
+        <v>0.5393</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6067</v>
+        <v>0.5281</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7571</v>
+        <v>2.5314</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7571</v>
+        <v>2.5314</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7571</v>
+        <v>2.8155</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8705</v>
+        <v>2.8881</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8705</v>
+        <v>2.8881</v>
       </c>
       <c r="N16" t="n">
         <v>249</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.7535</v>
+        <v>2.4646</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5866</v>
+        <v>0.5251</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6051</v>
+        <v>0.4977</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7535</v>
+        <v>2.4646</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2983</v>
+        <v>2.4646</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4552</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6114</v>
+        <v>2.6692</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3578</v>
+        <v>2.738</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4552</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="L17" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.813</v>
+        <v>2.738</v>
       </c>
       <c r="N17" t="n">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7466</v>
+        <v>2.4585</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5851</v>
+        <v>0.5238</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6019</v>
+        <v>0.495</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7466</v>
+        <v>2.4585</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7466</v>
+        <v>2.4585</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7466</v>
+        <v>2.656</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7466</v>
+        <v>2.656</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7466</v>
+        <v>2.656</v>
       </c>
       <c r="N18" t="n">
         <v>253</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6992</v>
+        <v>2.445</v>
       </c>
       <c r="C19" t="n">
-        <v>0.575</v>
+        <v>0.5209</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5805</v>
+        <v>0.4888</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6992</v>
+        <v>2.445</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6992</v>
+        <v>2.445</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6992</v>
+        <v>2.6265</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6992</v>
+        <v>2.6265</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6992</v>
+        <v>2.6265</v>
       </c>
       <c r="N19" t="n">
         <v>253</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.3208</v>
+        <v>2.2415</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4944</v>
+        <v>0.4775</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4097</v>
+        <v>0.3962</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3208</v>
+        <v>2.2415</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5453</v>
+        <v>2.4573</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2245</v>
+        <v>-0.2158</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4817</v>
+        <v>3.2132</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8103</v>
+        <v>1.7351</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2245</v>
+        <v>-0.2158</v>
       </c>
       <c r="K20" t="n">
         <v>290</v>
@@ -1357,7 +1357,7 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5858</v>
+        <v>1.5193</v>
       </c>
       <c r="N20" t="n">
         <v>375</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0988</v>
+        <v>2.0478</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4471</v>
+        <v>0.4363</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3095</v>
+        <v>0.308</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0988</v>
+        <v>2.0478</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0988</v>
+        <v>2.0478</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0988</v>
+        <v>2.0478</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1851</v>
+        <v>2.1006</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1851</v>
+        <v>2.1006</v>
       </c>
       <c r="N21" t="n">
         <v>249</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0171</v>
+        <v>1.8838</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4297</v>
+        <v>0.4013</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2726</v>
+        <v>0.2333</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0171</v>
+        <v>1.8838</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1034</v>
+        <v>3.0316</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0863</v>
+        <v>-1.1478</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4482</v>
+        <v>5.1082</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8328</v>
+        <v>2.7584</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0863</v>
+        <v>-1.1478</v>
       </c>
       <c r="K22" t="n">
         <v>338</v>
@@ -1449,7 +1449,7 @@
         <v>77</v>
       </c>
       <c r="M22" t="n">
-        <v>1.7465</v>
+        <v>1.6106</v>
       </c>
       <c r="N22" t="n">
         <v>415</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8648</v>
+        <v>1.7669</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3973</v>
+        <v>0.3764</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2039</v>
+        <v>0.1801</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8648</v>
+        <v>1.7669</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6151</v>
+        <v>0.4178</v>
       </c>
       <c r="G23" t="n">
-        <v>1.2497</v>
+        <v>1.3491</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6151</v>
+        <v>0.4178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3198</v>
+        <v>0.2256</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2497</v>
+        <v>1.3491</v>
       </c>
       <c r="K23" t="n">
         <v>290</v>
@@ -1495,7 +1495,7 @@
         <v>85</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5695</v>
+        <v>1.5747</v>
       </c>
       <c r="N23" t="n">
         <v>375</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.7004</v>
+        <v>1.5935</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3623</v>
+        <v>0.3395</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1296</v>
+        <v>0.1012</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7004</v>
+        <v>1.5935</v>
       </c>
       <c r="F24" t="n">
-        <v>2.2668</v>
+        <v>2.1998</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5664</v>
+        <v>-0.6063</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5004</v>
+        <v>2.3637</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3001</v>
+        <v>1.2764</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5664</v>
+        <v>-0.6063</v>
       </c>
       <c r="K24" t="n">
         <v>167</v>
@@ -1541,7 +1541,7 @@
         <v>85</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7337</v>
+        <v>0.6701</v>
       </c>
       <c r="N24" t="n">
         <v>252</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.631</v>
+        <v>1.5206</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3475</v>
+        <v>0.324</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0983</v>
+        <v>0.068</v>
       </c>
       <c r="E25" t="n">
-        <v>1.631</v>
+        <v>1.5206</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5082</v>
+        <v>2.4535</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8772</v>
+        <v>-0.9329</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3511</v>
+        <v>3.201</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7424</v>
+        <v>1.7285</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8772</v>
+        <v>-0.9329</v>
       </c>
       <c r="K25" t="n">
         <v>338</v>
@@ -1587,7 +1587,7 @@
         <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8652</v>
+        <v>0.7956</v>
       </c>
       <c r="N25" t="n">
         <v>415</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3132</v>
+        <v>0.3049</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0258</v>
+        <v>0.0274</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4703</v>
+        <v>1.4314</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="C27" t="n">
-        <v>0.176</v>
+        <v>0.1588</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2652</v>
+        <v>-0.2848</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8259</v>
+        <v>0.7456</v>
       </c>
       <c r="N27" t="n">
         <v>253</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1572</v>
+        <v>0.1378</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3049</v>
+        <v>-0.3297</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7378</v>
+        <v>0.647</v>
       </c>
       <c r="N28" t="n">
         <v>99</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>vanity</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6099</v>
+        <v>0.5528</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1299</v>
+        <v>0.1178</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3627</v>
+        <v>-0.3726</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6099</v>
+        <v>0.5528</v>
       </c>
       <c r="F29" t="n">
-        <v>1.1113</v>
+        <v>0.5528</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5014</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1113</v>
+        <v>0.5528</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5778</v>
+        <v>0.5528</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5014</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="L29" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.07640000000000002</v>
+        <v>0.5528</v>
       </c>
       <c r="N29" t="n">
-        <v>375</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vanity</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6059</v>
+        <v>0.3835</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1291</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3645</v>
+        <v>-0.4496</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6059</v>
+        <v>0.3835</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6059</v>
+        <v>0.8224</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4389</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6059</v>
+        <v>0.8224</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6059</v>
+        <v>0.4441</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4389</v>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6059</v>
+        <v>0.005199999999999982</v>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0155</v>
+        <v>-0.0257</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.679</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0728</v>
+        <v>-0.1204</v>
       </c>
       <c r="N31" t="n">
         <v>99</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1041</v>
+        <v>-0.1163</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8585</v>
+        <v>-0.8727</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4884</v>
+        <v>-0.5458</v>
       </c>
       <c r="N32" t="n">
         <v>100</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6273</v>
+        <v>-0.6617</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1336</v>
+        <v>-0.141</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9212</v>
+        <v>-0.9254</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6273</v>
+        <v>-0.6617</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6273</v>
+        <v>-0.6617</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6273</v>
+        <v>-0.6617</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6531</v>
+        <v>-0.6788</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6531</v>
+        <v>-0.6788</v>
       </c>
       <c r="N33" t="n">
         <v>249</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.137</v>
+        <v>-0.1454</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9284</v>
+        <v>-0.9349</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6432</v>
+        <v>-0.6826</v>
       </c>
       <c r="N34" t="n">
         <v>99</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1394</v>
+        <v>-0.1511</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9334</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6542</v>
+        <v>-0.7094</v>
       </c>
       <c r="N35" t="n">
         <v>99</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1552</v>
+        <v>-0.1614</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9669</v>
+        <v>-0.9691</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7286</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>253</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1799</v>
+        <v>-0.1867</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0192</v>
+        <v>-1.0231</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8762</v>
       </c>
       <c r="N37" t="n">
         <v>99</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1838</v>
+        <v>-0.1966</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0275</v>
+        <v>-1.0442</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8628</v>
+        <v>-0.9227</v>
       </c>
       <c r="N38" t="n">
         <v>100</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9434</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1968</v>
+        <v>-0.201</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0551</v>
+        <v>-1.0537</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9434</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9434</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.9434</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9619</v>
+        <v>-0.9677</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9619</v>
+        <v>-0.9677</v>
       </c>
       <c r="N39" t="n">
         <v>249</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.1417</v>
+        <v>-0.9687</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2432</v>
+        <v>-0.2064</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1534</v>
+        <v>-1.0652</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.1417</v>
+        <v>-0.9687</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2086</v>
+        <v>-1.0608</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0669</v>
+        <v>0.0921</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2086</v>
+        <v>-1.0608</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6284</v>
+        <v>-0.5728</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0669</v>
+        <v>0.0921</v>
       </c>
       <c r="K40" t="n">
         <v>338</v>
@@ -2277,7 +2277,7 @@
         <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.5615</v>
+        <v>-0.4807</v>
       </c>
       <c r="N40" t="n">
         <v>415</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2472</v>
+        <v>-0.2594</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1619</v>
+        <v>-1.1784</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1604</v>
+        <v>-1.2175</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -2429,10 +2429,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6723</v>
+        <v>1.8165</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6723</v>
+        <v>1.8165</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2148</v>
+        <v>1.2591</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2148</v>
+        <v>1.2591</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9766</v>
+        <v>0.9293</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9766</v>
+        <v>0.9293</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7441</v>
+        <v>0.7191</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7441</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.162</v>
+        <v>-0.1344</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.162</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1465</v>
+        <v>-0.1695</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1465</v>
+        <v>-0.1695</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.75</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2512</v>
+        <v>-0.2722</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2512</v>
+        <v>-0.2722</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3246</v>
+        <v>-0.3439</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3246</v>
+        <v>-0.3439</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3616</v>
+        <v>-0.3794</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3616</v>
+        <v>-0.3794</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.61</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3802</v>
+        <v>-0.3972</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2744</v>
+        <v>1.3301</v>
       </c>
       <c r="J12" t="n">
-        <v>25.488</v>
+        <v>26.602</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2744</v>
+        <v>1.3301</v>
       </c>
       <c r="J13" t="n">
-        <v>25.488</v>
+        <v>26.602</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2771</v>
+        <v>-0.2639</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.542</v>
+        <v>-5.278</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3687</v>
+        <v>-0.3493</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.374</v>
+        <v>-6.986</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5646</v>
+        <v>-0.5276</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.292</v>
+        <v>-10.552</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6282</v>
+        <v>0.6026</v>
       </c>
       <c r="J17" t="n">
-        <v>12.564</v>
+        <v>12.052</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.96</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0578</v>
+        <v>-0.0684</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.156</v>
+        <v>-1.368</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.127</v>
+        <v>-0.1413</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.54</v>
+        <v>-2.826</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.77</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2606</v>
+        <v>-0.2754</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.212</v>
+        <v>-5.508</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2898</v>
+        <v>-0.304</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.796</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3281</v>
+        <v>0.3312</v>
       </c>
       <c r="J22" t="n">
-        <v>9.514900000000001</v>
+        <v>9.604799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3138</v>
+        <v>0.3175</v>
       </c>
       <c r="J23" t="n">
-        <v>9.100199999999999</v>
+        <v>9.2075</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0321</v>
+        <v>0.0363</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.0527</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2259</v>
+        <v>-0.2401</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.5511</v>
+        <v>-6.9629</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3522</v>
+        <v>-0.3636</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.2138</v>
+        <v>-10.5444</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.22</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3263</v>
+        <v>0.3381</v>
       </c>
       <c r="J27" t="n">
-        <v>9.4627</v>
+        <v>9.8049</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2619</v>
+        <v>0.2755</v>
       </c>
       <c r="J28" t="n">
-        <v>7.5951</v>
+        <v>7.9895</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0419</v>
+        <v>0.0507</v>
       </c>
       <c r="J29" t="n">
-        <v>1.2151</v>
+        <v>1.4703</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0255</v>
+        <v>-0.029</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7395</v>
+        <v>-0.841</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1624</v>
+        <v>-0.1742</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.7096</v>
+        <v>-5.0518</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4884</v>
+        <v>0.4689</v>
       </c>
       <c r="J32" t="n">
-        <v>14.1636</v>
+        <v>13.5981</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3489</v>
+        <v>0.342</v>
       </c>
       <c r="J33" t="n">
-        <v>10.1181</v>
+        <v>9.917999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.229</v>
+        <v>0.2304</v>
       </c>
       <c r="J34" t="n">
-        <v>6.641</v>
+        <v>6.6816</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.229</v>
+        <v>-0.2304</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.641</v>
+        <v>-6.6816</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7492</v>
+        <v>-0.7003</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.7268</v>
+        <v>-20.3087</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.569</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>16.501</v>
+        <v>16.211</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3593</v>
+        <v>0.3647</v>
       </c>
       <c r="J38" t="n">
-        <v>10.4197</v>
+        <v>10.5763</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1478</v>
+        <v>0.1603</v>
       </c>
       <c r="J39" t="n">
-        <v>4.2862</v>
+        <v>4.6487</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1257</v>
+        <v>0.1382</v>
       </c>
       <c r="J40" t="n">
-        <v>3.6453</v>
+        <v>4.0078</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1445</v>
+        <v>-0.1549</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.1905</v>
+        <v>-4.4921</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.1</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8168</v>
+        <v>1.8219</v>
       </c>
       <c r="J42" t="n">
-        <v>45.42</v>
+        <v>45.5475</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.788</v>
+        <v>0.7537</v>
       </c>
       <c r="J43" t="n">
-        <v>19.7</v>
+        <v>18.8425</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.28</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7207</v>
+        <v>0.6942</v>
       </c>
       <c r="J44" t="n">
-        <v>18.0175</v>
+        <v>17.355</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2394</v>
+        <v>0.2597</v>
       </c>
       <c r="J45" t="n">
-        <v>5.985</v>
+        <v>6.4925</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2519</v>
+        <v>-0.2298</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.2975</v>
+        <v>-5.745</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1612</v>
+        <v>0.1575</v>
       </c>
       <c r="J47" t="n">
-        <v>4.03</v>
+        <v>3.9375</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0838</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.095</v>
+        <v>-2.4775</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1073</v>
+        <v>-0.1234</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.6825</v>
+        <v>-3.085</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2202</v>
+        <v>-0.2378</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.505</v>
+        <v>-5.945</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4574</v>
+        <v>-0.4669</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.435</v>
+        <v>-11.6725</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.87</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1274</v>
+        <v>-0.1498</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.9302</v>
+        <v>-3.4454</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2239</v>
+        <v>-0.245</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.1497</v>
+        <v>-5.635</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2239</v>
+        <v>-0.245</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.1497</v>
+        <v>-5.635</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.65</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3451</v>
+        <v>-0.3633</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.9373</v>
+        <v>-8.3559</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4853</v>
+        <v>-0.496</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.1619</v>
+        <v>-11.408</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1211</v>
+        <v>1.0889</v>
       </c>
       <c r="J57" t="n">
-        <v>25.7853</v>
+        <v>25.0447</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.39</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9517</v>
+        <v>0.9014</v>
       </c>
       <c r="J58" t="n">
-        <v>21.8891</v>
+        <v>20.7322</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.33</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8288</v>
+        <v>0.7903</v>
       </c>
       <c r="J59" t="n">
-        <v>19.0624</v>
+        <v>18.1769</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>18.0504</v>
+        <v>17.2845</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.29</v>
       </c>
       <c r="I61" t="n">
-        <v>0.74</v>
+        <v>0.7119</v>
       </c>
       <c r="J61" t="n">
-        <v>17.02</v>
+        <v>16.3737</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4413</v>
+        <v>0.4356</v>
       </c>
       <c r="J62" t="n">
-        <v>13.239</v>
+        <v>13.068</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.328</v>
+        <v>0.3297</v>
       </c>
       <c r="J63" t="n">
-        <v>9.84</v>
+        <v>9.891</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0674</v>
+        <v>0.0743</v>
       </c>
       <c r="J64" t="n">
-        <v>2.022</v>
+        <v>2.229</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1108</v>
+        <v>-0.123</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.324</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.68</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3542</v>
+        <v>-0.3653</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.626</v>
+        <v>-10.959</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.54</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2093</v>
+        <v>1.1737</v>
       </c>
       <c r="J67" t="n">
-        <v>36.279</v>
+        <v>35.211</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4722</v>
+        <v>0.4632</v>
       </c>
       <c r="J68" t="n">
-        <v>14.166</v>
+        <v>13.896</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.0625</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>1.875</v>
+        <v>2.346</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0625</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>1.875</v>
+        <v>2.346</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.96</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2015</v>
+        <v>-0.1945</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.045</v>
+        <v>-5.835</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7711</v>
+        <v>0.7389</v>
       </c>
       <c r="J72" t="n">
-        <v>32.3862</v>
+        <v>31.0338</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3718</v>
+        <v>0.3737</v>
       </c>
       <c r="J73" t="n">
-        <v>15.6156</v>
+        <v>15.6954</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.99</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.024</v>
+        <v>-0.0278</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.008</v>
+        <v>-1.1676</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.86</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.182</v>
+        <v>-0.1944</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.644</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2635</v>
+        <v>-0.2756</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.067</v>
+        <v>-11.5752</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9786</v>
+        <v>0.9115</v>
       </c>
       <c r="J77" t="n">
-        <v>41.1012</v>
+        <v>38.283</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4662</v>
+        <v>0.4534</v>
       </c>
       <c r="J78" t="n">
-        <v>19.5804</v>
+        <v>19.0428</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3021</v>
+        <v>0.303</v>
       </c>
       <c r="J79" t="n">
-        <v>12.6882</v>
+        <v>12.726</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1458</v>
+        <v>-0.1463</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.1236</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7921</v>
+        <v>-0.7349</v>
       </c>
       <c r="J81" t="n">
-        <v>-33.2682</v>
+        <v>-30.8658</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.5968</v>
       </c>
       <c r="J82" t="n">
-        <v>17.8756</v>
+        <v>17.3072</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5815</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>16.8635</v>
+        <v>16.385</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1119</v>
+        <v>-0.1238</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.2451</v>
+        <v>-3.5902</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2292</v>
+        <v>-0.2426</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.6468</v>
+        <v>-7.0354</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3365</v>
+        <v>-0.3479</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.7585</v>
+        <v>-10.0891</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9105</v>
+        <v>0.8512</v>
       </c>
       <c r="J87" t="n">
-        <v>26.4045</v>
+        <v>24.6848</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8408</v>
+        <v>0.79</v>
       </c>
       <c r="J88" t="n">
-        <v>24.3832</v>
+        <v>22.91</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.23</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6493</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>18.8297</v>
+        <v>18.0235</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0296</v>
+        <v>-0.0204</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.5916</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.784</v>
+        <v>-0.7248</v>
       </c>
       <c r="J91" t="n">
-        <v>-22.736</v>
+        <v>-21.0192</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4076</v>
+        <v>0.3999</v>
       </c>
       <c r="J92" t="n">
-        <v>10.5976</v>
+        <v>10.3974</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.97</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.1466</v>
+        <v>-1.3962</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0441</v>
+        <v>-0.0537</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.1466</v>
+        <v>-1.3962</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1587</v>
+        <v>-0.1738</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.1262</v>
+        <v>-4.5188</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.66</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3655</v>
+        <v>-0.3775</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.503</v>
+        <v>-9.815</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1738</v>
+        <v>1.1376</v>
       </c>
       <c r="J97" t="n">
-        <v>30.5188</v>
+        <v>29.5776</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4422</v>
+        <v>0.4371</v>
       </c>
       <c r="J98" t="n">
-        <v>11.4972</v>
+        <v>11.3646</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3363</v>
+        <v>0.3401</v>
       </c>
       <c r="J99" t="n">
-        <v>8.7438</v>
+        <v>8.842599999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1905</v>
+        <v>0.2041</v>
       </c>
       <c r="J100" t="n">
-        <v>4.953</v>
+        <v>5.3066</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.091</v>
+        <v>0.1087</v>
       </c>
       <c r="J101" t="n">
-        <v>2.366</v>
+        <v>2.8262</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8808</v>
+        <v>0.8727</v>
       </c>
       <c r="J102" t="n">
-        <v>14.9736</v>
+        <v>14.8359</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.75</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8232</v>
+        <v>0.8196</v>
       </c>
       <c r="J103" t="n">
-        <v>13.9944</v>
+        <v>13.9332</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.63</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7069</v>
+        <v>0.7116</v>
       </c>
       <c r="J104" t="n">
-        <v>12.0173</v>
+        <v>12.0972</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.59</v>
       </c>
       <c r="I105" t="n">
-        <v>0.668</v>
+        <v>0.6752</v>
       </c>
       <c r="J105" t="n">
-        <v>11.356</v>
+        <v>11.4784</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1368</v>
+        <v>-0.1371</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.3256</v>
+        <v>-2.3307</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.82</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1745</v>
+        <v>-0.1981</v>
       </c>
       <c r="J107" t="n">
-        <v>-2.9665</v>
+        <v>-3.3677</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2574</v>
+        <v>-0.279</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.3758</v>
+        <v>-4.743</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2574</v>
+        <v>-0.279</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.3758</v>
+        <v>-4.743</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.65</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.34</v>
+        <v>-0.3593</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.78</v>
+        <v>-6.1081</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5173</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.7941</v>
+        <v>-8.953900000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.23</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.4954</v>
       </c>
       <c r="J112" t="n">
-        <v>13.2236</v>
+        <v>12.8804</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.18</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4156</v>
+        <v>0.4095</v>
       </c>
       <c r="J113" t="n">
-        <v>10.8056</v>
+        <v>10.647</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1514</v>
+        <v>-0.1656</v>
       </c>
       <c r="J114" t="n">
-        <v>-3.9364</v>
+        <v>-4.3056</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2736</v>
+        <v>-0.2875</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.1136</v>
+        <v>-7.475</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.74</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.293</v>
+        <v>-0.3065</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.618</v>
+        <v>-7.969</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1989</v>
+        <v>1.1645</v>
       </c>
       <c r="J117" t="n">
-        <v>31.1714</v>
+        <v>30.277</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.31</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8237</v>
+        <v>0.7781</v>
       </c>
       <c r="J118" t="n">
-        <v>21.4162</v>
+        <v>20.2306</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.14</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4161</v>
+        <v>0.4133</v>
       </c>
       <c r="J119" t="n">
-        <v>10.8186</v>
+        <v>10.7458</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2207</v>
+        <v>0.2327</v>
       </c>
       <c r="J120" t="n">
-        <v>5.7382</v>
+        <v>6.0502</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6172</v>
+        <v>-0.5748</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.0472</v>
+        <v>-14.9448</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7622</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>22.866</v>
+        <v>25.146</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3747</v>
+        <v>0.3981</v>
       </c>
       <c r="J123" t="n">
-        <v>11.241</v>
+        <v>11.943</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2382</v>
+        <v>0.2447</v>
       </c>
       <c r="J124" t="n">
-        <v>7.146</v>
+        <v>7.341</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1909</v>
+        <v>-0.1871</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.727</v>
+        <v>-5.613</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2564</v>
+        <v>-0.2494</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.692</v>
+        <v>-7.482</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.46</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6563</v>
+        <v>0.732</v>
       </c>
       <c r="J127" t="n">
-        <v>19.689</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0513</v>
+        <v>-0.0592</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.539</v>
+        <v>-1.776</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1132</v>
+        <v>-0.1248</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.396</v>
+        <v>-3.744</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1358</v>
+        <v>-0.1481</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.074</v>
+        <v>-4.443</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2205</v>
+        <v>-0.2336</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.615</v>
+        <v>-7.008</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0272</v>
+        <v>1.1257</v>
       </c>
       <c r="J132" t="n">
-        <v>26.7072</v>
+        <v>29.2682</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4271</v>
+        <v>0.4709</v>
       </c>
       <c r="J133" t="n">
-        <v>11.1046</v>
+        <v>12.2434</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3978</v>
+        <v>0.4345</v>
       </c>
       <c r="J134" t="n">
-        <v>10.3428</v>
+        <v>11.297</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.251</v>
+        <v>0.261</v>
       </c>
       <c r="J135" t="n">
-        <v>6.526</v>
+        <v>6.786</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5367</v>
+        <v>-0.5027</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.9542</v>
+        <v>-13.0702</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2854</v>
+        <v>0.2856</v>
       </c>
       <c r="J137" t="n">
-        <v>7.4204</v>
+        <v>7.4256</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2003</v>
+        <v>0.2037</v>
       </c>
       <c r="J138" t="n">
-        <v>5.2078</v>
+        <v>5.2962</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.93</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.094</v>
+        <v>-0.1069</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.444</v>
+        <v>-2.7794</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2112</v>
+        <v>-0.2264</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.4912</v>
+        <v>-5.8864</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2806</v>
+        <v>-0.2949</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.2956</v>
+        <v>-7.6674</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4444</v>
+        <v>0.49</v>
       </c>
       <c r="J142" t="n">
-        <v>12.4432</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.3792</v>
+        <v>0.4057</v>
       </c>
       <c r="J143" t="n">
-        <v>10.6176</v>
+        <v>11.3596</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2053</v>
+        <v>-0.2196</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.7484</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.82</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2155</v>
+        <v>-0.2298</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.034</v>
+        <v>-6.4344</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2457</v>
+        <v>-0.2597</v>
       </c>
       <c r="J146" t="n">
-        <v>-6.8796</v>
+        <v>-7.2716</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0313</v>
+        <v>1.125</v>
       </c>
       <c r="J147" t="n">
-        <v>28.8764</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.19</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4685</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>13.118</v>
+        <v>14.4088</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1522</v>
+        <v>-0.1507</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.2616</v>
+        <v>-4.2196</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3441</v>
+        <v>-0.3321</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.6348</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7484</v>
+        <v>-0.6953</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.9552</v>
+        <v>-19.4684</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4249</v>
+        <v>0.4812</v>
       </c>
       <c r="J152" t="n">
-        <v>12.3221</v>
+        <v>13.9548</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3559</v>
+        <v>0.3848</v>
       </c>
       <c r="J153" t="n">
-        <v>10.3211</v>
+        <v>11.1592</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2491</v>
+        <v>0.2659</v>
       </c>
       <c r="J154" t="n">
-        <v>7.2239</v>
+        <v>7.7111</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.09</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1436</v>
+        <v>0.1601</v>
       </c>
       <c r="J155" t="n">
-        <v>4.1644</v>
+        <v>4.6429</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2042</v>
+        <v>-0.2142</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.9218</v>
+        <v>-6.2118</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3258</v>
+        <v>0.3312</v>
       </c>
       <c r="J157" t="n">
-        <v>9.4482</v>
+        <v>9.604799999999999</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.1286</v>
+        <v>-2.4418</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.92</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1089</v>
+        <v>-0.1215</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.1581</v>
+        <v>-3.5235</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.91</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1202</v>
+        <v>-0.1332</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.4858</v>
+        <v>-3.8628</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1314</v>
+        <v>-0.1447</v>
       </c>
       <c r="J161" t="n">
-        <v>-3.8106</v>
+        <v>-4.1963</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.23</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4483</v>
+        <v>0.4911</v>
       </c>
       <c r="J162" t="n">
-        <v>12.5524</v>
+        <v>13.7508</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3312</v>
+        <v>0.3304</v>
       </c>
       <c r="J163" t="n">
-        <v>9.2736</v>
+        <v>9.251200000000001</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1569</v>
+        <v>-0.1725</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.3932</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2383</v>
+        <v>-0.254</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.6724</v>
+        <v>-7.112</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4745</v>
+        <v>-0.4818</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.286</v>
+        <v>-13.4904</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.25</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5401</v>
+        <v>0.5984</v>
       </c>
       <c r="J167" t="n">
-        <v>15.1228</v>
+        <v>16.7552</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.498</v>
+        <v>0.5513</v>
       </c>
       <c r="J168" t="n">
-        <v>13.944</v>
+        <v>15.4364</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4554</v>
+        <v>0.5033</v>
       </c>
       <c r="J169" t="n">
-        <v>12.7512</v>
+        <v>14.0924</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.13</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3672</v>
+        <v>0.3896</v>
       </c>
       <c r="J170" t="n">
-        <v>10.2816</v>
+        <v>10.9088</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I171" t="n">
-        <v>0.251</v>
+        <v>0.261</v>
       </c>
       <c r="J171" t="n">
-        <v>7.028</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0355</v>
+        <v>-0.0547</v>
       </c>
       <c r="J172" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-1.1487</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.82</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.1873</v>
+        <v>-0.2081</v>
       </c>
       <c r="J173" t="n">
-        <v>-3.9333</v>
+        <v>-4.3701</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1977</v>
+        <v>-0.2184</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.1517</v>
+        <v>-4.5864</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2079</v>
+        <v>-0.2285</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.3659</v>
+        <v>-4.7985</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.32</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6553</v>
+        <v>-0.6535</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.7613</v>
+        <v>-13.7235</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8112</v>
+        <v>0.8057</v>
       </c>
       <c r="J177" t="n">
-        <v>17.0352</v>
+        <v>16.9197</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7312</v>
+        <v>0.7317</v>
       </c>
       <c r="J178" t="n">
-        <v>15.3552</v>
+        <v>15.3657</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.61</v>
       </c>
       <c r="I179" t="n">
-        <v>0.701</v>
+        <v>0.7036</v>
       </c>
       <c r="J179" t="n">
-        <v>14.721</v>
+        <v>14.7756</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3664</v>
+        <v>0.3862</v>
       </c>
       <c r="J180" t="n">
-        <v>7.6944</v>
+        <v>8.110200000000001</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.86</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2172</v>
+        <v>-0.2221</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.5612</v>
+        <v>-4.6641</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1526</v>
+        <v>1.1189</v>
       </c>
       <c r="J182" t="n">
-        <v>33.4254</v>
+        <v>32.4481</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.36</v>
       </c>
       <c r="I183" t="n">
-        <v>0.9117</v>
+        <v>0.86</v>
       </c>
       <c r="J183" t="n">
-        <v>26.4393</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6212</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="J184" t="n">
-        <v>18.0148</v>
+        <v>17.4667</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3973</v>
+        <v>0.4004</v>
       </c>
       <c r="J185" t="n">
-        <v>11.5217</v>
+        <v>11.6116</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1691</v>
+        <v>0.1892</v>
       </c>
       <c r="J186" t="n">
-        <v>4.9039</v>
+        <v>5.4868</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.02</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1029</v>
+        <v>0.1001</v>
       </c>
       <c r="J187" t="n">
-        <v>2.9841</v>
+        <v>2.9029</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.92</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0978</v>
+        <v>-0.1131</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.8362</v>
+        <v>-3.2799</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.0978</v>
+        <v>-0.1131</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.8362</v>
+        <v>-3.2799</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1093</v>
+        <v>-0.1249</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.1697</v>
+        <v>-3.6221</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4775</v>
+        <v>-0.4856</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.8475</v>
+        <v>-14.0824</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.59</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2567</v>
+        <v>1.2272</v>
       </c>
       <c r="J192" t="n">
-        <v>36.4443</v>
+        <v>35.5888</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7946</v>
+        <v>0.7537</v>
       </c>
       <c r="J193" t="n">
-        <v>23.0434</v>
+        <v>21.8573</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.12</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3587</v>
+        <v>0.3618</v>
       </c>
       <c r="J194" t="n">
-        <v>10.4023</v>
+        <v>10.4922</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2458</v>
+        <v>0.2573</v>
       </c>
       <c r="J195" t="n">
-        <v>7.1282</v>
+        <v>7.4617</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.89</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4312</v>
+        <v>-0.4058</v>
       </c>
       <c r="J196" t="n">
-        <v>-12.5048</v>
+        <v>-11.7682</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3391</v>
+        <v>0.3378</v>
       </c>
       <c r="J197" t="n">
-        <v>9.8339</v>
+        <v>9.796200000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1494</v>
+        <v>0.1552</v>
       </c>
       <c r="J198" t="n">
-        <v>4.3326</v>
+        <v>4.5008</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1257</v>
+        <v>0.1316</v>
       </c>
       <c r="J199" t="n">
-        <v>3.6453</v>
+        <v>3.8164</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.101</v>
+        <v>0.1066</v>
       </c>
       <c r="J200" t="n">
-        <v>2.929</v>
+        <v>3.0914</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.4973</v>
+        <v>-0.5027</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.4217</v>
+        <v>-14.5783</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5344</v>
+        <v>0.5144</v>
       </c>
       <c r="J202" t="n">
-        <v>12.8256</v>
+        <v>12.3456</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.0098</v>
+        <v>-0.017</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.2352</v>
+        <v>-0.408</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2066</v>
+        <v>-0.2229</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.9584</v>
+        <v>-5.3496</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2758</v>
+        <v>-0.2912</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.6192</v>
+        <v>-6.9888</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3239</v>
+        <v>-0.338</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.7736</v>
+        <v>-8.112</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3369</v>
+        <v>1.3157</v>
       </c>
       <c r="J207" t="n">
-        <v>32.0856</v>
+        <v>31.5768</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1643</v>
+        <v>1.1316</v>
       </c>
       <c r="J208" t="n">
-        <v>27.9432</v>
+        <v>27.1584</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.6018</v>
       </c>
       <c r="J209" t="n">
-        <v>14.892</v>
+        <v>14.4432</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1198</v>
+        <v>-0.1047</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.8752</v>
+        <v>-2.5128</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3902</v>
+        <v>-0.3644</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.364800000000001</v>
+        <v>-8.7456</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4707</v>
+        <v>0.4572</v>
       </c>
       <c r="J212" t="n">
-        <v>12.2382</v>
+        <v>11.8872</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0121</v>
+        <v>-0.0188</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.3146</v>
+        <v>-0.4888</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0424</v>
+        <v>-0.0524</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.1024</v>
+        <v>-1.3624</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2681</v>
+        <v>-0.2832</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.9706</v>
+        <v>-7.3632</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3732</v>
+        <v>-0.3852</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.703200000000001</v>
+        <v>-10.0152</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9248</v>
+        <v>0.8694</v>
       </c>
       <c r="J217" t="n">
-        <v>24.0448</v>
+        <v>22.6044</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.34</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8807</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>22.8982</v>
+        <v>21.5826</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.24</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6513</v>
+        <v>0.6276</v>
       </c>
       <c r="J219" t="n">
-        <v>16.9338</v>
+        <v>16.3176</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.09</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2707</v>
+        <v>0.2815</v>
       </c>
       <c r="J220" t="n">
-        <v>7.0382</v>
+        <v>7.319</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.04</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1158</v>
+        <v>0.1354</v>
       </c>
       <c r="J221" t="n">
-        <v>3.0108</v>
+        <v>3.5204</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.2214</v>
+        <v>1.1961</v>
       </c>
       <c r="J222" t="n">
-        <v>28.0922</v>
+        <v>27.5103</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.54</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1607</v>
+        <v>1.1309</v>
       </c>
       <c r="J223" t="n">
-        <v>26.6961</v>
+        <v>26.0107</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6279</v>
+        <v>0.6117</v>
       </c>
       <c r="J224" t="n">
-        <v>14.4417</v>
+        <v>14.0691</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6041</v>
+        <v>0.5905</v>
       </c>
       <c r="J225" t="n">
-        <v>13.8943</v>
+        <v>13.5815</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3778</v>
+        <v>0.3869</v>
       </c>
       <c r="J226" t="n">
-        <v>8.689399999999999</v>
+        <v>8.8987</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.07</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2533</v>
+        <v>0.2426</v>
       </c>
       <c r="J227" t="n">
-        <v>5.8259</v>
+        <v>5.5798</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.91</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1</v>
+        <v>-0.1177</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.3</v>
+        <v>-2.7071</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.244</v>
+        <v>-0.2626</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.612</v>
+        <v>-6.0398</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.66</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3487</v>
+        <v>-0.3643</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.020099999999999</v>
+        <v>-8.3789</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.405</v>
+        <v>-0.4181</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.315</v>
+        <v>-9.616300000000001</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.7</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3636</v>
+        <v>1.3456</v>
       </c>
       <c r="J232" t="n">
-        <v>29.9992</v>
+        <v>29.6032</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2912</v>
+        <v>1.2688</v>
       </c>
       <c r="J233" t="n">
-        <v>28.4064</v>
+        <v>27.9136</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.516</v>
+        <v>0.5097</v>
       </c>
       <c r="J234" t="n">
-        <v>11.352</v>
+        <v>11.2134</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.1203</v>
       </c>
       <c r="J235" t="n">
-        <v>2.0724</v>
+        <v>2.6466</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2754</v>
+        <v>-0.2548</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.0588</v>
+        <v>-5.6056</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2888</v>
+        <v>0.2788</v>
       </c>
       <c r="J237" t="n">
-        <v>6.3536</v>
+        <v>6.1336</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.0673</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.4806</v>
+        <v>-1.8282</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1689</v>
+        <v>-0.1869</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.7158</v>
+        <v>-4.1118</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2465</v>
+        <v>-0.2644</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.423</v>
+        <v>-5.8168</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.46</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5421</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.8096</v>
+        <v>-11.9262</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.02</v>
       </c>
       <c r="I242" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J242" t="n">
-        <v>2.6332</v>
+        <v>2.6477</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.96</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0535</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.5515</v>
+        <v>-1.8879</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0788</v>
+        <v>-0.0919</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.2852</v>
+        <v>-2.6651</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.87</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1553</v>
+        <v>-0.1712</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.5037</v>
+        <v>-4.9648</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3332</v>
+        <v>-0.347</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.662800000000001</v>
+        <v>-10.063</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2511</v>
+        <v>1.2245</v>
       </c>
       <c r="J247" t="n">
-        <v>36.2819</v>
+        <v>35.5105</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.57</v>
       </c>
       <c r="I248" t="n">
-        <v>1.214</v>
+        <v>1.1849</v>
       </c>
       <c r="J248" t="n">
-        <v>35.206</v>
+        <v>34.3621</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5241</v>
+        <v>0.5154</v>
       </c>
       <c r="J249" t="n">
-        <v>15.1989</v>
+        <v>14.9466</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3697</v>
+        <v>0.3754</v>
       </c>
       <c r="J250" t="n">
-        <v>10.7213</v>
+        <v>10.8866</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5855</v>
+        <v>-0.5423</v>
       </c>
       <c r="J251" t="n">
-        <v>-16.9795</v>
+        <v>-15.7267</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.91</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0712</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.5664</v>
+        <v>-2.0944</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.76</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2382</v>
+        <v>-0.2603</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.2404</v>
+        <v>-5.7266</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.68</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3136</v>
+        <v>-0.3336</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.8992</v>
+        <v>-7.3392</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.58</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4056</v>
+        <v>-0.4217</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.9232</v>
+        <v>-9.2774</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.5</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4805</v>
+        <v>-0.4922</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.571</v>
+        <v>-10.8284</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.04</v>
       </c>
       <c r="I257" t="n">
-        <v>1.7264</v>
+        <v>1.7314</v>
       </c>
       <c r="J257" t="n">
-        <v>37.9808</v>
+        <v>38.0908</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.42</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9972</v>
+        <v>0.9492</v>
       </c>
       <c r="J258" t="n">
-        <v>21.9384</v>
+        <v>20.8824</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.39</v>
       </c>
       <c r="I259" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.8965</v>
       </c>
       <c r="J259" t="n">
-        <v>20.7922</v>
+        <v>19.723</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3613</v>
+        <v>0.3753</v>
       </c>
       <c r="J260" t="n">
-        <v>7.9486</v>
+        <v>8.256600000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.13</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3345</v>
+        <v>0.3509</v>
       </c>
       <c r="J261" t="n">
-        <v>7.359</v>
+        <v>7.7198</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3144</v>
+        <v>0.3112</v>
       </c>
       <c r="J262" t="n">
-        <v>7.5456</v>
+        <v>7.4688</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.05</v>
       </c>
       <c r="I263" t="n">
-        <v>0.162</v>
+        <v>0.1644</v>
       </c>
       <c r="J263" t="n">
-        <v>3.888</v>
+        <v>3.9456</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2184</v>
+        <v>-0.2342</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.2416</v>
+        <v>-5.6208</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.8</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2284</v>
+        <v>-0.2441</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.4816</v>
+        <v>-5.8584</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2482</v>
+        <v>-0.2637</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.9568</v>
+        <v>-6.3288</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.49</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1087</v>
+        <v>1.0727</v>
       </c>
       <c r="J267" t="n">
-        <v>26.6088</v>
+        <v>25.7448</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.48</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0961</v>
+        <v>1.0588</v>
       </c>
       <c r="J268" t="n">
-        <v>26.3064</v>
+        <v>25.4112</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.35</v>
       </c>
       <c r="I269" t="n">
-        <v>0.8827</v>
+        <v>0.8356</v>
       </c>
       <c r="J269" t="n">
-        <v>21.1848</v>
+        <v>20.0544</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.4163</v>
+        <v>0.4193</v>
       </c>
       <c r="J270" t="n">
-        <v>9.991199999999999</v>
+        <v>10.0632</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0495</v>
       </c>
       <c r="J271" t="n">
-        <v>-1.7136</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.31</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6409</v>
+        <v>0.6178</v>
       </c>
       <c r="J272" t="n">
-        <v>16.0225</v>
+        <v>15.445</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.444</v>
+        <v>0.4376</v>
       </c>
       <c r="J273" t="n">
-        <v>11.1</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.92</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.11</v>
+        <v>-0.1223</v>
       </c>
       <c r="J274" t="n">
-        <v>-2.75</v>
+        <v>-3.0575</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.82</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.217</v>
+        <v>-0.2309</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.425</v>
+        <v>-5.7725</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3627</v>
+        <v>-0.3736</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.067500000000001</v>
+        <v>-9.34</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>1.0322</v>
+        <v>0.9737</v>
       </c>
       <c r="J277" t="n">
-        <v>25.805</v>
+        <v>24.3425</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.6062</v>
+        <v>0.5819</v>
       </c>
       <c r="J278" t="n">
-        <v>15.155</v>
+        <v>14.5475</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3754</v>
+        <v>0.3731</v>
       </c>
       <c r="J279" t="n">
-        <v>9.385</v>
+        <v>9.327500000000001</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0793</v>
+        <v>-0.0765</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.9825</v>
+        <v>-1.9125</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6253</v>
+        <v>-0.5855</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.6325</v>
+        <v>-14.6375</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2427</v>
+        <v>0.2348</v>
       </c>
       <c r="J282" t="n">
-        <v>5.8248</v>
+        <v>5.6352</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.95</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0549</v>
+        <v>-0.0699</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.3176</v>
+        <v>-1.6776</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.79</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2274</v>
+        <v>-0.2455</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.4576</v>
+        <v>-5.892</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.74</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2757</v>
+        <v>-0.293</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.6168</v>
+        <v>-7.032</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.436</v>
+        <v>-0.4471</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.464</v>
+        <v>-10.7304</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0562</v>
+        <v>1.0095</v>
       </c>
       <c r="J287" t="n">
-        <v>25.3488</v>
+        <v>24.228</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8296</v>
+        <v>0.7864</v>
       </c>
       <c r="J288" t="n">
-        <v>19.9104</v>
+        <v>18.8736</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.24</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6478</v>
+        <v>0.6253</v>
       </c>
       <c r="J289" t="n">
-        <v>15.5472</v>
+        <v>15.0072</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3766</v>
+        <v>0.3802</v>
       </c>
       <c r="J290" t="n">
-        <v>9.038399999999999</v>
+        <v>9.1248</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1435</v>
+        <v>0.1634</v>
       </c>
       <c r="J291" t="n">
-        <v>3.444</v>
+        <v>3.9216</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.707</v>
+        <v>0.661</v>
       </c>
       <c r="J292" t="n">
-        <v>15.554</v>
+        <v>14.542</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1572</v>
+        <v>0.1476</v>
       </c>
       <c r="J293" t="n">
-        <v>3.4584</v>
+        <v>3.2472</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2719</v>
+        <v>-0.2901</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.9818</v>
+        <v>-6.3822</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5336</v>
+        <v>-0.5396</v>
       </c>
       <c r="J295" t="n">
-        <v>-11.7392</v>
+        <v>-11.8712</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.46</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5336</v>
+        <v>-0.5396</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.7392</v>
+        <v>-11.8712</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.62</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2625</v>
+        <v>1.2391</v>
       </c>
       <c r="J297" t="n">
-        <v>27.775</v>
+        <v>27.2602</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.55</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1773</v>
+        <v>1.1479</v>
       </c>
       <c r="J298" t="n">
-        <v>25.9006</v>
+        <v>25.2538</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.24</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6328</v>
+        <v>0.6151</v>
       </c>
       <c r="J299" t="n">
-        <v>13.9216</v>
+        <v>13.5322</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.4356</v>
+        <v>0.4381</v>
       </c>
       <c r="J300" t="n">
-        <v>9.5832</v>
+        <v>9.638199999999999</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.05</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1227</v>
+        <v>0.1488</v>
       </c>
       <c r="J301" t="n">
-        <v>2.6994</v>
+        <v>3.2736</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4016</v>
+        <v>0.3954</v>
       </c>
       <c r="J302" t="n">
-        <v>11.2448</v>
+        <v>11.0712</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.14</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3432</v>
+        <v>0.3408</v>
       </c>
       <c r="J303" t="n">
-        <v>9.6096</v>
+        <v>9.542400000000001</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0159</v>
+        <v>-0.0217</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.4452</v>
+        <v>-0.6076</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.202</v>
+        <v>-0.217</v>
       </c>
       <c r="J305" t="n">
-        <v>-5.656</v>
+        <v>-6.076</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.59</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4324</v>
+        <v>-0.4412</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.1072</v>
+        <v>-12.3536</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.58</v>
       </c>
       <c r="I307" t="n">
-        <v>1.251</v>
+        <v>1.2198</v>
       </c>
       <c r="J307" t="n">
-        <v>35.028</v>
+        <v>34.1544</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0572</v>
+        <v>1.0075</v>
       </c>
       <c r="J308" t="n">
-        <v>29.6016</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.16</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4677</v>
+        <v>0.4602</v>
       </c>
       <c r="J309" t="n">
-        <v>13.0956</v>
+        <v>12.8856</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.88</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4535</v>
+        <v>-0.4274</v>
       </c>
       <c r="J310" t="n">
-        <v>-12.698</v>
+        <v>-11.9672</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.6424</v>
+        <v>-0.5975</v>
       </c>
       <c r="J311" t="n">
-        <v>-17.9872</v>
+        <v>-16.73</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5367</v>
+        <v>0.5258</v>
       </c>
       <c r="J312" t="n">
-        <v>15.0276</v>
+        <v>14.7224</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.23</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4836</v>
+        <v>0.4771</v>
       </c>
       <c r="J313" t="n">
-        <v>13.5408</v>
+        <v>13.3588</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.02</v>
       </c>
       <c r="I314" t="n">
-        <v>0.0626</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J314" t="n">
-        <v>1.7528</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2121</v>
+        <v>-0.2249</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.9388</v>
+        <v>-6.2972</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2324</v>
+        <v>-0.2451</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.5072</v>
+        <v>-6.8628</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.6</v>
       </c>
       <c r="I317" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="J317" t="n">
-        <v>35.84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.24</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6637</v>
+        <v>0.6362</v>
       </c>
       <c r="J318" t="n">
-        <v>18.5836</v>
+        <v>17.8136</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.09</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2834</v>
+        <v>0.2903</v>
       </c>
       <c r="J319" t="n">
-        <v>7.9352</v>
+        <v>8.128399999999999</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.97</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1718</v>
+        <v>-0.1644</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.8104</v>
+        <v>-4.6032</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.9</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.3933</v>
+        <v>-0.373</v>
       </c>
       <c r="J321" t="n">
-        <v>-11.0124</v>
+        <v>-10.444</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.13</v>
       </c>
       <c r="I322" t="n">
-        <v>0.24</v>
+        <v>0.2468</v>
       </c>
       <c r="J322" t="n">
-        <v>7.2</v>
+        <v>7.404</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.0929</v>
+        <v>0.1006</v>
       </c>
       <c r="J323" t="n">
-        <v>2.787</v>
+        <v>3.018</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0321</v>
+        <v>0.0363</v>
       </c>
       <c r="J324" t="n">
-        <v>0.963</v>
+        <v>1.089</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1202</v>
+        <v>-0.1332</v>
       </c>
       <c r="J325" t="n">
-        <v>-3.606</v>
+        <v>-3.996</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2558</v>
+        <v>-0.2697</v>
       </c>
       <c r="J326" t="n">
-        <v>-7.674</v>
+        <v>-8.090999999999999</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.6</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7665</v>
+        <v>0.7523</v>
       </c>
       <c r="J327" t="n">
-        <v>22.995</v>
+        <v>22.569</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.122</v>
+        <v>0.1359</v>
       </c>
       <c r="J328" t="n">
-        <v>3.66</v>
+        <v>4.077</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.03</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0579</v>
+        <v>0.0688</v>
       </c>
       <c r="J329" t="n">
-        <v>1.737</v>
+        <v>2.064</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1753</v>
+        <v>-0.1868</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.259</v>
+        <v>-5.604</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2375</v>
+        <v>-0.2491</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.125</v>
+        <v>-7.473</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.58</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2458</v>
+        <v>1.2153</v>
       </c>
       <c r="J332" t="n">
-        <v>36.1282</v>
+        <v>35.2437</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.24</v>
       </c>
       <c r="I333" t="n">
-        <v>0.6562</v>
+        <v>0.631</v>
       </c>
       <c r="J333" t="n">
-        <v>19.0298</v>
+        <v>18.299</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.12</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3601</v>
+        <v>0.3627</v>
       </c>
       <c r="J334" t="n">
-        <v>10.4429</v>
+        <v>10.5183</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.02</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0499</v>
+        <v>0.0694</v>
       </c>
       <c r="J335" t="n">
-        <v>1.4471</v>
+        <v>2.0126</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.101</v>
+        <v>-0.0916</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.929</v>
+        <v>-2.6564</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.17</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4287</v>
+        <v>0.4154</v>
       </c>
       <c r="J337" t="n">
-        <v>12.4323</v>
+        <v>12.0466</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.0639</v>
+        <v>-0.077</v>
       </c>
       <c r="J338" t="n">
-        <v>-1.8531</v>
+        <v>-2.233</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.89</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1333</v>
+        <v>-0.149</v>
       </c>
       <c r="J339" t="n">
-        <v>-3.8657</v>
+        <v>-4.321</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2142</v>
+        <v>-0.231</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.2118</v>
+        <v>-6.699</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.57</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.443</v>
+        <v>-0.4526</v>
       </c>
       <c r="J341" t="n">
-        <v>-12.847</v>
+        <v>-13.1254</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.59</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2631</v>
+        <v>1.2328</v>
       </c>
       <c r="J342" t="n">
-        <v>36.6299</v>
+        <v>35.7512</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8933</v>
+        <v>0.8389</v>
       </c>
       <c r="J343" t="n">
-        <v>25.9057</v>
+        <v>24.3281</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5159</v>
+        <v>0.5043</v>
       </c>
       <c r="J344" t="n">
-        <v>14.9611</v>
+        <v>14.6247</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.9</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3969</v>
+        <v>-0.3755</v>
       </c>
       <c r="J345" t="n">
-        <v>-11.5101</v>
+        <v>-10.8895</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.86</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5095</v>
+        <v>-0.4781</v>
       </c>
       <c r="J346" t="n">
-        <v>-14.7755</v>
+        <v>-13.8649</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.46</v>
+        <v>0.4494</v>
       </c>
       <c r="J347" t="n">
-        <v>13.34</v>
+        <v>13.0326</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.07</v>
       </c>
       <c r="I348" t="n">
-        <v>0.1991</v>
+        <v>0.2029</v>
       </c>
       <c r="J348" t="n">
-        <v>5.7739</v>
+        <v>5.8841</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.02</v>
       </c>
       <c r="I349" t="n">
-        <v>0.0785</v>
+        <v>0.0823</v>
       </c>
       <c r="J349" t="n">
-        <v>2.2765</v>
+        <v>2.3867</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3101</v>
+        <v>-0.3236</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.992900000000001</v>
+        <v>-9.384399999999999</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3387</v>
+        <v>-0.3513</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.8223</v>
+        <v>-10.1877</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.53</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1481</v>
+        <v>1.1175</v>
       </c>
       <c r="J352" t="n">
-        <v>27.5544</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.52</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1359</v>
+        <v>1.1043</v>
       </c>
       <c r="J353" t="n">
-        <v>27.2616</v>
+        <v>26.5032</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0491</v>
+        <v>1.0058</v>
       </c>
       <c r="J354" t="n">
-        <v>25.1784</v>
+        <v>24.1392</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.2</v>
       </c>
       <c r="I355" t="n">
-        <v>0.5308</v>
+        <v>0.5251</v>
       </c>
       <c r="J355" t="n">
-        <v>12.7392</v>
+        <v>12.6024</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.05</v>
       </c>
       <c r="I356" t="n">
-        <v>0.1168</v>
+        <v>0.1447</v>
       </c>
       <c r="J356" t="n">
-        <v>2.8032</v>
+        <v>3.4728</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.07</v>
       </c>
       <c r="I357" t="n">
-        <v>0.2638</v>
+        <v>0.2503</v>
       </c>
       <c r="J357" t="n">
-        <v>6.3312</v>
+        <v>6.0072</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1525</v>
+        <v>-0.1718</v>
       </c>
       <c r="J358" t="n">
-        <v>-3.66</v>
+        <v>-4.1232</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.85</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1632</v>
+        <v>-0.1825</v>
       </c>
       <c r="J359" t="n">
-        <v>-3.9168</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.62</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.3834</v>
+        <v>-0.398</v>
       </c>
       <c r="J360" t="n">
-        <v>-9.201599999999999</v>
+        <v>-9.552</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.51</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4858</v>
+        <v>-0.495</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.6592</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.926</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="J362" t="n">
-        <v>25.002</v>
+        <v>23.3928</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4464</v>
+        <v>0.4399</v>
       </c>
       <c r="J363" t="n">
-        <v>12.0528</v>
+        <v>11.8773</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.14</v>
       </c>
       <c r="I364" t="n">
-        <v>0.4216</v>
+        <v>0.4171</v>
       </c>
       <c r="J364" t="n">
-        <v>11.3832</v>
+        <v>11.2617</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.287</v>
+        <v>0.2928</v>
       </c>
       <c r="J365" t="n">
-        <v>7.749</v>
+        <v>7.9056</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.0892</v>
+        <v>-0.0834</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.4084</v>
+        <v>-2.2518</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.6005</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J367" t="n">
-        <v>16.2135</v>
+        <v>15.6357</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.26</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5647</v>
+        <v>0.5464</v>
       </c>
       <c r="J368" t="n">
-        <v>15.2469</v>
+        <v>14.7528</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1292</v>
+        <v>-0.1431</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.4884</v>
+        <v>-3.8637</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.72</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3118</v>
+        <v>-0.3249</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.4186</v>
+        <v>-8.7723</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.61</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4151</v>
+        <v>-0.4245</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.2077</v>
+        <v>-11.4615</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.76</v>
       </c>
       <c r="I372" t="n">
-        <v>1.4523</v>
+        <v>1.4364</v>
       </c>
       <c r="J372" t="n">
-        <v>36.3075</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.19</v>
       </c>
       <c r="I373" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5185</v>
       </c>
       <c r="J373" t="n">
-        <v>13.2175</v>
+        <v>12.9625</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.16</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4534</v>
+        <v>0.4505</v>
       </c>
       <c r="J374" t="n">
-        <v>11.335</v>
+        <v>11.2625</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.3477</v>
+        <v>0.3542</v>
       </c>
       <c r="J375" t="n">
-        <v>8.692500000000001</v>
+        <v>8.855</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.99</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.1145</v>
+        <v>-0.101</v>
       </c>
       <c r="J376" t="n">
-        <v>-2.8625</v>
+        <v>-2.525</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>0.9</v>
       </c>
       <c r="I377" t="n">
-        <v>-0.1123</v>
+        <v>-0.1301</v>
       </c>
       <c r="J377" t="n">
-        <v>-2.8075</v>
+        <v>-3.2525</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.87</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1457</v>
+        <v>-0.1639</v>
       </c>
       <c r="J378" t="n">
-        <v>-3.6425</v>
+        <v>-4.0975</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.85</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1669</v>
+        <v>-0.1853</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.1725</v>
+        <v>-4.6325</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.73</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.2828</v>
+        <v>-0.3005</v>
       </c>
       <c r="J380" t="n">
-        <v>-7.07</v>
+        <v>-7.5125</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.68</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3304</v>
+        <v>-0.3466</v>
       </c>
       <c r="J381" t="n">
-        <v>-8.26</v>
+        <v>-8.664999999999999</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.6747</v>
+        <v>0.6345</v>
       </c>
       <c r="J382" t="n">
-        <v>18.8916</v>
+        <v>17.766</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.06</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2302</v>
+        <v>0.2313</v>
       </c>
       <c r="J383" t="n">
-        <v>6.4456</v>
+        <v>6.4764</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1634</v>
+        <v>-0.1681</v>
       </c>
       <c r="J384" t="n">
-        <v>-4.5752</v>
+        <v>-4.7068</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.9</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.3477</v>
+        <v>-0.3412</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.7356</v>
+        <v>-9.553599999999999</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.84</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.5142</v>
+        <v>-0.4923</v>
       </c>
       <c r="J386" t="n">
-        <v>-14.3976</v>
+        <v>-13.7844</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.31</v>
       </c>
       <c r="I387" t="n">
-        <v>0.6125</v>
+        <v>0.597</v>
       </c>
       <c r="J387" t="n">
-        <v>17.15</v>
+        <v>16.716</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.17</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3663</v>
+        <v>0.3697</v>
       </c>
       <c r="J388" t="n">
-        <v>10.2564</v>
+        <v>10.3516</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.03</v>
       </c>
       <c r="I389" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J389" t="n">
-        <v>2.3408</v>
+        <v>2.6376</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.96</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.07729999999999999</v>
       </c>
       <c r="J390" t="n">
-        <v>-1.946</v>
+        <v>-2.1644</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.2053</v>
+        <v>-0.2174</v>
       </c>
       <c r="J391" t="n">
-        <v>-5.7484</v>
+        <v>-6.0872</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5339/event_5339_evp_summary.xlsx
+++ b/database/event/5339/event_5339_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2741</v>
+        <v>6.1806</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3367</v>
+        <v>1.3167</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2319</v>
+        <v>2.2098</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2741</v>
+        <v>6.1806</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7895</v>
+        <v>3.6352</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4846</v>
+        <v>2.5454</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6086</v>
+        <v>7.2054</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1086</v>
+        <v>4.0456</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4846</v>
+        <v>2.5454</v>
       </c>
       <c r="K2" t="n">
         <v>192</v>
@@ -529,7 +529,7 @@
         <v>77</v>
       </c>
       <c r="M2" t="n">
-        <v>6.5932</v>
+        <v>6.591</v>
       </c>
       <c r="N2" t="n">
         <v>269</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.2231</v>
+        <v>6.1462</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3258</v>
+        <v>1.3094</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2087</v>
+        <v>2.1941</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2231</v>
+        <v>6.1462</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4832</v>
+        <v>3.372</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7399</v>
+        <v>2.7742</v>
       </c>
       <c r="H3" t="n">
-        <v>6.5981</v>
+        <v>6.2174</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5629</v>
+        <v>3.4909</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7399</v>
+        <v>2.7742</v>
       </c>
       <c r="K3" t="n">
         <v>192</v>
@@ -575,7 +575,7 @@
         <v>77</v>
       </c>
       <c r="M3" t="n">
-        <v>6.3028</v>
+        <v>6.2651</v>
       </c>
       <c r="N3" t="n">
         <v>269</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.584</v>
+        <v>5.5913</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1896</v>
+        <v>1.1912</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9177</v>
+        <v>1.9413</v>
       </c>
       <c r="E4" t="n">
-        <v>5.584</v>
+        <v>5.5913</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4497</v>
+        <v>3.3801</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1343</v>
+        <v>2.2112</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4875</v>
+        <v>6.2479</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5032</v>
+        <v>3.508</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1343</v>
+        <v>2.2112</v>
       </c>
       <c r="K4" t="n">
         <v>192</v>
@@ -621,7 +621,7 @@
         <v>77</v>
       </c>
       <c r="M4" t="n">
-        <v>5.6375</v>
+        <v>5.7192</v>
       </c>
       <c r="N4" t="n">
         <v>269</v>
@@ -630,185 +630,185 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1033</v>
+        <v>4.8869</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0872</v>
+        <v>1.0411</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6989</v>
+        <v>1.6204</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1033</v>
+        <v>4.8869</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3608</v>
+        <v>4.6003</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7425</v>
+        <v>0.2866</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4937</v>
+        <v>10.8287</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1265</v>
+        <v>6.08</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7425</v>
+        <v>0.2866</v>
       </c>
       <c r="K5" t="n">
-        <v>167</v>
+        <v>338</v>
       </c>
       <c r="L5" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M5" t="n">
-        <v>5.869</v>
+        <v>6.3666</v>
       </c>
       <c r="N5" t="n">
-        <v>252</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9414</v>
+        <v>4.7634</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0527</v>
+        <v>1.0148</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6252</v>
+        <v>1.5642</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9414</v>
+        <v>4.7634</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5807</v>
+        <v>4.0915</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3607</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>11.8283</v>
+        <v>8.918799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>6.3872</v>
+        <v>5.0076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3607</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="L6" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M6" t="n">
-        <v>6.7479</v>
+        <v>5.6795</v>
       </c>
       <c r="N6" t="n">
-        <v>415</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BnTeT</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0617</v>
+        <v>4.0565</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8653</v>
+        <v>0.8642</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2248</v>
+        <v>1.2421</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0617</v>
+        <v>4.0565</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1551</v>
+        <v>3.3371</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0934</v>
+        <v>0.7194</v>
       </c>
       <c r="H7" t="n">
-        <v>8.815099999999999</v>
+        <v>6.0862</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7601</v>
+        <v>3.4172</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0934</v>
+        <v>0.7194</v>
       </c>
       <c r="K7" t="n">
-        <v>338</v>
+        <v>192</v>
       </c>
       <c r="L7" t="n">
         <v>77</v>
       </c>
       <c r="M7" t="n">
-        <v>4.666700000000001</v>
+        <v>4.1366</v>
       </c>
       <c r="N7" t="n">
-        <v>415</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>BnTeT</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0468</v>
+        <v>3.7913</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8621</v>
+        <v>0.8077</v>
       </c>
       <c r="D8" t="n">
-        <v>1.218</v>
+        <v>1.1213</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0468</v>
+        <v>3.7913</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3698</v>
+        <v>3.8855</v>
       </c>
       <c r="G8" t="n">
-        <v>0.677</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>6.224</v>
+        <v>8.145099999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3.3609</v>
+        <v>4.5732</v>
       </c>
       <c r="J8" t="n">
-        <v>0.677</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>192</v>
+        <v>338</v>
       </c>
       <c r="L8" t="n">
         <v>77</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0379</v>
+        <v>4.479</v>
       </c>
       <c r="N8" t="n">
-        <v>269</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6581</v>
+        <v>3.6444</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7793</v>
+        <v>0.7764</v>
       </c>
       <c r="D9" t="n">
-        <v>1.041</v>
+        <v>1.0544</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6581</v>
+        <v>3.6444</v>
       </c>
       <c r="F9" t="n">
-        <v>2.751</v>
+        <v>2.7736</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9071</v>
+        <v>0.8708</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1823</v>
+        <v>3.9708</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2584</v>
+        <v>2.2295</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9071</v>
+        <v>0.8708</v>
       </c>
       <c r="K9" t="n">
         <v>192</v>
@@ -851,7 +851,7 @@
         <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1655</v>
+        <v>3.1003</v>
       </c>
       <c r="N9" t="n">
         <v>269</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6448</v>
+        <v>3.4747</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7765</v>
+        <v>0.7403</v>
       </c>
       <c r="D10" t="n">
-        <v>1.035</v>
+        <v>0.9771</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6448</v>
+        <v>3.4747</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3361</v>
+        <v>3.2819</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3087</v>
+        <v>0.1928</v>
       </c>
       <c r="H10" t="n">
-        <v>6.1127</v>
+        <v>5.879</v>
       </c>
       <c r="I10" t="n">
-        <v>3.3008</v>
+        <v>3.3009</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3087</v>
+        <v>0.1928</v>
       </c>
       <c r="K10" t="n">
         <v>167</v>
@@ -897,7 +897,7 @@
         <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6095</v>
+        <v>3.4937</v>
       </c>
       <c r="N10" t="n">
         <v>252</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2508</v>
+        <v>3.1184</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6926</v>
+        <v>0.6644</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8556</v>
+        <v>0.8148</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2508</v>
+        <v>3.1184</v>
       </c>
       <c r="F11" t="n">
-        <v>3.02</v>
+        <v>2.9552</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2308</v>
+        <v>0.1632</v>
       </c>
       <c r="H11" t="n">
-        <v>5.0699</v>
+        <v>4.6526</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7377</v>
+        <v>2.6123</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2308</v>
+        <v>0.1632</v>
       </c>
       <c r="K11" t="n">
         <v>167</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9685</v>
+        <v>2.7755</v>
       </c>
       <c r="N11" t="n">
         <v>252</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.0669</v>
+        <v>3.1068</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6534</v>
+        <v>0.6619</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7719</v>
+        <v>0.8095</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0669</v>
+        <v>3.1068</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5121</v>
+        <v>2.7079</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5548</v>
+        <v>0.3989</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5121</v>
+        <v>3.7242</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8165</v>
+        <v>2.091</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5548</v>
+        <v>0.3989</v>
       </c>
       <c r="K12" t="n">
         <v>290</v>
@@ -989,7 +989,7 @@
         <v>85</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3713</v>
+        <v>2.4899</v>
       </c>
       <c r="N12" t="n">
         <v>375</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9972</v>
+        <v>2.9463</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6385</v>
+        <v>0.6277</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7402</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9972</v>
+        <v>2.9463</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6337</v>
+        <v>1.3846</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3635</v>
+        <v>1.5617</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7954</v>
+        <v>1.3846</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0495</v>
+        <v>0.7774</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3635</v>
+        <v>1.5617</v>
       </c>
       <c r="K13" t="n">
         <v>290</v>
@@ -1035,7 +1035,7 @@
         <v>85</v>
       </c>
       <c r="M13" t="n">
-        <v>2.413</v>
+        <v>2.3391</v>
       </c>
       <c r="N13" t="n">
         <v>375</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8964</v>
+        <v>2.8025</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6171</v>
+        <v>0.5971</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6943</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8964</v>
+        <v>2.8025</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8964</v>
+        <v>2.3713</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.4312</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6143</v>
+        <v>2.4603</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6143</v>
+        <v>1.3814</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.4312</v>
       </c>
       <c r="K14" t="n">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6143</v>
+        <v>1.8126</v>
       </c>
       <c r="N14" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7468</v>
+        <v>2.789</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5942</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6262</v>
+        <v>0.6647</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7468</v>
+        <v>2.789</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2449</v>
+        <v>2.789</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5019</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5126</v>
+        <v>3.4413</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3568</v>
+        <v>3.4413</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5019</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="L15" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8587</v>
+        <v>3.4413</v>
       </c>
       <c r="N15" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.5314</v>
+        <v>2.4399</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5393</v>
+        <v>0.5198</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5281</v>
+        <v>0.5057</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5314</v>
+        <v>2.4399</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5314</v>
+        <v>2.4399</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8155</v>
+        <v>2.6414</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8881</v>
+        <v>2.7119</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8881</v>
+        <v>2.7119</v>
       </c>
       <c r="N16" t="n">
         <v>249</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4646</v>
+        <v>2.4081</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5251</v>
+        <v>0.513</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4977</v>
+        <v>0.4912</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4646</v>
+        <v>2.4081</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4646</v>
+        <v>2.4081</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6692</v>
+        <v>2.5684</v>
       </c>
       <c r="I17" t="n">
-        <v>2.738</v>
+        <v>2.6371</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.738</v>
+        <v>2.6371</v>
       </c>
       <c r="N17" t="n">
         <v>249</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.4585</v>
+        <v>2.3742</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5238</v>
+        <v>0.5058</v>
       </c>
       <c r="D18" t="n">
-        <v>0.495</v>
+        <v>0.4758</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4585</v>
+        <v>2.3742</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4585</v>
+        <v>2.3742</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.656</v>
+        <v>2.4908</v>
       </c>
       <c r="I18" t="n">
-        <v>2.656</v>
+        <v>2.4908</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.656</v>
+        <v>2.4908</v>
       </c>
       <c r="N18" t="n">
         <v>253</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.445</v>
+        <v>2.3055</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5209</v>
+        <v>0.4912</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4888</v>
+        <v>0.4445</v>
       </c>
       <c r="E19" t="n">
-        <v>2.445</v>
+        <v>2.3055</v>
       </c>
       <c r="F19" t="n">
-        <v>2.445</v>
+        <v>2.3055</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6265</v>
+        <v>2.3334</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6265</v>
+        <v>2.3334</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.6265</v>
+        <v>2.3334</v>
       </c>
       <c r="N19" t="n">
         <v>253</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.2415</v>
+        <v>2.2724</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4775</v>
+        <v>0.4841</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3962</v>
+        <v>0.4294</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2415</v>
+        <v>2.2724</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4573</v>
+        <v>2.4583</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2158</v>
+        <v>-0.1859</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2132</v>
+        <v>2.787</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7351</v>
+        <v>1.5648</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2158</v>
+        <v>-0.1859</v>
       </c>
       <c r="K20" t="n">
         <v>290</v>
@@ -1357,7 +1357,7 @@
         <v>85</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5193</v>
+        <v>1.3789</v>
       </c>
       <c r="N20" t="n">
         <v>375</v>
@@ -1366,231 +1366,231 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sonic</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0478</v>
+        <v>1.9353</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4363</v>
+        <v>0.4123</v>
       </c>
       <c r="D21" t="n">
-        <v>0.308</v>
+        <v>0.2758</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0478</v>
+        <v>1.9353</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0478</v>
+        <v>3.0119</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-1.0766</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0478</v>
+        <v>4.8655</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1006</v>
+        <v>2.7318</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-1.0766</v>
       </c>
       <c r="K21" t="n">
-        <v>249</v>
+        <v>338</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1006</v>
+        <v>1.6552</v>
       </c>
       <c r="N21" t="n">
-        <v>249</v>
+        <v>415</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>Sonic</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.8838</v>
+        <v>1.9114</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4013</v>
+        <v>0.4072</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2333</v>
+        <v>0.2649</v>
       </c>
       <c r="E22" t="n">
-        <v>1.8838</v>
+        <v>1.9114</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0316</v>
+        <v>1.9114</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1478</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1082</v>
+        <v>1.9114</v>
       </c>
       <c r="I22" t="n">
-        <v>2.7584</v>
+        <v>1.9625</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1478</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>338</v>
+        <v>249</v>
       </c>
       <c r="L22" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6106</v>
+        <v>1.9625</v>
       </c>
       <c r="N22" t="n">
-        <v>415</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>s0m</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.7669</v>
+        <v>1.7391</v>
       </c>
       <c r="C23" t="n">
-        <v>0.3764</v>
+        <v>0.3705</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1801</v>
+        <v>0.1865</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7669</v>
+        <v>1.7391</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4178</v>
+        <v>2.6081</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3491</v>
+        <v>-0.869</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4178</v>
+        <v>3.3493</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2256</v>
+        <v>1.8805</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3491</v>
+        <v>-0.869</v>
       </c>
       <c r="K23" t="n">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="L23" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5747</v>
+        <v>1.0115</v>
       </c>
       <c r="N23" t="n">
-        <v>375</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5935</v>
+        <v>1.6728</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3395</v>
+        <v>0.3564</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1012</v>
+        <v>0.1563</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5935</v>
+        <v>1.6728</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1998</v>
+        <v>0.3623</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6063</v>
+        <v>1.3105</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3637</v>
+        <v>0.3623</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2764</v>
+        <v>0.2034</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6063</v>
+        <v>1.3105</v>
       </c>
       <c r="K24" t="n">
-        <v>167</v>
+        <v>290</v>
       </c>
       <c r="L24" t="n">
         <v>85</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6701</v>
+        <v>1.5139</v>
       </c>
       <c r="N24" t="n">
-        <v>252</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>s0m</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5206</v>
+        <v>1.5844</v>
       </c>
       <c r="C25" t="n">
-        <v>0.324</v>
+        <v>0.3375</v>
       </c>
       <c r="D25" t="n">
-        <v>0.068</v>
+        <v>0.116</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5206</v>
+        <v>1.5844</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4535</v>
+        <v>2.131</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9329</v>
+        <v>-0.5466</v>
       </c>
       <c r="H25" t="n">
-        <v>3.201</v>
+        <v>2.131</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7285</v>
+        <v>1.1965</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9329</v>
+        <v>-0.5466</v>
       </c>
       <c r="K25" t="n">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="L25" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7956</v>
+        <v>0.6498999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>415</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3049</v>
+        <v>0.2623</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0274</v>
+        <v>-0.045</v>
       </c>
       <c r="E26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4314</v>
+        <v>1.231</v>
       </c>
       <c r="N26" t="n">
         <v>100</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1588</v>
+        <v>0.1481</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2848</v>
+        <v>-0.2891</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7456</v>
+        <v>0.6952</v>
       </c>
       <c r="N27" t="n">
         <v>253</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1378</v>
+        <v>0.1205</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3297</v>
+        <v>-0.3482</v>
       </c>
       <c r="E28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="F28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="I28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.647</v>
+        <v>0.5655</v>
       </c>
       <c r="N28" t="n">
         <v>99</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1178</v>
+        <v>0.1012</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3726</v>
+        <v>-0.3894</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5528</v>
+        <v>0.4751</v>
       </c>
       <c r="N29" t="n">
         <v>100</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3835</v>
+        <v>0.2485</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0529</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4496</v>
+        <v>-0.4926</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3835</v>
+        <v>0.2485</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8224</v>
+        <v>0.672</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4389</v>
+        <v>-0.4235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8224</v>
+        <v>0.672</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4441</v>
+        <v>0.3773</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4389</v>
+        <v>-0.4235</v>
       </c>
       <c r="K30" t="n">
         <v>290</v>
@@ -1817,7 +1817,7 @@
         <v>85</v>
       </c>
       <c r="M30" t="n">
-        <v>0.005199999999999982</v>
+        <v>-0.04619999999999996</v>
       </c>
       <c r="N30" t="n">
         <v>375</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0257</v>
+        <v>-0.0281</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.679</v>
+        <v>-0.6659</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1204</v>
+        <v>-0.1319</v>
       </c>
       <c r="N31" t="n">
         <v>99</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1163</v>
+        <v>-0.1228</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8727</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.5458</v>
+        <v>-0.5765</v>
       </c>
       <c r="N32" t="n">
         <v>100</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.6617</v>
+        <v>-0.6385</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.141</v>
+        <v>-0.136</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9254</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6617</v>
+        <v>-0.6385</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6617</v>
+        <v>-0.6385</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6617</v>
+        <v>-0.6385</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6788</v>
+        <v>-0.6556</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.6788</v>
+        <v>-0.6556</v>
       </c>
       <c r="N33" t="n">
         <v>249</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1454</v>
+        <v>-0.146</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9349</v>
+        <v>-0.9181</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6826</v>
+        <v>-0.6855</v>
       </c>
       <c r="N34" t="n">
         <v>99</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1511</v>
+        <v>-0.1483</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.923</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7094</v>
+        <v>-0.6963</v>
       </c>
       <c r="N35" t="n">
         <v>99</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1614</v>
+        <v>-0.1731</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9691</v>
+        <v>-0.976</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.8126</v>
       </c>
       <c r="N36" t="n">
         <v>253</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>trk</t>
+          <t>Jonji</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1867</v>
+        <v>-0.1822</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0231</v>
+        <v>-0.9953</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8762</v>
+        <v>-0.8551</v>
       </c>
       <c r="N37" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jonji</t>
+          <t>trk</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1966</v>
+        <v>-0.1851</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0442</v>
+        <v>-1.0017</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9227</v>
+        <v>-0.869</v>
       </c>
       <c r="N38" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9434</v>
+        <v>-0.9437</v>
       </c>
       <c r="C39" t="n">
         <v>-0.201</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0537</v>
+        <v>-1.0357</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9434</v>
+        <v>-0.9437</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.9434</v>
+        <v>-0.9437</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.9434</v>
+        <v>-0.9437</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.9677</v>
+        <v>-0.9689</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.9677</v>
+        <v>-0.9689</v>
       </c>
       <c r="N39" t="n">
         <v>249</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.9687</v>
+        <v>-1.0234</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2064</v>
+        <v>-0.218</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0652</v>
+        <v>-1.072</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.9687</v>
+        <v>-1.0234</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0608</v>
+        <v>-1.1347</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0921</v>
+        <v>0.1113</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0608</v>
+        <v>-1.1347</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5728</v>
+        <v>-0.6371</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0921</v>
+        <v>0.1113</v>
       </c>
       <c r="K40" t="n">
         <v>338</v>
@@ -2277,7 +2277,7 @@
         <v>77</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.4807</v>
+        <v>-0.5258</v>
       </c>
       <c r="N40" t="n">
         <v>415</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2594</v>
+        <v>-0.2449</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1784</v>
+        <v>-1.1294</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2175</v>
+        <v>-1.1494</v>
       </c>
       <c r="N41" t="n">
         <v>100</v>
@@ -2429,10 +2429,10 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8165</v>
+        <v>1.8585</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8165</v>
+        <v>1.8585</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2591</v>
+        <v>1.2863</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2591</v>
+        <v>1.2863</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.41</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9293</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9293</v>
+        <v>0.9258999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7191</v>
+        <v>0.7013</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7191</v>
+        <v>0.7013</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.99</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1344</v>
+        <v>-0.1186</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1344</v>
+        <v>-0.1186</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.85</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1695</v>
+        <v>-0.1537</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1695</v>
+        <v>-0.1537</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.75</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2722</v>
+        <v>-0.258</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2722</v>
+        <v>-0.258</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.67</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3439</v>
+        <v>-0.3305</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3439</v>
+        <v>-0.3305</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3794</v>
+        <v>-0.3674</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3794</v>
+        <v>-0.3674</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.61</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3972</v>
+        <v>-0.3861</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3301</v>
+        <v>1.3628</v>
       </c>
       <c r="J12" t="n">
-        <v>26.602</v>
+        <v>27.256</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3301</v>
+        <v>1.3628</v>
       </c>
       <c r="J13" t="n">
-        <v>26.602</v>
+        <v>27.256</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2639</v>
+        <v>-0.2253</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.278</v>
+        <v>-4.506</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3493</v>
+        <v>-0.3081</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.986</v>
+        <v>-6.162</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5276</v>
+        <v>-0.4886</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.552</v>
+        <v>-9.772</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6026</v>
+        <v>0.5463</v>
       </c>
       <c r="J17" t="n">
-        <v>12.052</v>
+        <v>10.926</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.96</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0684</v>
+        <v>-0.056</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.368</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.9</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1413</v>
+        <v>-0.1229</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.826</v>
+        <v>-2.458</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.77</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2754</v>
+        <v>-0.2562</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.508</v>
+        <v>-5.124</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.74</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.304</v>
+        <v>-0.2861</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.08</v>
+        <v>-5.722</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.19</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3312</v>
+        <v>0.3216</v>
       </c>
       <c r="J22" t="n">
-        <v>9.604799999999999</v>
+        <v>9.3264</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3175</v>
+        <v>0.3068</v>
       </c>
       <c r="J23" t="n">
-        <v>9.2075</v>
+        <v>8.8972</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0363</v>
+        <v>0.0272</v>
       </c>
       <c r="J24" t="n">
-        <v>1.0527</v>
+        <v>0.7887999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2401</v>
+        <v>-0.2199</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.9629</v>
+        <v>-6.3771</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.68</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3636</v>
+        <v>-0.3499</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.5444</v>
+        <v>-10.1471</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.22</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3381</v>
+        <v>0.2791</v>
       </c>
       <c r="J27" t="n">
-        <v>9.8049</v>
+        <v>8.0939</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.17</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2755</v>
+        <v>0.2225</v>
       </c>
       <c r="J28" t="n">
-        <v>7.9895</v>
+        <v>6.4525</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.02</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0507</v>
+        <v>0.0351</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4703</v>
+        <v>1.0179</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.029</v>
+        <v>-0.0206</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.841</v>
+        <v>-0.5974</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.88</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1742</v>
+        <v>-0.1537</v>
       </c>
       <c r="J31" t="n">
-        <v>-5.0518</v>
+        <v>-4.4573</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.15</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4689</v>
+        <v>0.4262</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5981</v>
+        <v>12.3598</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.342</v>
+        <v>0.3001</v>
       </c>
       <c r="J33" t="n">
-        <v>9.917999999999999</v>
+        <v>8.7029</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2304</v>
+        <v>0.1937</v>
       </c>
       <c r="J34" t="n">
-        <v>6.6816</v>
+        <v>5.6173</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2304</v>
+        <v>-0.1937</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.6816</v>
+        <v>-5.6173</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.75</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7003</v>
+        <v>-0.6672</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.3087</v>
+        <v>-19.3488</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.29</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.4993</v>
       </c>
       <c r="J37" t="n">
-        <v>16.211</v>
+        <v>14.4797</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3647</v>
+        <v>0.3115</v>
       </c>
       <c r="J38" t="n">
-        <v>10.5763</v>
+        <v>9.0335</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1603</v>
+        <v>0.1274</v>
       </c>
       <c r="J39" t="n">
-        <v>4.6487</v>
+        <v>3.6946</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1382</v>
+        <v>0.1086</v>
       </c>
       <c r="J40" t="n">
-        <v>4.0078</v>
+        <v>3.1494</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1549</v>
+        <v>-0.1349</v>
       </c>
       <c r="J41" t="n">
-        <v>-4.4921</v>
+        <v>-3.9121</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>2.1</v>
       </c>
       <c r="I42" t="n">
-        <v>1.8219</v>
+        <v>1.8866</v>
       </c>
       <c r="J42" t="n">
-        <v>45.5475</v>
+        <v>47.165</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.31</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7537</v>
+        <v>0.734</v>
       </c>
       <c r="J43" t="n">
-        <v>18.8425</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.28</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6942</v>
+        <v>0.6716</v>
       </c>
       <c r="J44" t="n">
-        <v>17.355</v>
+        <v>16.79</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2597</v>
+        <v>0.2286</v>
       </c>
       <c r="J45" t="n">
-        <v>6.4925</v>
+        <v>5.715</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.96</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2298</v>
+        <v>-0.1984</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.745</v>
+        <v>-4.96</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1575</v>
+        <v>0.1232</v>
       </c>
       <c r="J47" t="n">
-        <v>3.9375</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.93</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.0852</v>
       </c>
       <c r="J48" t="n">
-        <v>-2.4775</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.91</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1234</v>
+        <v>-0.1081</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.085</v>
+        <v>-2.7025</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2378</v>
+        <v>-0.219</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.945</v>
+        <v>-5.475</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.55</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4669</v>
+        <v>-0.4624</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.6725</v>
+        <v>-11.56</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>0.87</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1498</v>
+        <v>-0.1341</v>
       </c>
       <c r="J52" t="n">
-        <v>-3.4454</v>
+        <v>-3.0843</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.78</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.245</v>
+        <v>-0.2301</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.635</v>
+        <v>-5.2923</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.78</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.245</v>
+        <v>-0.2301</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.635</v>
+        <v>-5.2923</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.65</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3633</v>
+        <v>-0.3502</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.3559</v>
+        <v>-8.054600000000001</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.5</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.496</v>
+        <v>-0.4939</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.408</v>
+        <v>-11.3597</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.51</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0889</v>
+        <v>1.1016</v>
       </c>
       <c r="J57" t="n">
-        <v>25.0447</v>
+        <v>25.3368</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.39</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9014</v>
+        <v>0.8915</v>
       </c>
       <c r="J58" t="n">
-        <v>20.7322</v>
+        <v>20.5045</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.33</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7903</v>
+        <v>0.7734</v>
       </c>
       <c r="J59" t="n">
-        <v>18.1769</v>
+        <v>17.7882</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7325</v>
       </c>
       <c r="J60" t="n">
-        <v>17.2845</v>
+        <v>16.8475</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>1.29</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7119</v>
+        <v>0.6909</v>
       </c>
       <c r="J61" t="n">
-        <v>16.3737</v>
+        <v>15.8907</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.2</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4356</v>
+        <v>0.3781</v>
       </c>
       <c r="J62" t="n">
-        <v>13.068</v>
+        <v>11.343</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.14</v>
       </c>
       <c r="I63" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J63" t="n">
-        <v>9.891</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.02</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0743</v>
+        <v>0.053</v>
       </c>
       <c r="J64" t="n">
-        <v>2.229</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.92</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.123</v>
+        <v>-0.1046</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.69</v>
+        <v>-3.138</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.68</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3653</v>
+        <v>-0.3518</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.959</v>
+        <v>-10.554</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.54</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1737</v>
+        <v>1.1887</v>
       </c>
       <c r="J67" t="n">
-        <v>35.211</v>
+        <v>35.661</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.16</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4632</v>
+        <v>0.4255</v>
       </c>
       <c r="J68" t="n">
-        <v>13.896</v>
+        <v>12.765</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.02</v>
       </c>
       <c r="I69" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="J69" t="n">
-        <v>2.346</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.02</v>
       </c>
       <c r="I70" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0614</v>
       </c>
       <c r="J70" t="n">
-        <v>2.346</v>
+        <v>1.842</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.96</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1945</v>
+        <v>-0.1598</v>
       </c>
       <c r="J71" t="n">
-        <v>-5.835</v>
+        <v>-4.794</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.4</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7389</v>
+        <v>0.6828</v>
       </c>
       <c r="J72" t="n">
-        <v>31.0338</v>
+        <v>28.6776</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.17</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3737</v>
+        <v>0.3189</v>
       </c>
       <c r="J73" t="n">
-        <v>15.6954</v>
+        <v>13.3938</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.99</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0278</v>
+        <v>-0.0197</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.1676</v>
+        <v>-0.8274</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.86</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1944</v>
+        <v>-0.1738</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.1648</v>
+        <v>-7.2996</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.78</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2756</v>
+        <v>-0.2568</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.5752</v>
+        <v>-10.7856</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.36</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9115</v>
+        <v>0.8951</v>
       </c>
       <c r="J77" t="n">
-        <v>38.283</v>
+        <v>37.5942</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4534</v>
+        <v>0.412</v>
       </c>
       <c r="J78" t="n">
-        <v>19.0428</v>
+        <v>17.304</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.09</v>
       </c>
       <c r="I79" t="n">
-        <v>0.303</v>
+        <v>0.2648</v>
       </c>
       <c r="J79" t="n">
-        <v>12.726</v>
+        <v>11.1216</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.97</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1463</v>
+        <v>-0.1159</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.1446</v>
+        <v>-4.8678</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7349</v>
+        <v>-0.7053</v>
       </c>
       <c r="J81" t="n">
-        <v>-30.8658</v>
+        <v>-29.6226</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5968</v>
+        <v>0.5379</v>
       </c>
       <c r="J82" t="n">
-        <v>17.3072</v>
+        <v>15.5991</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.28</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5058</v>
       </c>
       <c r="J83" t="n">
-        <v>16.385</v>
+        <v>14.6682</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.92</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1238</v>
+        <v>-0.1052</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.5902</v>
+        <v>-3.0508</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2426</v>
+        <v>-0.2225</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.0354</v>
+        <v>-6.4525</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.7</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3479</v>
+        <v>-0.3331</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.0891</v>
+        <v>-9.6599</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.34</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8512</v>
+        <v>0.8288</v>
       </c>
       <c r="J87" t="n">
-        <v>24.6848</v>
+        <v>24.0352</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.79</v>
+        <v>0.763</v>
       </c>
       <c r="J88" t="n">
-        <v>22.91</v>
+        <v>22.127</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.23</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5855</v>
       </c>
       <c r="J89" t="n">
-        <v>18.0235</v>
+        <v>16.9795</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0204</v>
+        <v>-0.0153</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.5916</v>
+        <v>-0.4437</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.75</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7248</v>
+        <v>-0.696</v>
       </c>
       <c r="J91" t="n">
-        <v>-21.0192</v>
+        <v>-20.184</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3999</v>
+        <v>0.3444</v>
       </c>
       <c r="J92" t="n">
-        <v>10.3974</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.97</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.3962</v>
+        <v>-1.1206</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.97</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0537</v>
+        <v>-0.0431</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.3962</v>
+        <v>-1.1206</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1738</v>
+        <v>-0.1542</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.5188</v>
+        <v>-4.0092</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.66</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3775</v>
+        <v>-0.3646</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.815</v>
+        <v>-9.4796</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.52</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1376</v>
+        <v>1.1505</v>
       </c>
       <c r="J97" t="n">
-        <v>29.5776</v>
+        <v>29.913</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.15</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4371</v>
+        <v>0.4012</v>
       </c>
       <c r="J98" t="n">
-        <v>11.3646</v>
+        <v>10.4312</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.11</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3401</v>
+        <v>0.3058</v>
       </c>
       <c r="J99" t="n">
-        <v>8.842599999999999</v>
+        <v>7.9508</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2041</v>
+        <v>0.1755</v>
       </c>
       <c r="J100" t="n">
-        <v>5.3066</v>
+        <v>4.563</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.03</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1087</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>2.8262</v>
+        <v>2.288</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.81</v>
       </c>
       <c r="I102" t="n">
-        <v>0.8727</v>
+        <v>0.8035</v>
       </c>
       <c r="J102" t="n">
-        <v>14.8359</v>
+        <v>13.6595</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.75</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8196</v>
+        <v>0.75</v>
       </c>
       <c r="J103" t="n">
-        <v>13.9332</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.63</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7116</v>
+        <v>0.643</v>
       </c>
       <c r="J104" t="n">
-        <v>12.0972</v>
+        <v>10.931</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.59</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6752</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>11.4784</v>
+        <v>10.3258</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1371</v>
+        <v>-0.1232</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.3307</v>
+        <v>-2.0944</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>0.82</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.1981</v>
+        <v>-0.1827</v>
       </c>
       <c r="J107" t="n">
-        <v>-3.3677</v>
+        <v>-3.1059</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.74</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.279</v>
+        <v>-0.2655</v>
       </c>
       <c r="J108" t="n">
-        <v>-4.743</v>
+        <v>-4.5135</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.279</v>
+        <v>-0.2655</v>
       </c>
       <c r="J109" t="n">
-        <v>-4.743</v>
+        <v>-4.5135</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.65</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3593</v>
+        <v>-0.3471</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.1081</v>
+        <v>-5.9007</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.46</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5282</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.953900000000001</v>
+        <v>-8.9794</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.23</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4954</v>
+        <v>0.4373</v>
       </c>
       <c r="J112" t="n">
-        <v>12.8804</v>
+        <v>11.3698</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.18</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4095</v>
+        <v>0.3531</v>
       </c>
       <c r="J113" t="n">
-        <v>10.647</v>
+        <v>9.1806</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.88</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1656</v>
+        <v>-0.1458</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.3056</v>
+        <v>-3.7908</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.76</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2875</v>
+        <v>-0.2688</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.475</v>
+        <v>-6.9888</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.74</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3065</v>
+        <v>-0.2888</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.969</v>
+        <v>-7.5088</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.54</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1645</v>
+        <v>1.1784</v>
       </c>
       <c r="J117" t="n">
-        <v>30.277</v>
+        <v>30.6384</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.31</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7781</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>20.2306</v>
+        <v>19.539</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.14</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4133</v>
+        <v>0.3778</v>
       </c>
       <c r="J119" t="n">
-        <v>10.7458</v>
+        <v>9.822800000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.07</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2327</v>
+        <v>0.2025</v>
       </c>
       <c r="J120" t="n">
-        <v>6.0502</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.82</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5748</v>
+        <v>-0.5377</v>
       </c>
       <c r="J121" t="n">
-        <v>-14.9448</v>
+        <v>-13.9802</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.4</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8226</v>
       </c>
       <c r="J122" t="n">
-        <v>25.146</v>
+        <v>24.678</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3981</v>
+        <v>0.359</v>
       </c>
       <c r="J123" t="n">
-        <v>11.943</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.07</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2447</v>
+        <v>0.2117</v>
       </c>
       <c r="J124" t="n">
-        <v>7.341</v>
+        <v>6.351</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1871</v>
+        <v>-0.1526</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.613</v>
+        <v>-4.578</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2494</v>
+        <v>-0.2106</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.482</v>
+        <v>-6.318</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.46</v>
       </c>
       <c r="I127" t="n">
-        <v>0.732</v>
+        <v>0.6984</v>
       </c>
       <c r="J127" t="n">
-        <v>21.96</v>
+        <v>20.952</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.97</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0592</v>
+        <v>-0.0463</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.776</v>
+        <v>-1.389</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.92</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1248</v>
+        <v>-0.1061</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.744</v>
+        <v>-3.183</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.9</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1481</v>
+        <v>-0.1284</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.443</v>
+        <v>-3.852</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.82</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2336</v>
+        <v>-0.2133</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.008</v>
+        <v>-6.399</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.62</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1257</v>
+        <v>1.1196</v>
       </c>
       <c r="J132" t="n">
-        <v>29.2682</v>
+        <v>29.1096</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.17</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4709</v>
+        <v>0.4464</v>
       </c>
       <c r="J133" t="n">
-        <v>12.2434</v>
+        <v>11.6064</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4345</v>
+        <v>0.4012</v>
       </c>
       <c r="J134" t="n">
-        <v>11.297</v>
+        <v>10.4312</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.08</v>
       </c>
       <c r="I135" t="n">
-        <v>0.261</v>
+        <v>0.2294</v>
       </c>
       <c r="J135" t="n">
-        <v>6.786</v>
+        <v>5.9644</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.85</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5027</v>
+        <v>-0.4627</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.0702</v>
+        <v>-12.0302</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.11</v>
       </c>
       <c r="I137" t="n">
-        <v>0.2856</v>
+        <v>0.2361</v>
       </c>
       <c r="J137" t="n">
-        <v>7.4256</v>
+        <v>6.1386</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.07</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2037</v>
+        <v>0.1618</v>
       </c>
       <c r="J138" t="n">
-        <v>5.2962</v>
+        <v>4.2068</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.93</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1069</v>
+        <v>-0.0907</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.7794</v>
+        <v>-2.3582</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2264</v>
+        <v>-0.2062</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.8864</v>
+        <v>-5.3612</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2949</v>
+        <v>-0.2766</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.6674</v>
+        <v>-7.1916</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.24</v>
       </c>
       <c r="I142" t="n">
-        <v>0.49</v>
+        <v>0.4496</v>
       </c>
       <c r="J142" t="n">
-        <v>13.72</v>
+        <v>12.5888</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.18</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4057</v>
+        <v>0.3495</v>
       </c>
       <c r="J143" t="n">
-        <v>11.3596</v>
+        <v>9.786</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.83</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2196</v>
+        <v>-0.1992</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.1488</v>
+        <v>-5.5776</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.82</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2298</v>
+        <v>-0.2094</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.4344</v>
+        <v>-5.8632</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2597</v>
+        <v>-0.24</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.2716</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.125</v>
+        <v>1.1221</v>
       </c>
       <c r="J147" t="n">
-        <v>31.5</v>
+        <v>31.4188</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.19</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.4996</v>
       </c>
       <c r="J148" t="n">
-        <v>14.4088</v>
+        <v>13.9888</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.97</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1507</v>
+        <v>-0.1198</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.2196</v>
+        <v>-3.3544</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3321</v>
+        <v>-0.2899</v>
       </c>
       <c r="J150" t="n">
-        <v>-9.2988</v>
+        <v>-8.1172</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.76</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6953</v>
+        <v>-0.6633</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.4684</v>
+        <v>-18.5724</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.37</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4812</v>
+        <v>0.4281</v>
       </c>
       <c r="J152" t="n">
-        <v>13.9548</v>
+        <v>12.4149</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.27</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3848</v>
+        <v>0.3232</v>
       </c>
       <c r="J153" t="n">
-        <v>11.1592</v>
+        <v>9.3728</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.17</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2659</v>
+        <v>0.2159</v>
       </c>
       <c r="J154" t="n">
-        <v>7.7111</v>
+        <v>6.2611</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.09</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1601</v>
+        <v>0.1247</v>
       </c>
       <c r="J155" t="n">
-        <v>4.6429</v>
+        <v>3.6163</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.85</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2142</v>
+        <v>-0.1942</v>
       </c>
       <c r="J156" t="n">
-        <v>-6.2118</v>
+        <v>-5.6318</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.19</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3312</v>
+        <v>0.3216</v>
       </c>
       <c r="J157" t="n">
-        <v>9.604799999999999</v>
+        <v>9.3264</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.95</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.0842</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.4418</v>
+        <v>-2.0039</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.92</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1215</v>
+        <v>-0.1034</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.5235</v>
+        <v>-2.9986</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.91</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1332</v>
+        <v>-0.1145</v>
       </c>
       <c r="J160" t="n">
-        <v>-3.8628</v>
+        <v>-3.3205</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.9</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1447</v>
+        <v>-0.1254</v>
       </c>
       <c r="J161" t="n">
-        <v>-4.1963</v>
+        <v>-3.6366</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.23</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4911</v>
+        <v>0.4532</v>
       </c>
       <c r="J162" t="n">
-        <v>13.7508</v>
+        <v>12.6896</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3304</v>
+        <v>0.2785</v>
       </c>
       <c r="J163" t="n">
-        <v>9.251200000000001</v>
+        <v>7.798</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.87</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1725</v>
+        <v>-0.1532</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.83</v>
+        <v>-4.2896</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.79</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.254</v>
+        <v>-0.2343</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.112</v>
+        <v>-6.5604</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4818</v>
+        <v>-0.4799</v>
       </c>
       <c r="J166" t="n">
-        <v>-13.4904</v>
+        <v>-13.4372</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.25</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5984</v>
+        <v>0.5878</v>
       </c>
       <c r="J167" t="n">
-        <v>16.7552</v>
+        <v>16.4584</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.22</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5513</v>
+        <v>0.543</v>
       </c>
       <c r="J168" t="n">
-        <v>15.4364</v>
+        <v>15.204</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5033</v>
+        <v>0.4893</v>
       </c>
       <c r="J169" t="n">
-        <v>14.0924</v>
+        <v>13.7004</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.13</v>
       </c>
       <c r="I170" t="n">
-        <v>0.3896</v>
+        <v>0.3543</v>
       </c>
       <c r="J170" t="n">
-        <v>10.9088</v>
+        <v>9.920400000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.08</v>
       </c>
       <c r="I171" t="n">
-        <v>0.261</v>
+        <v>0.2294</v>
       </c>
       <c r="J171" t="n">
-        <v>7.308</v>
+        <v>6.4232</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>0.95</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.0547</v>
+        <v>-0.0418</v>
       </c>
       <c r="J172" t="n">
-        <v>-1.1487</v>
+        <v>-0.8778</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.82</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2081</v>
+        <v>-0.1925</v>
       </c>
       <c r="J173" t="n">
-        <v>-4.3701</v>
+        <v>-4.0425</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2184</v>
+        <v>-0.2028</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.5864</v>
+        <v>-4.2588</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.8</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2285</v>
+        <v>-0.2129</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.7985</v>
+        <v>-4.4709</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.32</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6535</v>
+        <v>-0.6767</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.7235</v>
+        <v>-14.2107</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.72</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8057</v>
+        <v>0.7346</v>
       </c>
       <c r="J177" t="n">
-        <v>16.9197</v>
+        <v>15.4266</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.64</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7317</v>
+        <v>0.6606</v>
       </c>
       <c r="J178" t="n">
-        <v>15.3657</v>
+        <v>13.8726</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.61</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7036</v>
+        <v>0.6328</v>
       </c>
       <c r="J179" t="n">
-        <v>14.7756</v>
+        <v>13.2888</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.3862</v>
+        <v>0.3303</v>
       </c>
       <c r="J180" t="n">
-        <v>8.110200000000001</v>
+        <v>6.9363</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.86</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.2221</v>
+        <v>-0.2056</v>
       </c>
       <c r="J181" t="n">
-        <v>-4.6641</v>
+        <v>-4.3176</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1189</v>
+        <v>1.1312</v>
       </c>
       <c r="J182" t="n">
-        <v>32.4481</v>
+        <v>32.8048</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.36</v>
       </c>
       <c r="I183" t="n">
-        <v>0.86</v>
+        <v>0.842</v>
       </c>
       <c r="J183" t="n">
-        <v>24.94</v>
+        <v>24.418</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.5725</v>
       </c>
       <c r="J184" t="n">
-        <v>17.4667</v>
+        <v>16.6025</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.14</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4004</v>
+        <v>0.3677</v>
       </c>
       <c r="J185" t="n">
-        <v>11.6116</v>
+        <v>10.6633</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.06</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1892</v>
+        <v>0.1615</v>
       </c>
       <c r="J186" t="n">
-        <v>5.4868</v>
+        <v>4.6835</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.02</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1001</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>2.9029</v>
+        <v>2.1576</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.92</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1131</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.2799</v>
+        <v>-2.8449</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.92</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1131</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.2799</v>
+        <v>-2.8449</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.91</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1249</v>
+        <v>-0.1092</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.6221</v>
+        <v>-3.1668</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.53</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4856</v>
+        <v>-0.4836</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.0824</v>
+        <v>-14.0244</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.59</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2272</v>
+        <v>1.2437</v>
       </c>
       <c r="J192" t="n">
-        <v>35.5888</v>
+        <v>36.0673</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.3</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7537</v>
+        <v>0.7264</v>
       </c>
       <c r="J193" t="n">
-        <v>21.8573</v>
+        <v>21.0656</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.12</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3618</v>
+        <v>0.3278</v>
       </c>
       <c r="J194" t="n">
-        <v>10.4922</v>
+        <v>9.5062</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.08</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2573</v>
+        <v>0.2263</v>
       </c>
       <c r="J195" t="n">
-        <v>7.4617</v>
+        <v>6.5627</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.89</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4058</v>
+        <v>-0.3647</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.7682</v>
+        <v>-10.5763</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.14</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3378</v>
+        <v>0.2847</v>
       </c>
       <c r="J197" t="n">
-        <v>9.796200000000001</v>
+        <v>8.2563</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.05</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1552</v>
+        <v>0.1194</v>
       </c>
       <c r="J198" t="n">
-        <v>4.5008</v>
+        <v>3.4626</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.04</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1316</v>
+        <v>0.0993</v>
       </c>
       <c r="J199" t="n">
-        <v>3.8164</v>
+        <v>2.8797</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.03</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1066</v>
+        <v>0.0784</v>
       </c>
       <c r="J200" t="n">
-        <v>3.0914</v>
+        <v>2.2736</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.52</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5027</v>
+        <v>-0.5041</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.5783</v>
+        <v>-14.6189</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.23</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5144</v>
+        <v>0.4587</v>
       </c>
       <c r="J202" t="n">
-        <v>12.3456</v>
+        <v>11.0088</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.99</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.017</v>
+        <v>-0.0123</v>
       </c>
       <c r="J203" t="n">
-        <v>-0.408</v>
+        <v>-0.2952</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.82</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2229</v>
+        <v>-0.2031</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.3496</v>
+        <v>-4.8744</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.75</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2912</v>
+        <v>-0.2727</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.9888</v>
+        <v>-6.5448</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.7</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.338</v>
+        <v>-0.322</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.112</v>
+        <v>-7.728</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.67</v>
       </c>
       <c r="I207" t="n">
-        <v>1.3157</v>
+        <v>1.336</v>
       </c>
       <c r="J207" t="n">
-        <v>31.5768</v>
+        <v>32.064</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.53</v>
       </c>
       <c r="I208" t="n">
-        <v>1.1316</v>
+        <v>1.1443</v>
       </c>
       <c r="J208" t="n">
-        <v>27.1584</v>
+        <v>27.4632</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.23</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6018</v>
+        <v>0.5722</v>
       </c>
       <c r="J209" t="n">
-        <v>14.4432</v>
+        <v>13.7328</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1047</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.5128</v>
+        <v>-2.028</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.91</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3644</v>
+        <v>-0.3252</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.7456</v>
+        <v>-7.8048</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4572</v>
+        <v>0.4009</v>
       </c>
       <c r="J212" t="n">
-        <v>11.8872</v>
+        <v>10.4234</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.99</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0188</v>
+        <v>-0.0138</v>
       </c>
       <c r="J213" t="n">
-        <v>-0.4888</v>
+        <v>-0.3588</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0524</v>
+        <v>-0.0422</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.3624</v>
+        <v>-1.0972</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.76</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2832</v>
+        <v>-0.2644</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.3632</v>
+        <v>-6.8744</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.65</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3852</v>
+        <v>-0.3728</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.0152</v>
+        <v>-9.6928</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.36</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8694</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="J217" t="n">
-        <v>22.6044</v>
+        <v>22.1078</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.34</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8082</v>
       </c>
       <c r="J218" t="n">
-        <v>21.5826</v>
+        <v>21.0132</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.24</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6276</v>
+        <v>0.596</v>
       </c>
       <c r="J219" t="n">
-        <v>16.3176</v>
+        <v>15.496</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.09</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2815</v>
+        <v>0.2498</v>
       </c>
       <c r="J220" t="n">
-        <v>7.319</v>
+        <v>6.4948</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.04</v>
       </c>
       <c r="I221" t="n">
-        <v>0.1354</v>
+        <v>0.1118</v>
       </c>
       <c r="J221" t="n">
-        <v>3.5204</v>
+        <v>2.9068</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.59</v>
       </c>
       <c r="I222" t="n">
-        <v>1.1961</v>
+        <v>1.2114</v>
       </c>
       <c r="J222" t="n">
-        <v>27.5103</v>
+        <v>27.8622</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.54</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1309</v>
+        <v>1.1447</v>
       </c>
       <c r="J223" t="n">
-        <v>26.0107</v>
+        <v>26.3281</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.24</v>
       </c>
       <c r="I224" t="n">
-        <v>0.6117</v>
+        <v>0.5856</v>
       </c>
       <c r="J224" t="n">
-        <v>14.0691</v>
+        <v>13.4688</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.23</v>
       </c>
       <c r="I225" t="n">
-        <v>0.5905</v>
+        <v>0.5636</v>
       </c>
       <c r="J225" t="n">
-        <v>13.5815</v>
+        <v>12.9628</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.14</v>
       </c>
       <c r="I226" t="n">
-        <v>0.3869</v>
+        <v>0.355</v>
       </c>
       <c r="J226" t="n">
-        <v>8.8987</v>
+        <v>8.164999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.07</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2426</v>
+        <v>0.2019</v>
       </c>
       <c r="J227" t="n">
-        <v>5.5798</v>
+        <v>4.6437</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.91</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1177</v>
+        <v>-0.1031</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.7071</v>
+        <v>-2.3713</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.77</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2626</v>
+        <v>-0.2449</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.0398</v>
+        <v>-5.6327</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.66</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3643</v>
+        <v>-0.3502</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.3789</v>
+        <v>-8.054600000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.6</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4181</v>
+        <v>-0.4082</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.616300000000001</v>
+        <v>-9.3886</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.7</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3456</v>
+        <v>1.3673</v>
       </c>
       <c r="J232" t="n">
-        <v>29.6032</v>
+        <v>30.0806</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.64</v>
       </c>
       <c r="I233" t="n">
-        <v>1.2688</v>
+        <v>1.2865</v>
       </c>
       <c r="J233" t="n">
-        <v>27.9136</v>
+        <v>28.303</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.19</v>
       </c>
       <c r="I234" t="n">
-        <v>0.5097</v>
+        <v>0.4793</v>
       </c>
       <c r="J234" t="n">
-        <v>11.2134</v>
+        <v>10.5446</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.04</v>
       </c>
       <c r="I235" t="n">
-        <v>0.1203</v>
+        <v>0.0964</v>
       </c>
       <c r="J235" t="n">
-        <v>2.6466</v>
+        <v>2.1208</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.95</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2548</v>
+        <v>-0.2202</v>
       </c>
       <c r="J236" t="n">
-        <v>-5.6056</v>
+        <v>-4.8444</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.09</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2788</v>
+        <v>0.234</v>
       </c>
       <c r="J237" t="n">
-        <v>6.1336</v>
+        <v>5.148</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I238" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.0702</v>
       </c>
       <c r="J238" t="n">
-        <v>-1.8282</v>
+        <v>-1.5444</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.85</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1869</v>
+        <v>-0.1697</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.1118</v>
+        <v>-3.7334</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.77</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2644</v>
+        <v>-0.2463</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.8168</v>
+        <v>-5.4186</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.46</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5421</v>
+        <v>-0.5475</v>
       </c>
       <c r="J241" t="n">
-        <v>-11.9262</v>
+        <v>-12.045</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.02</v>
       </c>
       <c r="I242" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J242" t="n">
-        <v>2.6477</v>
+        <v>1.9198</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.96</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0536</v>
       </c>
       <c r="J243" t="n">
-        <v>-1.8879</v>
+        <v>-1.5544</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0919</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J244" t="n">
-        <v>-2.6651</v>
+        <v>-2.2562</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.87</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1712</v>
+        <v>-0.1524</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.9648</v>
+        <v>-4.4196</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.347</v>
+        <v>-0.3316</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.063</v>
+        <v>-9.616400000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.6</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2245</v>
+        <v>1.2403</v>
       </c>
       <c r="J247" t="n">
-        <v>35.5105</v>
+        <v>35.9687</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.57</v>
       </c>
       <c r="I248" t="n">
-        <v>1.1849</v>
+        <v>1.1992</v>
       </c>
       <c r="J248" t="n">
-        <v>34.3621</v>
+        <v>34.7768</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.19</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5154</v>
+        <v>0.4839</v>
       </c>
       <c r="J249" t="n">
-        <v>14.9466</v>
+        <v>14.0331</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.13</v>
       </c>
       <c r="I250" t="n">
-        <v>0.3754</v>
+        <v>0.3429</v>
       </c>
       <c r="J250" t="n">
-        <v>10.8866</v>
+        <v>9.944100000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.84</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5423</v>
+        <v>-0.5061</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.7267</v>
+        <v>-14.6769</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.91</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0786</v>
       </c>
       <c r="J252" t="n">
-        <v>-2.0944</v>
+        <v>-1.7292</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.76</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.2603</v>
+        <v>-0.2462</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.7266</v>
+        <v>-5.4164</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.68</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3336</v>
+        <v>-0.3207</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.3392</v>
+        <v>-7.0554</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.58</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4217</v>
+        <v>-0.4125</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.2774</v>
+        <v>-9.074999999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.5</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4922</v>
+        <v>-0.4895</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.8284</v>
+        <v>-10.769</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>2.04</v>
       </c>
       <c r="I257" t="n">
-        <v>1.7314</v>
+        <v>1.7833</v>
       </c>
       <c r="J257" t="n">
-        <v>38.0908</v>
+        <v>39.2326</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.42</v>
       </c>
       <c r="I258" t="n">
-        <v>0.9492</v>
+        <v>0.947</v>
       </c>
       <c r="J258" t="n">
-        <v>20.8824</v>
+        <v>20.834</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.39</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8965</v>
+        <v>0.8892</v>
       </c>
       <c r="J259" t="n">
-        <v>19.723</v>
+        <v>19.5624</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.14</v>
       </c>
       <c r="I260" t="n">
-        <v>0.3753</v>
+        <v>0.3431</v>
       </c>
       <c r="J260" t="n">
-        <v>8.256600000000001</v>
+        <v>7.5482</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.13</v>
       </c>
       <c r="I261" t="n">
-        <v>0.3509</v>
+        <v>0.3184</v>
       </c>
       <c r="J261" t="n">
-        <v>7.7198</v>
+        <v>7.0048</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.12</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3112</v>
+        <v>0.2604</v>
       </c>
       <c r="J262" t="n">
-        <v>7.4688</v>
+        <v>6.2496</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.05</v>
       </c>
       <c r="I263" t="n">
-        <v>0.1644</v>
+        <v>0.1274</v>
       </c>
       <c r="J263" t="n">
-        <v>3.9456</v>
+        <v>3.0576</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.2342</v>
+        <v>-0.2143</v>
       </c>
       <c r="J264" t="n">
-        <v>-5.6208</v>
+        <v>-5.1432</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.8</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2441</v>
+        <v>-0.2243</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.8584</v>
+        <v>-5.3832</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.78</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2637</v>
+        <v>-0.2443</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.3288</v>
+        <v>-5.8632</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.49</v>
       </c>
       <c r="I267" t="n">
-        <v>1.0727</v>
+        <v>1.0824</v>
       </c>
       <c r="J267" t="n">
-        <v>25.7448</v>
+        <v>25.9776</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.48</v>
       </c>
       <c r="I268" t="n">
-        <v>1.0588</v>
+        <v>1.0668</v>
       </c>
       <c r="J268" t="n">
-        <v>25.4112</v>
+        <v>25.6032</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.35</v>
       </c>
       <c r="I269" t="n">
-        <v>0.8356</v>
+        <v>0.8176</v>
       </c>
       <c r="J269" t="n">
-        <v>20.0544</v>
+        <v>19.6224</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>1.15</v>
       </c>
       <c r="I270" t="n">
-        <v>0.4193</v>
+        <v>0.3872</v>
       </c>
       <c r="J270" t="n">
-        <v>10.0632</v>
+        <v>9.2928</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>1</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.0495</v>
+        <v>-0.0449</v>
       </c>
       <c r="J271" t="n">
-        <v>-1.188</v>
+        <v>-1.0776</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.31</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6178</v>
+        <v>0.5597</v>
       </c>
       <c r="J272" t="n">
-        <v>15.445</v>
+        <v>13.9925</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.2</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4376</v>
+        <v>0.38</v>
       </c>
       <c r="J273" t="n">
-        <v>10.94</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.92</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1223</v>
+        <v>-0.1041</v>
       </c>
       <c r="J274" t="n">
-        <v>-3.0575</v>
+        <v>-2.6025</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.82</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2309</v>
+        <v>-0.2105</v>
       </c>
       <c r="J275" t="n">
-        <v>-5.7725</v>
+        <v>-5.2625</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3736</v>
+        <v>-0.3608</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.34</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.4</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9737</v>
+        <v>0.9659</v>
       </c>
       <c r="J277" t="n">
-        <v>24.3425</v>
+        <v>24.1475</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.21</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5819</v>
+        <v>0.544</v>
       </c>
       <c r="J278" t="n">
-        <v>14.5475</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.12</v>
       </c>
       <c r="I279" t="n">
-        <v>0.3731</v>
+        <v>0.3348</v>
       </c>
       <c r="J279" t="n">
-        <v>9.327500000000001</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.99</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0765</v>
+        <v>-0.0562</v>
       </c>
       <c r="J280" t="n">
-        <v>-1.9125</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5855</v>
+        <v>-0.5473</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.6375</v>
+        <v>-13.6825</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2348</v>
+        <v>0.1932</v>
       </c>
       <c r="J282" t="n">
-        <v>5.6352</v>
+        <v>4.6368</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.95</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0699</v>
+        <v>-0.0581</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.6776</v>
+        <v>-1.3944</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.79</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2455</v>
+        <v>-0.2273</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.892</v>
+        <v>-5.4552</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.74</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.293</v>
+        <v>-0.2753</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.032</v>
+        <v>-6.6072</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.57</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4471</v>
+        <v>-0.4401</v>
       </c>
       <c r="J286" t="n">
-        <v>-10.7304</v>
+        <v>-10.5624</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.44</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0095</v>
+        <v>1.0087</v>
       </c>
       <c r="J287" t="n">
-        <v>24.228</v>
+        <v>24.2088</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.32</v>
       </c>
       <c r="I288" t="n">
-        <v>0.7864</v>
+        <v>0.7627</v>
       </c>
       <c r="J288" t="n">
-        <v>18.8736</v>
+        <v>18.3048</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.24</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6253</v>
+        <v>0.5949</v>
       </c>
       <c r="J289" t="n">
-        <v>15.0072</v>
+        <v>14.2776</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.13</v>
       </c>
       <c r="I290" t="n">
-        <v>0.3802</v>
+        <v>0.347</v>
       </c>
       <c r="J290" t="n">
-        <v>9.1248</v>
+        <v>8.327999999999999</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.05</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1634</v>
+        <v>0.1374</v>
       </c>
       <c r="J291" t="n">
-        <v>3.9216</v>
+        <v>3.2976</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.29</v>
       </c>
       <c r="I292" t="n">
-        <v>0.661</v>
+        <v>0.62</v>
       </c>
       <c r="J292" t="n">
-        <v>14.542</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.03</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1476</v>
+        <v>0.118</v>
       </c>
       <c r="J293" t="n">
-        <v>3.2472</v>
+        <v>2.596</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.74</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.2901</v>
+        <v>-0.2729</v>
       </c>
       <c r="J294" t="n">
-        <v>-6.3822</v>
+        <v>-6.0038</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.46</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.5396</v>
+        <v>-0.5442</v>
       </c>
       <c r="J295" t="n">
-        <v>-11.8712</v>
+        <v>-11.9724</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.46</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5396</v>
+        <v>-0.5442</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.8712</v>
+        <v>-11.9724</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.62</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2391</v>
+        <v>1.2556</v>
       </c>
       <c r="J297" t="n">
-        <v>27.2602</v>
+        <v>27.6232</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.55</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1479</v>
+        <v>1.1616</v>
       </c>
       <c r="J298" t="n">
-        <v>25.2538</v>
+        <v>25.5552</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.24</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6151</v>
+        <v>0.5884</v>
       </c>
       <c r="J299" t="n">
-        <v>13.5322</v>
+        <v>12.9448</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.16</v>
       </c>
       <c r="I300" t="n">
-        <v>0.4381</v>
+        <v>0.4067</v>
       </c>
       <c r="J300" t="n">
-        <v>9.638199999999999</v>
+        <v>8.9474</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>1.05</v>
       </c>
       <c r="I301" t="n">
-        <v>0.1488</v>
+        <v>0.1225</v>
       </c>
       <c r="J301" t="n">
-        <v>3.2736</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3954</v>
+        <v>0.3398</v>
       </c>
       <c r="J302" t="n">
-        <v>11.0712</v>
+        <v>9.5144</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.14</v>
       </c>
       <c r="I303" t="n">
-        <v>0.3408</v>
+        <v>0.2876</v>
       </c>
       <c r="J303" t="n">
-        <v>9.542400000000001</v>
+        <v>8.0528</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.99</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.0217</v>
+        <v>-0.0161</v>
       </c>
       <c r="J304" t="n">
-        <v>-0.6076</v>
+        <v>-0.4508</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.83</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.217</v>
+        <v>-0.1967</v>
       </c>
       <c r="J305" t="n">
-        <v>-6.076</v>
+        <v>-5.5076</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.59</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4412</v>
+        <v>-0.4348</v>
       </c>
       <c r="J306" t="n">
-        <v>-12.3536</v>
+        <v>-12.1744</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.58</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2198</v>
+        <v>1.2363</v>
       </c>
       <c r="J307" t="n">
-        <v>34.1544</v>
+        <v>34.6164</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.43</v>
       </c>
       <c r="I308" t="n">
-        <v>1.0075</v>
+        <v>1.0056</v>
       </c>
       <c r="J308" t="n">
-        <v>28.21</v>
+        <v>28.1568</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.16</v>
       </c>
       <c r="I309" t="n">
-        <v>0.4602</v>
+        <v>0.4242</v>
       </c>
       <c r="J309" t="n">
-        <v>12.8856</v>
+        <v>11.8776</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.88</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4274</v>
+        <v>-0.3859</v>
       </c>
       <c r="J310" t="n">
-        <v>-11.9672</v>
+        <v>-10.8052</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5975</v>
+        <v>-0.5614</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.73</v>
+        <v>-15.7192</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.26</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5258</v>
+        <v>0.4663</v>
       </c>
       <c r="J312" t="n">
-        <v>14.7224</v>
+        <v>13.0564</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.23</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4771</v>
+        <v>0.4183</v>
       </c>
       <c r="J313" t="n">
-        <v>13.3588</v>
+        <v>11.7124</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.02</v>
       </c>
       <c r="I314" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0515</v>
       </c>
       <c r="J314" t="n">
-        <v>1.988</v>
+        <v>1.442</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.83</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2249</v>
+        <v>-0.2044</v>
       </c>
       <c r="J315" t="n">
-        <v>-6.2972</v>
+        <v>-5.7232</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2451</v>
+        <v>-0.2251</v>
       </c>
       <c r="J316" t="n">
-        <v>-6.8628</v>
+        <v>-6.3028</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.6</v>
       </c>
       <c r="I317" t="n">
-        <v>1.25</v>
+        <v>1.2684</v>
       </c>
       <c r="J317" t="n">
-        <v>35</v>
+        <v>35.5152</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.24</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6362</v>
+        <v>0.6021</v>
       </c>
       <c r="J318" t="n">
-        <v>17.8136</v>
+        <v>16.8588</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.09</v>
       </c>
       <c r="I319" t="n">
-        <v>0.2903</v>
+        <v>0.2572</v>
       </c>
       <c r="J319" t="n">
-        <v>8.128399999999999</v>
+        <v>7.2016</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.97</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1644</v>
+        <v>-0.1328</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.6032</v>
+        <v>-3.7184</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.9</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.373</v>
+        <v>-0.3312</v>
       </c>
       <c r="J321" t="n">
-        <v>-10.444</v>
+        <v>-9.2736</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.13</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2468</v>
+        <v>0.2315</v>
       </c>
       <c r="J322" t="n">
-        <v>7.404</v>
+        <v>6.945</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1006</v>
+        <v>0.0852</v>
       </c>
       <c r="J323" t="n">
-        <v>3.018</v>
+        <v>2.556</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.01</v>
       </c>
       <c r="I324" t="n">
-        <v>0.0363</v>
+        <v>0.0272</v>
       </c>
       <c r="J324" t="n">
-        <v>1.089</v>
+        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.91</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.1332</v>
+        <v>-0.1145</v>
       </c>
       <c r="J325" t="n">
-        <v>-3.996</v>
+        <v>-3.435</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.78</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.2697</v>
+        <v>-0.2503</v>
       </c>
       <c r="J326" t="n">
-        <v>-8.090999999999999</v>
+        <v>-7.509</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.6</v>
       </c>
       <c r="I327" t="n">
-        <v>0.7523</v>
+        <v>0.6841</v>
       </c>
       <c r="J327" t="n">
-        <v>22.569</v>
+        <v>20.523</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.07</v>
       </c>
       <c r="I328" t="n">
-        <v>0.1359</v>
+        <v>0.103</v>
       </c>
       <c r="J328" t="n">
-        <v>4.077</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.03</v>
       </c>
       <c r="I329" t="n">
-        <v>0.0688</v>
+        <v>0.0492</v>
       </c>
       <c r="J329" t="n">
-        <v>2.064</v>
+        <v>1.476</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.87</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1868</v>
+        <v>-0.1662</v>
       </c>
       <c r="J330" t="n">
-        <v>-5.604</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2491</v>
+        <v>-0.2294</v>
       </c>
       <c r="J331" t="n">
-        <v>-7.473</v>
+        <v>-6.882</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.58</v>
       </c>
       <c r="I332" t="n">
-        <v>1.2153</v>
+        <v>1.2312</v>
       </c>
       <c r="J332" t="n">
-        <v>35.2437</v>
+        <v>35.7048</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.24</v>
       </c>
       <c r="I333" t="n">
-        <v>0.631</v>
+        <v>0.5982</v>
       </c>
       <c r="J333" t="n">
-        <v>18.299</v>
+        <v>17.3478</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.12</v>
       </c>
       <c r="I334" t="n">
-        <v>0.3627</v>
+        <v>0.3285</v>
       </c>
       <c r="J334" t="n">
-        <v>10.5183</v>
+        <v>9.5265</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.02</v>
       </c>
       <c r="I335" t="n">
-        <v>0.0694</v>
+        <v>0.0532</v>
       </c>
       <c r="J335" t="n">
-        <v>2.0126</v>
+        <v>1.5428</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.99</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.0916</v>
+        <v>-0.0707</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.6564</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.17</v>
       </c>
       <c r="I337" t="n">
-        <v>0.4154</v>
+        <v>0.3615</v>
       </c>
       <c r="J337" t="n">
-        <v>12.0466</v>
+        <v>10.4835</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>0.95</v>
       </c>
       <c r="I338" t="n">
-        <v>-0.077</v>
+        <v>-0.0644</v>
       </c>
       <c r="J338" t="n">
-        <v>-2.233</v>
+        <v>-1.8676</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.89</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.149</v>
+        <v>-0.1316</v>
       </c>
       <c r="J339" t="n">
-        <v>-4.321</v>
+        <v>-3.8164</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.231</v>
+        <v>-0.2115</v>
       </c>
       <c r="J340" t="n">
-        <v>-6.699</v>
+        <v>-6.1335</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.57</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.4526</v>
+        <v>-0.4467</v>
       </c>
       <c r="J341" t="n">
-        <v>-13.1254</v>
+        <v>-12.9543</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.59</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2328</v>
+        <v>1.2499</v>
       </c>
       <c r="J342" t="n">
-        <v>35.7512</v>
+        <v>36.2471</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.34</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8389</v>
+        <v>0.8164</v>
       </c>
       <c r="J343" t="n">
-        <v>24.3281</v>
+        <v>23.6756</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5043</v>
+        <v>0.4684</v>
       </c>
       <c r="J344" t="n">
-        <v>14.6247</v>
+        <v>13.5836</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.9</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.3755</v>
+        <v>-0.3339</v>
       </c>
       <c r="J345" t="n">
-        <v>-10.8895</v>
+        <v>-9.6831</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.86</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4781</v>
+        <v>-0.4374</v>
       </c>
       <c r="J346" t="n">
-        <v>-13.8649</v>
+        <v>-12.6846</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.2</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4494</v>
+        <v>0.3924</v>
       </c>
       <c r="J347" t="n">
-        <v>13.0326</v>
+        <v>11.3796</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.07</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2029</v>
+        <v>0.161</v>
       </c>
       <c r="J348" t="n">
-        <v>5.8841</v>
+        <v>4.669</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.02</v>
       </c>
       <c r="I349" t="n">
-        <v>0.0823</v>
+        <v>0.0586</v>
       </c>
       <c r="J349" t="n">
-        <v>2.3867</v>
+        <v>1.6994</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3236</v>
+        <v>-0.3068</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.384399999999999</v>
+        <v>-8.8972</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3513</v>
+        <v>-0.3364</v>
       </c>
       <c r="J351" t="n">
-        <v>-10.1877</v>
+        <v>-9.755599999999999</v>
       </c>
     </row>
     <row r="352">
@@ -16429,10 +16429,10 @@
         <v>1.53</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1175</v>
+        <v>1.1311</v>
       </c>
       <c r="J352" t="n">
-        <v>26.82</v>
+        <v>27.1464</v>
       </c>
     </row>
     <row r="353">
@@ -16469,10 +16469,10 @@
         <v>1.52</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1043</v>
+        <v>1.1175</v>
       </c>
       <c r="J353" t="n">
-        <v>26.5032</v>
+        <v>26.82</v>
       </c>
     </row>
     <row r="354">
@@ -16509,10 +16509,10 @@
         <v>1.45</v>
       </c>
       <c r="I354" t="n">
-        <v>1.0058</v>
+        <v>1.0079</v>
       </c>
       <c r="J354" t="n">
-        <v>24.1392</v>
+        <v>24.1896</v>
       </c>
     </row>
     <row r="355">
@@ -16549,10 +16549,10 @@
         <v>1.2</v>
       </c>
       <c r="I355" t="n">
-        <v>0.5251</v>
+        <v>0.496</v>
       </c>
       <c r="J355" t="n">
-        <v>12.6024</v>
+        <v>11.904</v>
       </c>
     </row>
     <row r="356">
@@ -16589,10 +16589,10 @@
         <v>1.05</v>
       </c>
       <c r="I356" t="n">
-        <v>0.1447</v>
+        <v>0.118</v>
       </c>
       <c r="J356" t="n">
-        <v>3.4728</v>
+        <v>2.832</v>
       </c>
     </row>
     <row r="357">
@@ -16629,10 +16629,10 @@
         <v>1.07</v>
       </c>
       <c r="I357" t="n">
-        <v>0.2503</v>
+        <v>0.2108</v>
       </c>
       <c r="J357" t="n">
-        <v>6.0072</v>
+        <v>5.0592</v>
       </c>
     </row>
     <row r="358">
@@ -16669,10 +16669,10 @@
         <v>0.86</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.1718</v>
+        <v>-0.1558</v>
       </c>
       <c r="J358" t="n">
-        <v>-4.1232</v>
+        <v>-3.7392</v>
       </c>
     </row>
     <row r="359">
@@ -16709,10 +16709,10 @@
         <v>0.85</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.1825</v>
+        <v>-0.1663</v>
       </c>
       <c r="J359" t="n">
-        <v>-4.38</v>
+        <v>-3.9912</v>
       </c>
     </row>
     <row r="360">
@@ -16749,10 +16749,10 @@
         <v>0.62</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.398</v>
+        <v>-0.3863</v>
       </c>
       <c r="J360" t="n">
-        <v>-9.552</v>
+        <v>-9.2712</v>
       </c>
     </row>
     <row r="361">
@@ -16789,10 +16789,10 @@
         <v>0.51</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.495</v>
+        <v>-0.4933</v>
       </c>
       <c r="J361" t="n">
-        <v>-11.88</v>
+        <v>-11.8392</v>
       </c>
     </row>
     <row r="362">
@@ -16829,10 +16829,10 @@
         <v>1.35</v>
       </c>
       <c r="I362" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8455</v>
       </c>
       <c r="J362" t="n">
-        <v>23.3928</v>
+        <v>22.8285</v>
       </c>
     </row>
     <row r="363">
@@ -16869,10 +16869,10 @@
         <v>1.15</v>
       </c>
       <c r="I363" t="n">
-        <v>0.4399</v>
+        <v>0.4025</v>
       </c>
       <c r="J363" t="n">
-        <v>11.8773</v>
+        <v>10.8675</v>
       </c>
     </row>
     <row r="364">
@@ -16909,10 +16909,10 @@
         <v>1.14</v>
       </c>
       <c r="I364" t="n">
-        <v>0.4171</v>
+        <v>0.3799</v>
       </c>
       <c r="J364" t="n">
-        <v>11.2617</v>
+        <v>10.2573</v>
       </c>
     </row>
     <row r="365">
@@ -16949,10 +16949,10 @@
         <v>1.09</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2928</v>
+        <v>0.259</v>
       </c>
       <c r="J365" t="n">
-        <v>7.9056</v>
+        <v>6.993</v>
       </c>
     </row>
     <row r="366">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.0834</v>
+        <v>-0.0626</v>
       </c>
       <c r="J366" t="n">
-        <v>-2.2518</v>
+        <v>-1.6902</v>
       </c>
     </row>
     <row r="367">
@@ -17029,10 +17029,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5214</v>
       </c>
       <c r="J367" t="n">
-        <v>15.6357</v>
+        <v>14.0778</v>
       </c>
     </row>
     <row r="368">
@@ -17069,10 +17069,10 @@
         <v>1.26</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5464</v>
+        <v>0.4884</v>
       </c>
       <c r="J368" t="n">
-        <v>14.7528</v>
+        <v>13.1868</v>
       </c>
     </row>
     <row r="369">
@@ -17109,10 +17109,10 @@
         <v>0.9</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.1431</v>
+        <v>-0.1242</v>
       </c>
       <c r="J369" t="n">
-        <v>-3.8637</v>
+        <v>-3.3534</v>
       </c>
     </row>
     <row r="370">
@@ -17149,10 +17149,10 @@
         <v>0.72</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3249</v>
+        <v>-0.3083</v>
       </c>
       <c r="J370" t="n">
-        <v>-8.7723</v>
+        <v>-8.3241</v>
       </c>
     </row>
     <row r="371">
@@ -17189,10 +17189,10 @@
         <v>0.61</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4245</v>
+        <v>-0.4163</v>
       </c>
       <c r="J371" t="n">
-        <v>-11.4615</v>
+        <v>-11.2401</v>
       </c>
     </row>
     <row r="372">
@@ -17229,10 +17229,10 @@
         <v>1.76</v>
       </c>
       <c r="I372" t="n">
-        <v>1.4364</v>
+        <v>1.4654</v>
       </c>
       <c r="J372" t="n">
-        <v>35.91</v>
+        <v>36.635</v>
       </c>
     </row>
     <row r="373">
@@ -17269,10 +17269,10 @@
         <v>1.19</v>
       </c>
       <c r="I373" t="n">
-        <v>0.5185</v>
+        <v>0.4862</v>
       </c>
       <c r="J373" t="n">
-        <v>12.9625</v>
+        <v>12.155</v>
       </c>
     </row>
     <row r="374">
@@ -17309,10 +17309,10 @@
         <v>1.16</v>
       </c>
       <c r="I374" t="n">
-        <v>0.4505</v>
+        <v>0.4175</v>
       </c>
       <c r="J374" t="n">
-        <v>11.2625</v>
+        <v>10.4375</v>
       </c>
     </row>
     <row r="375">
@@ -17349,10 +17349,10 @@
         <v>1.12</v>
       </c>
       <c r="I375" t="n">
-        <v>0.3542</v>
+        <v>0.3214</v>
       </c>
       <c r="J375" t="n">
-        <v>8.855</v>
+        <v>8.035</v>
       </c>
     </row>
     <row r="376">
@@ -17389,10 +17389,10 @@
         <v>0.99</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.101</v>
+        <v>-0.0805</v>
       </c>
       <c r="J376" t="n">
-        <v>-2.525</v>
+        <v>-2.0125</v>
       </c>
     </row>
     <row r="377">
@@ -17429,10 +17429,10 @@
         <v>0.9</v>
       </c>
       <c r="I377" t="n">
-        <v>-0.1301</v>
+        <v>-0.115</v>
       </c>
       <c r="J377" t="n">
-        <v>-3.2525</v>
+        <v>-2.875</v>
       </c>
     </row>
     <row r="378">
@@ -17469,10 +17469,10 @@
         <v>0.87</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1639</v>
+        <v>-0.1477</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.0975</v>
+        <v>-3.6925</v>
       </c>
     </row>
     <row r="379">
@@ -17509,10 +17509,10 @@
         <v>0.85</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1853</v>
+        <v>-0.1685</v>
       </c>
       <c r="J379" t="n">
-        <v>-4.6325</v>
+        <v>-4.2125</v>
       </c>
     </row>
     <row r="380">
@@ -17549,10 +17549,10 @@
         <v>0.73</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3005</v>
+        <v>-0.2833</v>
       </c>
       <c r="J380" t="n">
-        <v>-7.5125</v>
+        <v>-7.0825</v>
       </c>
     </row>
     <row r="381">
@@ -17589,10 +17589,10 @@
         <v>0.68</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3466</v>
+        <v>-0.3313</v>
       </c>
       <c r="J381" t="n">
-        <v>-8.664999999999999</v>
+        <v>-8.282500000000001</v>
       </c>
     </row>
     <row r="382">
@@ -17629,10 +17629,10 @@
         <v>1.22</v>
       </c>
       <c r="I382" t="n">
-        <v>0.6345</v>
+        <v>0.5974</v>
       </c>
       <c r="J382" t="n">
-        <v>17.766</v>
+        <v>16.7272</v>
       </c>
     </row>
     <row r="383">
@@ -17669,10 +17669,10 @@
         <v>1.06</v>
       </c>
       <c r="I383" t="n">
-        <v>0.2313</v>
+        <v>0.1944</v>
       </c>
       <c r="J383" t="n">
-        <v>6.4764</v>
+        <v>5.4432</v>
       </c>
     </row>
     <row r="384">
@@ -17709,10 +17709,10 @@
         <v>0.96</v>
       </c>
       <c r="I384" t="n">
-        <v>-0.1681</v>
+        <v>-0.1368</v>
       </c>
       <c r="J384" t="n">
-        <v>-4.7068</v>
+        <v>-3.8304</v>
       </c>
     </row>
     <row r="385">
@@ -17749,10 +17749,10 @@
         <v>0.9</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.3412</v>
+        <v>-0.2994</v>
       </c>
       <c r="J385" t="n">
-        <v>-9.553599999999999</v>
+        <v>-8.3832</v>
       </c>
     </row>
     <row r="386">
@@ -17789,10 +17789,10 @@
         <v>0.84</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4923</v>
+        <v>-0.45</v>
       </c>
       <c r="J386" t="n">
-        <v>-13.7844</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="387">
@@ -17829,10 +17829,10 @@
         <v>1.31</v>
       </c>
       <c r="I387" t="n">
-        <v>0.597</v>
+        <v>0.5372</v>
       </c>
       <c r="J387" t="n">
-        <v>16.716</v>
+        <v>15.0416</v>
       </c>
     </row>
     <row r="388">
@@ -17869,10 +17869,10 @@
         <v>1.17</v>
       </c>
       <c r="I388" t="n">
-        <v>0.3697</v>
+        <v>0.3155</v>
       </c>
       <c r="J388" t="n">
-        <v>10.3516</v>
+        <v>8.834</v>
       </c>
     </row>
     <row r="389">
@@ -17909,10 +17909,10 @@
         <v>1.03</v>
       </c>
       <c r="I389" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J389" t="n">
-        <v>2.6376</v>
+        <v>1.988</v>
       </c>
     </row>
     <row r="390">
@@ -17949,10 +17949,10 @@
         <v>0.96</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.062</v>
       </c>
       <c r="J390" t="n">
-        <v>-2.1644</v>
+        <v>-1.736</v>
       </c>
     </row>
     <row r="391">
@@ -17989,10 +17989,10 @@
         <v>0.84</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.2174</v>
+        <v>-0.1969</v>
       </c>
       <c r="J391" t="n">
-        <v>-6.0872</v>
+        <v>-5.5132</v>
       </c>
     </row>
   </sheetData>
